--- a/raw_data/Instrumento_mercy_ODK.xlsx
+++ b/raw_data/Instrumento_mercy_ODK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\EQUILIBRIUM   Intranet 🌍📂\🥁 PROYECTOS\🏆 Proyectos S. Desarrollo\176. Mercy Corps\02. Implementación\Campo Mercy\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C302D7F0-D89B-410F-A46B-E17AC431DC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED126A4-7223-4A79-848D-4DC36DECD2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="534" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">choices!$A$1:$D$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$T$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$T$221</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="949">
   <si>
     <t>deviceid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2862,15 +2862,6 @@
     <t>Ninguna</t>
   </si>
   <si>
-    <t>select_multiple necesidades</t>
-  </si>
-  <si>
-    <t>nb_no_satisfechas</t>
-  </si>
-  <si>
-    <t>Puede seleccionar más de una</t>
-  </si>
-  <si>
     <t>necesidades</t>
   </si>
   <si>
@@ -3624,9 +3615,6 @@
     <t>Muchas gracias por su tiempo.</t>
   </si>
   <si>
-    <t>${satisfaccion_nb} &gt; 1</t>
-  </si>
-  <si>
     <t>socio_pull</t>
   </si>
   <si>
@@ -3792,15 +3780,6 @@
     <t>(Ej: "Llamar después de las 6pm", "Llamar por WhatsApp porque no tengo señal").</t>
   </si>
   <si>
-    <t>13.  ¿Cuáles de las siguientes condiciones de cuidado o dependencia se presentan en su hogar?</t>
-  </si>
-  <si>
-    <t>Seleccione todas las que apliquen</t>
-  </si>
-  <si>
-    <t>cuidado_hogar</t>
-  </si>
-  <si>
     <t>cuidado</t>
   </si>
   <si>
@@ -3814,15 +3793,6 @@
   </si>
   <si>
     <t>Ninguna de los anteriores</t>
-  </si>
-  <si>
-    <t>not(selected(., '4') and count-selected(.) &gt; 1)</t>
-  </si>
-  <si>
-    <t>select_multiple cuidado</t>
-  </si>
-  <si>
-    <t>Si marca "Ninguna de las anteriores" no puede marcar nada más</t>
   </si>
   <si>
     <t>14. Ahora, vamos a confirmar información sobre su hogar &lt;br&gt; Confirmo que el jefe del hogar sigue siendo el Sr./Sra. ${pull_name} ¿Es correcto?</t>
@@ -3950,18 +3920,9 @@
     <t>50. En los últimos 3 meses ¿su hogar ha podido satisfacer todas, la mayoría, algunas o ninguna de las necesidades básicas?</t>
   </si>
   <si>
-    <t>51. ¿Cuáles son las necesidades básicas que su hogar no puede satisfacer?</t>
-  </si>
-  <si>
     <t>52.  ¿En el último mes (30 días), alguien en su hogar se vio en la necesidad de hacer alguna de las siguientes actividades debido a que no había suficientes alimentos o dinero para comprar comida?</t>
   </si>
   <si>
-    <t>53. Durante su permanencia en Colombia, ¿usted o algún miembro de su familia ha experimentado alguna de las siguientes situaciones de inseguridad o violencia? (Seleccione todas las que apliquen).</t>
-  </si>
-  <si>
-    <t>select_multiple inseguridad</t>
-  </si>
-  <si>
     <t>Violencia física / abuso</t>
   </si>
   <si>
@@ -3983,18 +3944,6 @@
     <t xml:space="preserve"> Violencia basada en género</t>
   </si>
   <si>
-    <t>not(selected(., '8') and count-selected(.) &gt; 1)</t>
-  </si>
-  <si>
-    <t>Si selecciona que no ha sentido inseguridad no puede marcar nada más</t>
-  </si>
-  <si>
-    <t>54. Durante su permanencia en el país, ¿se ha sentido discriminado/a por alguno de los siguientes motivos?</t>
-  </si>
-  <si>
-    <t>select_multiple discriminacion</t>
-  </si>
-  <si>
     <t>Por su nacionalidad</t>
   </si>
   <si>
@@ -4022,9 +3971,6 @@
     <t>No he sentido discriminación</t>
   </si>
   <si>
-    <t>Si selecciona que no ha sentido discriminado no puede marcar nada más</t>
-  </si>
-  <si>
     <t>55. ¿Quién en el hogar decide cómo usar el dinero (decide sobre los gastos del hogar)?</t>
   </si>
   <si>
@@ -4085,36 +4031,6 @@
     <t>umbral_alerta_gastos</t>
   </si>
   <si>
-    <t>&lt;span style="color:red; font-weight:bold;"&gt;REVISIÓN DE GASTOS:&lt;/span&gt;&lt;br/&gt;
-Para ajustar la diferencia, por favor revise los valores ingresados y seleccione cuál desea corregir:&lt;br/&gt;&lt;br/&gt;
-• Alimentos: &lt;b&gt;${gasto_alimentos_number}&lt;/b&gt;&lt;br/&gt;
-• Educación: &lt;b&gt;${gasto_educacion_number}&lt;/b&gt;&lt;br/&gt;
-• Transporte: &lt;b&gt;${gasto_transporte_number}&lt;/b&gt;&lt;br/&gt;
-• Salud: &lt;b&gt;${gasto_salud_number}&lt;/b&gt;&lt;br/&gt;
-• Arriendo: &lt;b&gt;${gasto_arriendo_number}&lt;/b&gt;&lt;br/&gt;
-• Agua: &lt;b&gt;${gasto_agua_number}&lt;/b&gt;&lt;br/&gt;
-• Energía: &lt;b&gt;${gasto_energia_number}&lt;/b&gt;&lt;br/&gt;
-• Gas/Gasolina: &lt;b&gt;${gasto_gas_gasolina_number}&lt;/b&gt;&lt;br/&gt;
-• Carbón/Leña: &lt;b&gt;${gasto_carbon_lena_number}&lt;/b&gt;&lt;br/&gt;
-• Internet: &lt;b&gt;${gasto_internet_number}&lt;/b&gt;&lt;br/&gt;
-• No alimentarios: &lt;b&gt;${gasto_no_alim_number}&lt;/b&gt;&lt;br/&gt;
-• Préstamos: &lt;b&gt;${gasto_prestamos_number}&lt;/b&gt;&lt;br/&gt;
-• Inversión: &lt;b&gt;${gasto_inversion_number}&lt;/b&gt;&lt;br/&gt;
-• Remesas Ven: &lt;b&gt;${gasto_remesas_ven_number}&lt;/b&gt;&lt;br/&gt;
-• Ahorros: &lt;b&gt;${gasto_ahorros_number}&lt;/b&gt;&lt;br/&gt;
-• Otros: &lt;b&gt;${gasto_otros_number}&lt;/b&gt;&lt;br/&gt;&lt;br/&gt;
-&lt;b&gt;¿Qué rubro desea corregir?&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>Aquí el encuestador debe leer todos los valores poniendo especial atención a los ceros</t>
-  </si>
-  <si>
-    <t>corregir_cual</t>
-  </si>
-  <si>
-    <t>select_multiple lista_gastos</t>
-  </si>
-  <si>
     <t>lista_gastos</t>
   </si>
   <si>
@@ -4155,9 +4071,6 @@
   </si>
   <si>
     <t>Otros gastos</t>
-  </si>
-  <si>
-    <t>${validacion_gastos} = 0</t>
   </si>
   <si>
     <t>caseid</t>
@@ -9917,7 +9830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z226"/>
+  <dimension ref="A1:Z221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
@@ -10146,7 +10059,7 @@
     </row>
     <row r="8" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="58" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>314</v>
@@ -10186,7 +10099,7 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="N9" s="8" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -10194,12 +10107,12 @@
         <v>41</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="I10" s="50"/>
       <c r="J10" s="10"/>
       <c r="N10" s="8" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -10207,12 +10120,12 @@
         <v>41</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="I11" s="50"/>
       <c r="J11" s="10"/>
       <c r="N11" s="8" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -10220,13 +10133,13 @@
         <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>920</v>
+        <v>897</v>
       </c>
       <c r="C12" s="59"/>
       <c r="I12" s="50"/>
       <c r="J12" s="10"/>
       <c r="N12" s="8" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -10234,13 +10147,13 @@
         <v>41</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="C13" s="59"/>
       <c r="I13" s="50"/>
       <c r="J13" s="10"/>
       <c r="N13" s="8" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -10248,13 +10161,13 @@
         <v>41</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>928</v>
+        <v>905</v>
       </c>
       <c r="C14" s="59"/>
       <c r="I14" s="50"/>
       <c r="J14" s="10"/>
       <c r="N14" s="8" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -10262,13 +10175,13 @@
         <v>41</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="C15" s="59"/>
       <c r="I15" s="50"/>
       <c r="J15" s="10"/>
       <c r="N15" s="8" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -10276,13 +10189,13 @@
         <v>41</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>960</v>
+        <v>937</v>
       </c>
       <c r="C16" s="59"/>
       <c r="I16" s="50"/>
       <c r="J16" s="10"/>
       <c r="N16" s="8" t="s">
-        <v>958</v>
+        <v>935</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -10290,13 +10203,13 @@
         <v>41</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>961</v>
+        <v>938</v>
       </c>
       <c r="C17" s="59"/>
       <c r="I17" s="50"/>
       <c r="J17" s="10"/>
       <c r="N17" s="8" t="s">
-        <v>962</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -10304,13 +10217,13 @@
         <v>41</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>963</v>
+        <v>940</v>
       </c>
       <c r="C18" s="59"/>
       <c r="I18" s="50"/>
       <c r="J18" s="10"/>
       <c r="N18" s="8" t="s">
-        <v>964</v>
+        <v>941</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="47.25">
@@ -10318,13 +10231,13 @@
         <v>36</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>965</v>
+        <v>942</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>967</v>
+        <v>944</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="8" t="s">
@@ -10350,7 +10263,7 @@
         <v>290</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>919</v>
+        <v>896</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -10379,7 +10292,7 @@
         <v>299</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>328</v>
@@ -10396,10 +10309,10 @@
         <v>295</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>957</v>
+        <v>934</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>38</v>
@@ -10445,7 +10358,7 @@
         <v>333</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J27" s="10"/>
       <c r="K27" s="8" t="s">
@@ -10457,13 +10370,13 @@
         <v>41</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>924</v>
+        <v>901</v>
       </c>
       <c r="C28" s="51"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="N28" s="10" t="s">
-        <v>926</v>
+        <v>903</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="31.5">
@@ -10471,13 +10384,13 @@
         <v>41</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="C29" s="51"/>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="N29" s="10" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="141.75">
@@ -10485,13 +10398,13 @@
         <v>41</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>925</v>
+        <v>902</v>
       </c>
       <c r="C30" s="51"/>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="N30" s="10" t="s">
-        <v>956</v>
+        <v>933</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="141.75">
@@ -10499,13 +10412,13 @@
         <v>41</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>927</v>
+        <v>904</v>
       </c>
       <c r="C31" s="51"/>
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="N31" s="10" t="s">
-        <v>956</v>
+        <v>933</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -10513,13 +10426,13 @@
         <v>41</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>932</v>
+        <v>909</v>
       </c>
       <c r="C32" s="51"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="N32" s="8" t="s">
-        <v>937</v>
+        <v>914</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="31.5">
@@ -10527,13 +10440,13 @@
         <v>43</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="8" t="s">
@@ -10545,13 +10458,13 @@
         <v>41</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="C34" s="51"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="N34" s="8" t="s">
-        <v>933</v>
+        <v>910</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -10559,13 +10472,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="8" t="s">
@@ -10590,11 +10503,11 @@
         <v>157</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C37" s="51"/>
       <c r="F37" s="8" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -10604,11 +10517,11 @@
         <v>157</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C38" s="51"/>
       <c r="F38" s="8" t="s">
-        <v>934</v>
+        <v>911</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -10618,11 +10531,11 @@
         <v>157</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C39" s="51"/>
       <c r="F39" s="8" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -10635,7 +10548,7 @@
         <v>303</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>306</v>
@@ -10652,7 +10565,7 @@
         <v>433</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>304</v>
@@ -10672,7 +10585,7 @@
         <v>305</v>
       </c>
       <c r="C42" s="44" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>307</v>
@@ -10706,10 +10619,10 @@
         <v>153</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="N45" s="54" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -10725,10 +10638,10 @@
         <v>153</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="N47" s="54" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -10739,7 +10652,7 @@
         <v>338</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -10750,7 +10663,7 @@
         <v>339</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="47.25">
@@ -10761,7 +10674,7 @@
         <v>337</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>38</v>
@@ -10775,10 +10688,10 @@
         <v>340</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>38</v>
@@ -10792,13 +10705,13 @@
         <v>342</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="F52" s="49" t="s">
         <v>343</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="K52" s="8" t="s">
         <v>38</v>
@@ -10809,11 +10722,11 @@
         <v>41</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="F53" s="49"/>
       <c r="N53" s="8" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="31.5">
@@ -10827,10 +10740,10 @@
         <v>347</v>
       </c>
       <c r="F54" s="52" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>38</v>
@@ -10844,13 +10757,13 @@
         <v>348</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>349</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>38</v>
@@ -10864,7 +10777,7 @@
         <v>352</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>38</v>
@@ -10878,7 +10791,7 @@
         <v>353</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="K57" s="8" t="s">
         <v>38</v>
@@ -10895,10 +10808,10 @@
         <v>355</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="K58" s="8" t="s">
         <v>38</v>
@@ -10912,7 +10825,7 @@
         <v>356</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="K59" s="8" t="s">
         <v>38</v>
@@ -10935,7 +10848,7 @@
         <v>360</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="K60" s="8" t="s">
         <v>38</v>
@@ -10946,156 +10859,150 @@
         <v>43</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="K61" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="63">
+    <row r="62" spans="1:14">
       <c r="A62" s="8" t="s">
-        <v>796</v>
+        <v>153</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>787</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>797</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>38</v>
+        <v>694</v>
+      </c>
+      <c r="N62" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>697</v>
       </c>
       <c r="N63" s="54" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>700</v>
-      </c>
-      <c r="N64" s="54" t="s">
-        <v>702</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>701</v>
+      </c>
+      <c r="N66" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="78.75">
       <c r="A67" s="8" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="N67" s="54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="78.75">
+        <v>388</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="31.5">
       <c r="A68" s="8" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>798</v>
+        <v>390</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="K68" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="31.5">
+    <row r="69" spans="1:14">
       <c r="A69" s="8" t="s">
-        <v>43</v>
+        <v>404</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>393</v>
+        <v>789</v>
       </c>
       <c r="K69" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" ht="31.5">
       <c r="A70" s="8" t="s">
-        <v>404</v>
+        <v>43</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>799</v>
+        <v>790</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="K70" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="31.5">
+    <row r="71" spans="1:14">
       <c r="A71" s="8" t="s">
-        <v>43</v>
+        <v>408</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>800</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>407</v>
+        <v>791</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="K71" s="8" t="s">
         <v>38</v>
@@ -11103,13 +11010,13 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>393</v>
@@ -11120,191 +11027,191 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="8" t="s">
-        <v>413</v>
+        <v>43</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>802</v>
+        <v>419</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="K73" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" ht="47.25">
       <c r="A74" s="8" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>419</v>
+        <v>793</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>423</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="K74" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="47.25">
+    <row r="75" spans="1:14">
       <c r="A75" s="8" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>803</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="K75" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="N75" s="8" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="31.5">
+      <c r="A76" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="K76" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="N76" s="8" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="31.5">
+    <row r="77" spans="1:14" ht="47.25">
       <c r="A77" s="8" t="s">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>436</v>
+        <v>746</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>437</v>
       </c>
       <c r="K77" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="47.25">
+    <row r="78" spans="1:14">
       <c r="A78" s="8" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>38</v>
+        <v>702</v>
+      </c>
+      <c r="N78" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="N79" s="54" t="s">
-        <v>696</v>
+        <v>703</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="N80" s="8" t="s">
-        <v>707</v>
+        <v>387</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
+        <v>695</v>
+      </c>
+      <c r="N82" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="31.5">
       <c r="A83" s="8" t="s">
-        <v>153</v>
+        <v>794</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="N83" s="54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="31.5">
+        <v>795</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N83" s="54"/>
+    </row>
+    <row r="84" spans="1:14" ht="63">
       <c r="A84" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="I84" s="8" t="s">
         <v>804</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>812</v>
       </c>
       <c r="K84" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N84" s="54"/>
-    </row>
-    <row r="85" spans="1:14" ht="63">
+    </row>
+    <row r="85" spans="1:14" ht="31.5">
       <c r="A85" s="8" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="K85" s="8" t="s">
         <v>38</v>
@@ -11312,16 +11219,16 @@
     </row>
     <row r="86" spans="1:14" ht="31.5">
       <c r="A86" s="8" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="K86" s="8" t="s">
         <v>38</v>
@@ -11329,138 +11236,138 @@
     </row>
     <row r="87" spans="1:14" ht="31.5">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>378</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>816</v>
+        <v>386</v>
       </c>
       <c r="K87" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="31.5">
+    <row r="88" spans="1:14">
       <c r="A88" s="8" t="s">
-        <v>378</v>
+        <v>153</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="I88" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>38</v>
+        <v>696</v>
+      </c>
+      <c r="N88" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="N89" s="54" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="N90" s="54" t="s">
-        <v>703</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>361</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
+        <v>705</v>
+      </c>
+      <c r="N92" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="47.25">
       <c r="A93" s="8" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="N93" s="54" t="s">
-        <v>696</v>
+        <v>529</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="47.25">
       <c r="A94" s="8" t="s">
-        <v>291</v>
+        <v>530</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="K94" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="47.25">
+    <row r="95" spans="1:14" ht="31.5">
       <c r="A95" s="8" t="s">
-        <v>533</v>
+        <v>291</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="K95" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="31.5">
+    <row r="96" spans="1:14" ht="47.25">
       <c r="A96" s="8" t="s">
-        <v>291</v>
+        <v>537</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="K96" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="47.25">
+    <row r="97" spans="1:11">
       <c r="A97" s="8" t="s">
-        <v>540</v>
+        <v>43</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>541</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>825</v>
+        <v>542</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>812</v>
       </c>
       <c r="K97" s="8" t="s">
         <v>38</v>
@@ -11468,46 +11375,49 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B98" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="299.25">
+      <c r="A99" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C99" s="9" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="8" t="s">
         <v>545</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="299.25">
-      <c r="A100" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>547</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>826</v>
+        <v>548</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>550</v>
@@ -11516,7 +11426,7 @@
         <v>551</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>99</v>
@@ -11527,16 +11437,16 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B102" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="C102" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="D102" s="8" t="s">
         <v>554</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>99</v>
@@ -11547,7 +11457,7 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>555</v>
@@ -11556,7 +11466,7 @@
         <v>556</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>99</v>
@@ -11567,16 +11477,16 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B104" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="C104" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="D104" s="8" t="s">
         <v>559</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>576</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>99</v>
@@ -11585,40 +11495,40 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" ht="63">
       <c r="A105" s="8" t="s">
-        <v>548</v>
+        <v>36</v>
       </c>
       <c r="B105" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B106" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C106" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D106" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="F106" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="K105" s="8" t="s">
+      <c r="K106" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="63">
-      <c r="A106" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>563</v>
@@ -11638,7 +11548,7 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>566</v>
@@ -11658,7 +11568,7 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B109" s="8" t="s">
         <v>569</v>
@@ -11678,63 +11588,60 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8" t="s">
-        <v>548</v>
+        <v>46</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K110" s="8" t="s">
-        <v>38</v>
+        <v>543</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
+        <v>582</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="220.5">
       <c r="A112" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" ht="220.5">
+        <v>583</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="63">
       <c r="A113" s="8" t="s">
-        <v>36</v>
+        <v>545</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>592</v>
+        <v>817</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="63">
       <c r="A114" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>99</v>
@@ -11743,15 +11650,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="63">
+    <row r="115" spans="1:14" ht="47.25">
       <c r="A115" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>99</v>
@@ -11760,15 +11667,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="47.25">
+    <row r="116" spans="1:14" ht="78.75">
       <c r="A116" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>99</v>
@@ -11777,15 +11684,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="78.75">
+    <row r="117" spans="1:14" ht="47.25">
       <c r="A117" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>99</v>
@@ -11794,319 +11701,310 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="47.25">
+    <row r="118" spans="1:14">
       <c r="A118" s="8" t="s">
-        <v>548</v>
+        <v>46</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>831</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K118" s="8" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="47.25">
+      <c r="A119" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="K119" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
-      <c r="A119" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" ht="47.25">
+    <row r="120" spans="1:14" ht="31.5">
       <c r="A120" s="8" t="s">
-        <v>291</v>
+        <v>595</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>832</v>
+        <v>823</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>946</v>
       </c>
       <c r="K120" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="31.5">
+    <row r="121" spans="1:14" ht="47.25">
       <c r="A121" s="8" t="s">
-        <v>598</v>
+        <v>291</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>833</v>
-      </c>
-      <c r="I121" s="8" t="s">
-        <v>969</v>
+        <v>824</v>
       </c>
       <c r="K121" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="47.25">
+    <row r="122" spans="1:14" ht="31.5">
       <c r="A122" s="8" t="s">
-        <v>291</v>
+        <v>595</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>834</v>
+        <v>825</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>947</v>
       </c>
       <c r="K122" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="31.5">
+    <row r="123" spans="1:14" ht="47.25">
       <c r="A123" s="8" t="s">
-        <v>598</v>
+        <v>291</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>835</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>970</v>
+        <v>826</v>
       </c>
       <c r="K123" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="47.25">
+    <row r="124" spans="1:14" ht="31.5">
       <c r="A124" s="8" t="s">
-        <v>291</v>
+        <v>595</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>836</v>
+        <v>827</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>948</v>
       </c>
       <c r="K124" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="31.5">
+    <row r="125" spans="1:14">
       <c r="A125" s="8" t="s">
-        <v>598</v>
+        <v>153</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>837</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="K125" s="8" t="s">
-        <v>38</v>
+        <v>706</v>
+      </c>
+      <c r="N125" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="N126" s="54" t="s">
-        <v>696</v>
+        <v>707</v>
+      </c>
+      <c r="N126" s="8" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="N127" s="8" t="s">
-        <v>711</v>
+        <v>528</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>531</v>
+        <v>469</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="N129" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="63">
+      <c r="A130" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="K130" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B129" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
-      <c r="A130" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="N130" s="54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" ht="63">
-      <c r="A131" s="8" t="s">
-        <v>470</v>
-      </c>
       <c r="B131" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>838</v>
-      </c>
-      <c r="K131" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="94.5">
+      <c r="A132" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="47.25">
+      <c r="A133" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="K133" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="47.25">
-      <c r="A132" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="C132" s="9" t="s">
-        <v>839</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="K132" s="8" t="s">
+    <row r="134" spans="1:14">
+      <c r="A134" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K134" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
-      <c r="A133" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B133" s="8" t="s">
+    <row r="135" spans="1:14">
+      <c r="A135" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="F133" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" ht="94.5">
-      <c r="A134" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="C134" s="9" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" ht="47.25">
-      <c r="A135" s="8" t="s">
-        <v>490</v>
-      </c>
       <c r="B135" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K135" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" ht="31.5">
       <c r="A136" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K136" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" ht="47.25">
       <c r="A137" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K137" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="31.5">
+    <row r="138" spans="1:14" ht="94.5">
       <c r="A138" s="8" t="s">
-        <v>490</v>
+        <v>36</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>495</v>
+        <v>730</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="K138" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" ht="47.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K139" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="94.5">
+    <row r="140" spans="1:14" ht="31.5">
       <c r="A140" s="8" t="s">
-        <v>36</v>
+        <v>487</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>734</v>
+        <v>495</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
+        <v>510</v>
+      </c>
+      <c r="K140" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="31.5">
       <c r="A141" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K141" s="8" t="s">
         <v>38</v>
@@ -12114,13 +12012,13 @@
     </row>
     <row r="142" spans="1:14" ht="31.5">
       <c r="A142" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K142" s="8" t="s">
         <v>38</v>
@@ -12128,66 +12026,66 @@
     </row>
     <row r="143" spans="1:14" ht="31.5">
       <c r="A143" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K143" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="31.5">
+    <row r="144" spans="1:14" ht="94.5">
       <c r="A144" s="8" t="s">
-        <v>490</v>
+        <v>36</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>500</v>
+        <v>731</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="K144" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" ht="31.5">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K145" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="94.5">
+    <row r="146" spans="1:14" ht="31.5">
       <c r="A146" s="8" t="s">
-        <v>36</v>
+        <v>487</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>735</v>
+        <v>500</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14">
+        <v>515</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="31.5">
       <c r="A147" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K147" s="8" t="s">
         <v>38</v>
@@ -12195,13 +12093,13 @@
     </row>
     <row r="148" spans="1:14" ht="31.5">
       <c r="A148" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K148" s="8" t="s">
         <v>38</v>
@@ -12209,92 +12107,62 @@
     </row>
     <row r="149" spans="1:14" ht="31.5">
       <c r="A149" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K149" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="31.5">
+    <row r="150" spans="1:14">
       <c r="A150" s="8" t="s">
-        <v>490</v>
+        <v>46</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="C150" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="K150" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" ht="31.5">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151" s="8" t="s">
-        <v>490</v>
+        <v>153</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="C151" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="K151" s="8" t="s">
-        <v>38</v>
+        <v>710</v>
+      </c>
+      <c r="N151" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="N152" s="8" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
+      <c r="A153" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B152" s="8" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" ht="110.25">
-      <c r="A153" s="8" t="s">
-        <v>842</v>
-      </c>
       <c r="B153" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="C153" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>850</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>851</v>
-      </c>
-      <c r="K153" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" ht="78.75">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154" s="8" t="s">
-        <v>853</v>
+        <v>39</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="C154" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>850</v>
-      </c>
-      <c r="H154" s="10" t="s">
-        <v>863</v>
-      </c>
-      <c r="K154" s="8" t="s">
-        <v>38</v>
+        <v>629</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -12305,333 +12173,353 @@
         <v>713</v>
       </c>
       <c r="N155" s="54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" ht="47.25">
       <c r="A156" s="8" t="s">
-        <v>41</v>
+        <v>630</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="N156" s="8" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14">
+        <v>631</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" ht="47.25">
       <c r="A157" s="8" t="s">
-        <v>46</v>
+        <v>632</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14">
+        <v>633</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" ht="31.5">
       <c r="A158" s="8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="8" t="s">
-        <v>153</v>
+        <v>635</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="N159" s="54" t="s">
-        <v>696</v>
+        <v>636</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:14" ht="47.25">
       <c r="A160" s="8" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>864</v>
+        <v>850</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="47.25">
+    <row r="161" spans="1:14" ht="78.75">
       <c r="A161" s="8" t="s">
-        <v>635</v>
+        <v>45</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>636</v>
+        <v>852</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>865</v>
+        <v>894</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>854</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="31.5">
+    <row r="162" spans="1:14">
       <c r="A162" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B162" s="8" t="str">
+        <f>CONCATENATE(B161,"_number")</f>
+        <v>ingresos_mes_number</v>
+      </c>
+      <c r="N162" s="8" t="str">
+        <f>CONCATENATE("if(${",B161,"} = 88 or ${",B161,"} = 99, 0, ${",B161,"})")</f>
+        <v>if(${ingresos_mes} = 88 or ${ingresos_mes} = 99, 0, ${ingresos_mes})</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" ht="78.75">
+      <c r="A163" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B162" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="C162" s="9" t="s">
-        <v>866</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="K162" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14">
-      <c r="A163" s="8" t="s">
-        <v>638</v>
-      </c>
       <c r="B163" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>867</v>
+        <v>747</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>641</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="47.25">
+    <row r="164" spans="1:14">
       <c r="A164" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="B164" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B164" s="8" t="str">
+        <f>CONCATENATE(B163,"_number")</f>
+        <v>gasto_alimentos_number</v>
+      </c>
+      <c r="N164" s="8" t="str">
+        <f>CONCATENATE("if(${",B163,"} = 88 or ${",B163,"} = 99, 0, ${",B163,"})")</f>
+        <v>if(${gasto_alimentos} = 88 or ${gasto_alimentos} = 99, 0, ${gasto_alimentos})</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14">
+      <c r="A165" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="C165" t="s">
+        <v>917</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" ht="78.75">
+      <c r="A166" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="D166" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="C164" s="9" t="s">
-        <v>868</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="K164" s="8" t="s">
+      <c r="K166" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="78.75">
-      <c r="A165" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="C165" s="9" t="s">
-        <v>917</v>
-      </c>
-      <c r="G165" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>872</v>
-      </c>
-      <c r="K165" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14">
-      <c r="A166" s="8" t="s">
+    <row r="167" spans="1:14">
+      <c r="A167" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B166" s="8" t="str">
-        <f>CONCATENATE(B165,"_number")</f>
-        <v>ingresos_mes_number</v>
-      </c>
-      <c r="N166" s="8" t="str">
-        <f>CONCATENATE("if(${",B165,"} = 88 or ${",B165,"} = 99, 0, ${",B165,"})")</f>
-        <v>if(${ingresos_mes} = 88 or ${ingresos_mes} = 99, 0, ${ingresos_mes})</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" ht="78.75">
-      <c r="A167" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="C167" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K167" s="8" t="s">
-        <v>38</v>
+      <c r="B167" s="8" t="str">
+        <f>CONCATENATE(B166,"_number")</f>
+        <v>gasto_educacion_number</v>
+      </c>
+      <c r="N167" s="8" t="str">
+        <f>CONCATENATE("if(${",B166,"} = 88 or ${",B166,"} = 99, 0, ${",B166,"})")</f>
+        <v>if(${gasto_educacion} = 88 or ${gasto_educacion} = 99, 0, ${gasto_educacion})</v>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="C168" t="s">
+        <v>918</v>
+      </c>
+      <c r="I168" s="8" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" ht="78.75">
+      <c r="A169" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="A170" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B168" s="8" t="str">
-        <f>CONCATENATE(B167,"_number")</f>
-        <v>gasto_alimentos_number</v>
-      </c>
-      <c r="N168" s="8" t="str">
-        <f>CONCATENATE("if(${",B167,"} = 88 or ${",B167,"} = 99, 0, ${",B167,"})")</f>
-        <v>if(${gasto_alimentos} = 88 or ${gasto_alimentos} = 99, 0, ${gasto_alimentos})</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14">
-      <c r="A169" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C169" t="s">
-        <v>940</v>
-      </c>
-      <c r="I169" s="8" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" ht="78.75">
-      <c r="A170" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="C170" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K170" s="8" t="s">
-        <v>38</v>
+      <c r="B170" s="8" t="str">
+        <f>CONCATENATE(B169,"_number")</f>
+        <v>gasto_transporte_number</v>
+      </c>
+      <c r="N170" s="8" t="str">
+        <f>CONCATENATE("if(${",B169,"} = 88 or ${",B169,"} = 99, 0, ${",B169,"})")</f>
+        <v>if(${gasto_transporte} = 88 or ${gasto_transporte} = 99, 0, ${gasto_transporte})</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="C171" t="s">
+        <v>919</v>
+      </c>
+      <c r="I171" s="8" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" ht="94.5">
+      <c r="A172" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B171" s="8" t="str">
-        <f>CONCATENATE(B170,"_number")</f>
-        <v>gasto_educacion_number</v>
-      </c>
-      <c r="N171" s="8" t="str">
-        <f>CONCATENATE("if(${",B170,"} = 88 or ${",B170,"} = 99, 0, ${",B170,"})")</f>
-        <v>if(${gasto_educacion} = 88 or ${gasto_educacion} = 99, 0, ${gasto_educacion})</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14">
-      <c r="A172" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="C172" t="s">
-        <v>941</v>
-      </c>
-      <c r="I172" s="8" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" ht="78.75">
-      <c r="A173" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K173" s="8" t="s">
-        <v>38</v>
+      <c r="B173" s="8" t="str">
+        <f>CONCATENATE(B172,"_number")</f>
+        <v>gasto_salud_number</v>
+      </c>
+      <c r="N173" s="8" t="str">
+        <f>CONCATENATE("if(${",B172,"} = 88 or ${",B172,"} = 99, 0, ${",B172,"})")</f>
+        <v>if(${gasto_salud} = 88 or ${gasto_salud} = 99, 0, ${gasto_salud})</v>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C174" t="s">
+        <v>920</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" ht="78.75">
+      <c r="A175" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K175" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="A176" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B174" s="8" t="str">
-        <f>CONCATENATE(B173,"_number")</f>
-        <v>gasto_transporte_number</v>
-      </c>
-      <c r="N174" s="8" t="str">
-        <f>CONCATENATE("if(${",B173,"} = 88 or ${",B173,"} = 99, 0, ${",B173,"})")</f>
-        <v>if(${gasto_transporte} = 88 or ${gasto_transporte} = 99, 0, ${gasto_transporte})</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="A175" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="C175" t="s">
-        <v>942</v>
-      </c>
-      <c r="I175" s="8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" ht="94.5">
-      <c r="A176" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B176" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K176" s="8" t="s">
-        <v>38</v>
+      <c r="B176" s="8" t="str">
+        <f>CONCATENATE(B175,"_number")</f>
+        <v>gasto_arriendo_number</v>
+      </c>
+      <c r="N176" s="8" t="str">
+        <f>CONCATENATE("if(${",B175,"} = 88 or ${",B175,"} = 99, 0, ${",B175,"})")</f>
+        <v>if(${gasto_arriendo} = 88 or ${gasto_arriendo} = 99, 0, ${gasto_arriendo})</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B177" s="8" t="str">
-        <f>CONCATENATE(B176,"_number")</f>
-        <v>gasto_salud_number</v>
-      </c>
-      <c r="N177" s="8" t="str">
-        <f>CONCATENATE("if(${",B176,"} = 88 or ${",B176,"} = 99, 0, ${",B176,"})")</f>
-        <v>if(${gasto_salud} = 88 or ${gasto_salud} = 99, 0, ${gasto_salud})</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="C177" t="s">
+        <v>921</v>
+      </c>
+      <c r="I177" s="8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" ht="31.5">
       <c r="A178" s="8" t="s">
-        <v>36</v>
+        <v>291</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="C178" t="s">
-        <v>943</v>
-      </c>
-      <c r="I178" s="8" t="s">
-        <v>673</v>
+        <v>855</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="K178" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:14" ht="78.75">
@@ -12639,13 +12527,16 @@
         <v>45</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>668</v>
+        <v>644</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>644</v>
+        <v>861</v>
+      </c>
+      <c r="I179" s="8" t="s">
+        <v>860</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>38</v>
@@ -12657,11 +12548,11 @@
       </c>
       <c r="B180" s="8" t="str">
         <f>CONCATENATE(B179,"_number")</f>
-        <v>gasto_arriendo_number</v>
+        <v>gasto_agua_number</v>
       </c>
       <c r="N180" s="8" t="str">
         <f>CONCATENATE("if(${",B179,"} = 88 or ${",B179,"} = 99, 0, ${",B179,"})")</f>
-        <v>if(${gasto_arriendo} = 88 or ${gasto_arriendo} = 99, 0, ${gasto_arriendo})</v>
+        <v>if(${gasto_agua} = 88 or ${gasto_agua} = 99, 0, ${gasto_agua})</v>
       </c>
     </row>
     <row r="181" spans="1:14">
@@ -12669,658 +12560,576 @@
         <v>36</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="C181" t="s">
-        <v>944</v>
+        <v>922</v>
       </c>
       <c r="I181" s="8" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" ht="31.5">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" ht="94.5">
       <c r="A182" s="8" t="s">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>873</v>
+        <v>647</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>874</v>
+        <v>749</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="I182" s="8" t="s">
+        <v>860</v>
       </c>
       <c r="K182" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="78.75">
+    <row r="183" spans="1:14">
       <c r="A183" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>879</v>
-      </c>
-      <c r="I183" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="K183" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="B183" s="8" t="str">
+        <f>CONCATENATE(B182,"_number")</f>
+        <v>gasto_energia_number</v>
+      </c>
+      <c r="N183" s="8" t="str">
+        <f>CONCATENATE("if(${",B182,"} = 88 or ${",B182,"} = 99, 0, ${",B182,"})")</f>
+        <v>if(${gasto_energia} = 88 or ${gasto_energia} = 99, 0, ${gasto_energia})</v>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="C184" t="s">
+        <v>923</v>
+      </c>
+      <c r="I184" s="8" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" ht="78.75">
+      <c r="A185" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="I185" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="K185" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14">
+      <c r="A186" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B184" s="8" t="str">
-        <f>CONCATENATE(B183,"_number")</f>
-        <v>gasto_agua_number</v>
-      </c>
-      <c r="N184" s="8" t="str">
-        <f>CONCATENATE("if(${",B183,"} = 88 or ${",B183,"} = 99, 0, ${",B183,"})")</f>
-        <v>if(${gasto_agua} = 88 or ${gasto_agua} = 99, 0, ${gasto_agua})</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14">
-      <c r="A185" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="C185" t="s">
-        <v>945</v>
-      </c>
-      <c r="I185" s="8" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" ht="94.5">
-      <c r="A186" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>879</v>
-      </c>
-      <c r="I186" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="K186" s="8" t="s">
-        <v>38</v>
+      <c r="B186" s="8" t="str">
+        <f>CONCATENATE(B185,"_number")</f>
+        <v>gasto_gas_gasolina_number</v>
+      </c>
+      <c r="N186" s="8" t="str">
+        <f>CONCATENATE("if(${",B185,"} = 88 or ${",B185,"} = 99, 0, ${",B185,"})")</f>
+        <v>if(${gasto_gas_gasolina} = 88 or ${gasto_gas_gasolina} = 99, 0, ${gasto_gas_gasolina})</v>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C187" t="s">
+        <v>924</v>
+      </c>
+      <c r="I187" s="8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" ht="78.75">
+      <c r="A188" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K188" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14">
+      <c r="A189" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B187" s="8" t="str">
-        <f>CONCATENATE(B186,"_number")</f>
-        <v>gasto_energia_number</v>
-      </c>
-      <c r="N187" s="8" t="str">
-        <f>CONCATENATE("if(${",B186,"} = 88 or ${",B186,"} = 99, 0, ${",B186,"})")</f>
-        <v>if(${gasto_energia} = 88 or ${gasto_energia} = 99, 0, ${gasto_energia})</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14">
-      <c r="A188" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="C188" t="s">
-        <v>946</v>
-      </c>
-      <c r="I188" s="8" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" ht="78.75">
-      <c r="A189" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B189" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="D189" s="8" t="s">
-        <v>879</v>
-      </c>
-      <c r="I189" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="K189" s="8" t="s">
-        <v>38</v>
+      <c r="B189" s="8" t="str">
+        <f>CONCATENATE(B188,"_number")</f>
+        <v>gasto_carbon_lena_number</v>
+      </c>
+      <c r="N189" s="8" t="str">
+        <f>CONCATENATE("if(${",B188,"} = 88 or ${",B188,"} = 99, 0, ${",B188,"})")</f>
+        <v>if(${gasto_carbon_lena} = 88 or ${gasto_carbon_lena} = 99, 0, ${gasto_carbon_lena})</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C190" t="s">
+        <v>925</v>
+      </c>
+      <c r="I190" s="8" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" ht="94.5">
+      <c r="A191" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K191" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14">
+      <c r="A192" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B190" s="8" t="str">
-        <f>CONCATENATE(B189,"_number")</f>
-        <v>gasto_gas_gasolina_number</v>
-      </c>
-      <c r="N190" s="8" t="str">
-        <f>CONCATENATE("if(${",B189,"} = 88 or ${",B189,"} = 99, 0, ${",B189,"})")</f>
-        <v>if(${gasto_gas_gasolina} = 88 or ${gasto_gas_gasolina} = 99, 0, ${gasto_gas_gasolina})</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14">
-      <c r="A191" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B191" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="C191" t="s">
-        <v>947</v>
-      </c>
-      <c r="I191" s="8" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" ht="78.75">
-      <c r="A192" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="C192" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D192" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K192" s="8" t="s">
-        <v>38</v>
+      <c r="B192" s="8" t="str">
+        <f>CONCATENATE(B191,"_number")</f>
+        <v>gasto_internet_number</v>
+      </c>
+      <c r="N192" s="8" t="str">
+        <f>CONCATENATE("if(${",B191,"} = 88 or ${",B191,"} = 99, 0, ${",B191,"})")</f>
+        <v>if(${gasto_internet} = 88 or ${gasto_internet} = 99, 0, ${gasto_internet})</v>
       </c>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="C193" t="s">
+        <v>926</v>
+      </c>
+      <c r="I193" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" ht="110.25">
+      <c r="A194" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K194" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
+      <c r="A195" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B193" s="8" t="str">
-        <f>CONCATENATE(B192,"_number")</f>
-        <v>gasto_carbon_lena_number</v>
-      </c>
-      <c r="N193" s="8" t="str">
-        <f>CONCATENATE("if(${",B192,"} = 88 or ${",B192,"} = 99, 0, ${",B192,"})")</f>
-        <v>if(${gasto_carbon_lena} = 88 or ${gasto_carbon_lena} = 99, 0, ${gasto_carbon_lena})</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14">
-      <c r="A194" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="C194" t="s">
-        <v>948</v>
-      </c>
-      <c r="I194" s="8" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14" ht="94.5">
-      <c r="A195" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>875</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>764</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K195" s="8" t="s">
-        <v>38</v>
+      <c r="B195" s="8" t="str">
+        <f>CONCATENATE(B194,"_number")</f>
+        <v>gasto_no_alim_number</v>
+      </c>
+      <c r="N195" s="8" t="str">
+        <f>CONCATENATE("if(${",B194,"} = 88 or ${",B194,"} = 99, 0, ${",B194,"})")</f>
+        <v>if(${gasto_no_alim} = 88 or ${gasto_no_alim} = 99, 0, ${gasto_no_alim})</v>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="C196" t="s">
+        <v>927</v>
+      </c>
+      <c r="I196" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" ht="94.5">
+      <c r="A197" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K197" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14">
+      <c r="A198" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B196" s="8" t="str">
-        <f>CONCATENATE(B195,"_number")</f>
-        <v>gasto_internet_number</v>
-      </c>
-      <c r="N196" s="8" t="str">
-        <f>CONCATENATE("if(${",B195,"} = 88 or ${",B195,"} = 99, 0, ${",B195,"})")</f>
-        <v>if(${gasto_internet} = 88 or ${gasto_internet} = 99, 0, ${gasto_internet})</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14">
-      <c r="A197" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>876</v>
-      </c>
-      <c r="C197" t="s">
-        <v>949</v>
-      </c>
-      <c r="I197" s="8" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14" ht="110.25">
-      <c r="A198" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="D198" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K198" s="8" t="s">
-        <v>38</v>
+      <c r="B198" s="8" t="str">
+        <f>CONCATENATE(B197,"_number")</f>
+        <v>gasto_prestamos_number</v>
+      </c>
+      <c r="N198" s="8" t="str">
+        <f>CONCATENATE("if(${",B197,"} = 88 or ${",B197,"} = 99, 0, ${",B197,"})")</f>
+        <v>if(${gasto_prestamos} = 88 or ${gasto_prestamos} = 99, 0, ${gasto_prestamos})</v>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="C199" t="s">
+        <v>928</v>
+      </c>
+      <c r="I199" s="8" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" ht="94.5">
+      <c r="A200" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K200" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14">
+      <c r="A201" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B199" s="8" t="str">
-        <f>CONCATENATE(B198,"_number")</f>
-        <v>gasto_no_alim_number</v>
-      </c>
-      <c r="N199" s="8" t="str">
-        <f>CONCATENATE("if(${",B198,"} = 88 or ${",B198,"} = 99, 0, ${",B198,"})")</f>
-        <v>if(${gasto_no_alim} = 88 or ${gasto_no_alim} = 99, 0, ${gasto_no_alim})</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14">
-      <c r="A200" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="C200" t="s">
-        <v>950</v>
-      </c>
-      <c r="I200" s="8" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" ht="94.5">
-      <c r="A201" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>761</v>
-      </c>
-      <c r="D201" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K201" s="8" t="s">
-        <v>38</v>
+      <c r="B201" s="8" t="str">
+        <f>CONCATENATE(B200,"_number")</f>
+        <v>gasto_inversion_number</v>
+      </c>
+      <c r="N201" s="8" t="str">
+        <f>CONCATENATE("if(${",B200,"} = 88 or ${",B200,"} = 99, 0, ${",B200,"})")</f>
+        <v>if(${gasto_inversion} = 88 or ${gasto_inversion} = 99, 0, ${gasto_inversion})</v>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C202" t="s">
+        <v>929</v>
+      </c>
+      <c r="I202" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" ht="94.5">
+      <c r="A203" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K203" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14">
+      <c r="A204" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B202" s="8" t="str">
-        <f>CONCATENATE(B201,"_number")</f>
-        <v>gasto_prestamos_number</v>
-      </c>
-      <c r="N202" s="8" t="str">
-        <f>CONCATENATE("if(${",B201,"} = 88 or ${",B201,"} = 99, 0, ${",B201,"})")</f>
-        <v>if(${gasto_prestamos} = 88 or ${gasto_prestamos} = 99, 0, ${gasto_prestamos})</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14">
-      <c r="A203" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="C203" t="s">
-        <v>951</v>
-      </c>
-      <c r="I203" s="8" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" ht="94.5">
-      <c r="A204" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>762</v>
-      </c>
-      <c r="D204" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K204" s="8" t="s">
-        <v>38</v>
+      <c r="B204" s="8" t="str">
+        <f>CONCATENATE(B203,"_number")</f>
+        <v>gasto_remesas_ven_number</v>
+      </c>
+      <c r="N204" s="8" t="str">
+        <f>CONCATENATE("if(${",B203,"} = 88 or ${",B203,"} = 99, 0, ${",B203,"})")</f>
+        <v>if(${gasto_remesas_ven} = 88 or ${gasto_remesas_ven} = 99, 0, ${gasto_remesas_ven})</v>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C205" t="s">
+        <v>930</v>
+      </c>
+      <c r="I205" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" ht="78.75">
+      <c r="A206" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K206" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B205" s="8" t="str">
-        <f>CONCATENATE(B204,"_number")</f>
-        <v>gasto_inversion_number</v>
-      </c>
-      <c r="N205" s="8" t="str">
-        <f>CONCATENATE("if(${",B204,"} = 88 or ${",B204,"} = 99, 0, ${",B204,"})")</f>
-        <v>if(${gasto_inversion} = 88 or ${gasto_inversion} = 99, 0, ${gasto_inversion})</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14">
-      <c r="A206" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>678</v>
-      </c>
-      <c r="C206" t="s">
-        <v>952</v>
-      </c>
-      <c r="I206" s="8" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" ht="94.5">
-      <c r="A207" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B207" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K207" s="8" t="s">
-        <v>38</v>
+      <c r="B207" s="8" t="str">
+        <f>CONCATENATE(B206,"_number")</f>
+        <v>gasto_ahorros_number</v>
+      </c>
+      <c r="N207" s="8" t="str">
+        <f>CONCATENATE("if(${",B206,"} = 88 or ${",B206,"} = 99, 0, ${",B206,"})")</f>
+        <v>if(${gasto_ahorros} = 88 or ${gasto_ahorros} = 99, 0, ${gasto_ahorros})</v>
       </c>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C208" t="s">
+        <v>931</v>
+      </c>
+      <c r="I208" s="8" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" ht="78.75">
+      <c r="A209" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="D209" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="K209" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14">
+      <c r="A210" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B208" s="8" t="str">
-        <f>CONCATENATE(B207,"_number")</f>
-        <v>gasto_remesas_ven_number</v>
-      </c>
-      <c r="N208" s="8" t="str">
-        <f>CONCATENATE("if(${",B207,"} = 88 or ${",B207,"} = 99, 0, ${",B207,"})")</f>
-        <v>if(${gasto_remesas_ven} = 88 or ${gasto_remesas_ven} = 99, 0, ${gasto_remesas_ven})</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14">
-      <c r="A209" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="C209" t="s">
-        <v>953</v>
-      </c>
-      <c r="I209" s="8" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" ht="78.75">
-      <c r="A210" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>880</v>
-      </c>
-      <c r="D210" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K210" s="8" t="s">
-        <v>38</v>
+      <c r="B210" s="8" t="str">
+        <f>CONCATENATE(B209,"_number")</f>
+        <v>gasto_otros_number</v>
+      </c>
+      <c r="N210" s="8" t="str">
+        <f>CONCATENATE("if(${",B209,"} = 88 or ${",B209,"} = 99, 0, ${",B209,"})")</f>
+        <v>if(${gasto_otros} = 88 or ${gasto_otros} = 99, 0, ${gasto_otros})</v>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B211" s="8" t="str">
-        <f>CONCATENATE(B210,"_number")</f>
-        <v>gasto_ahorros_number</v>
-      </c>
-      <c r="N211" s="8" t="str">
-        <f>CONCATENATE("if(${",B210,"} = 88 or ${",B210,"} = 99, 0, ${",B210,"})")</f>
-        <v>if(${gasto_ahorros} = 88 or ${gasto_ahorros} = 99, 0, ${gasto_ahorros})</v>
+        <v>36</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C211" t="s">
+        <v>932</v>
+      </c>
+      <c r="I211" s="8" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="C212" t="s">
-        <v>954</v>
-      </c>
-      <c r="I212" s="8" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" ht="78.75">
+        <v>863</v>
+      </c>
+      <c r="N212" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="D213" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="K213" s="8" t="s">
-        <v>38</v>
+        <v>865</v>
+      </c>
+      <c r="N213" s="2" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B214" s="8" t="str">
-        <f>CONCATENATE(B213,"_number")</f>
-        <v>gasto_otros_number</v>
-      </c>
-      <c r="N214" s="8" t="str">
-        <f>CONCATENATE("if(${",B213,"} = 88 or ${",B213,"} = 99, 0, ${",B213,"})")</f>
-        <v>if(${gasto_otros} = 88 or ${gasto_otros} = 99, 0, ${gasto_otros})</v>
+        <v>153</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="N214" s="54" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="C215" t="s">
-        <v>955</v>
-      </c>
-      <c r="I215" s="8" t="s">
-        <v>688</v>
+        <v>715</v>
+      </c>
+      <c r="N215" s="8" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="N216" s="2" t="s">
-        <v>882</v>
+        <v>629</v>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="N217" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14">
+      <c r="A218" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B217" s="8" t="s">
-        <v>883</v>
-      </c>
-      <c r="N217" s="2" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14" ht="409.5">
-      <c r="A218" s="8" t="s">
-        <v>887</v>
-      </c>
       <c r="B218" s="8" t="s">
-        <v>886</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>884</v>
-      </c>
-      <c r="D218" s="8" t="s">
-        <v>885</v>
-      </c>
-      <c r="I218" s="8" t="s">
-        <v>902</v>
-      </c>
-      <c r="K218" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N218" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="N218" s="8" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="8" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="N219" s="54" t="s">
-        <v>696</v>
+        <v>292</v>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="N220" s="8" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14">
+        <v>691</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" ht="31.5">
       <c r="A221" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14">
-      <c r="A222" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="N222" s="54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
-      <c r="A223" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B223" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="N223" s="8" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14">
-      <c r="A224" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B224" s="8" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11">
-      <c r="A225" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B225" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" ht="31.5">
-      <c r="A226" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="D226" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="K226" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="D221" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="K221" s="8" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <autoFilter ref="A1:T226" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T221" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T62 A65:T66 A67:M67 A68:T77 A79:M79 A80:T82 A83:M84 A85:T88 A89:M90 A91:T92 A93:M93 A94:T125 A126:M126 A127:T129 A130:M130 A155:M156 A157:T158 A159:M159 A160:T194 A219:M219 A220:T221 A222:M223 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O67:T67 A78 O79:T79 O83:T84 O89:T90 O93:T93 O126:T126 O130:T130 O155:T156 N156 O159:T159 O219:T219 O222:T223 N223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="567" priority="737" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
@@ -13331,12 +13140,12 @@
       <formula>$A1="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T62 A65:T66 A67:M67 A68:T77 A79:M79 A80:T82 A83:M84 A85:T88 A89:M90 A91:T92 A93:M93 A94:T125 A126:M126 A127:T129 A130:M130 A155:M156 A157:T158 A159:M159 A219:M219 A220:T221 A222:M223 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O67:T67 A78 O79:T79 O83:T84 O89:T90 O93:T93 O126:T126 O130:T130 O155:T156 N156 O159:T159 O219:T219 O222:T223 N223 A131:T154 A160:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A214:M214 A215:T216 A217:M218 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A156:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="564" priority="727" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T62 A65:T66 A67:M67 A68:T77 A79:M79 A80:T82 A83:M84 A85:T88 A89:M90 A91:T92 A93:M93 A94:T125 A126:M126 A127:T129 A130:M130 A155:M156 A157:T158 A159:M159 A160:T194 A219:M219 A220:T221 A222:M223 O45:T45 G52:T54 O67:T67 A78 O79:T79 O83:T84 O89:T90 O93:T93 O126:T126 O130:T130 O155:T156 N156 O159:T159 O219:T219 O222:T223 N223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="563" priority="729" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
@@ -13353,7 +13162,7 @@
       <formula>$A1="text"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A55:T62 A65:T66 A67:M67 A68:T77 A79:M79 A80:T82 A83:M84 A85:T88 A89:M90 A91:T92 A93:M93 A94:T125 A126:M126 A127:T129 A130:M130 A155:M156 A157:T158 A159:M159 A160:T194 A219:M219 A220:T221 A222:M223 O45:T45 O67:T67 A78 O79:T79 O83:T84 O89:T90 O93:T93 O126:T126 O130:T130 O155:T156 N156 O159:T159 O219:T219 O222:T223 N223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 O45:T45 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="558" priority="758" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
     </cfRule>
@@ -13364,12 +13173,12 @@
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A55:T62 A65:T66 A67:M67 A68:T77 A79:M79 A80:T82 A83:M84 A85:T88 A89:M90 A91:T92 A93:M93 A94:T125 A126:M126 A127:T129 A130:M130 A155:M156 N156 A157:T158 A159:M159 A160:T194 A219:M219 A220:T221 A222:M223 N223 O45:T45 O67:T67 A78 O79:T79 O83:T84 O89:T90 O93:T93 O126:T126 O130:T130 O155:T156 O159:T159 O219:T219 O222:T223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 N152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 N218 O45:T45 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 O155:T155 O214:T214 O217:T218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="555" priority="735" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A55:T62 A65:T66 A67:M67 O67:T67 A68:T77 A78 A79:M79 O79:T79 A80:T82 A83:M84 O83:T84 A85:T88 A89:M90 O89:T90 A91:T92 A93:M93 O93:T93 A94:T125 A126:M126 O126:T126 A127:T129 A130:M130 O130:T130 A155:M156 O155:T156 N156 A157:T158 A159:M159 O159:T159 A160:T194 A219:M219 O219:T219 A220:T221 A222:M223 O222:T223 N223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 O66:T66 A67:T76 A77 A78:M78 O78:T78 A79:T81 A82:M83 O82:T83 A84:T87 A88:M89 O88:T89 A90:T91 A92:M92 O92:T92 A93:T124 A125:M125 O125:T125 A126:T128 A129:M129 O129:T129 A151:M152 O151:T152 N152 A153:T154 A155:M155 O155:T155 A156:T190 A214:M214 O214:T214 A215:T216 A217:M218 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="554" priority="746" stopIfTrue="1">
       <formula>OR($A1="username", $A1="phonenumber", $A1="start", $A1="end", $A1="deviceid", $A1="subscriberid", $A1="simserial")</formula>
     </cfRule>
@@ -13380,59 +13189,59 @@
       <formula>$A1="end group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A55:T62 A65:T66 A67:M67 O67:T67 A68:T77 A79:M79 O79:T79 A80:T82 A83:M84 O83:T84 A85:T88 A89:M90 O89:T90 A91:T92 A93:M93 O93:T93 A94:T125 A126:M126 O126:T126 A127:T129 A130:M130 O130:T130 A155:M156 O155:T156 A157:T158 A159:M159 O159:T159 A160:T194 A219:M219 O219:T219 A220:T221 A222:M223 O222:T223 A78 N156 N223 A131:T154 A198:T218 A224:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 O66:T66 A67:T76 A78:M78 O78:T78 A79:T81 A82:M83 O82:T83 A84:T87 A88:M89 O88:T89 A90:T91 A92:M92 O92:T92 A93:T124 A125:M125 O125:T125 A126:T128 A129:M129 O129:T129 A151:M152 O151:T152 A153:T154 A155:M155 O155:T155 A156:T190 A214:M214 O214:T214 A215:T216 A217:M218 O217:T218 A77 N152 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
     <cfRule type="expression" dxfId="551" priority="765" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A195:T197">
+  <conditionalFormatting sqref="A191:T193">
     <cfRule type="expression" dxfId="550" priority="4" stopIfTrue="1">
-      <formula>$A195="image"</formula>
+      <formula>$A191="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="549" priority="5" stopIfTrue="1">
-      <formula>OR($A195="date", $A195="datetime")</formula>
+      <formula>OR($A191="date", $A191="datetime")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="548" priority="6" stopIfTrue="1">
-      <formula>OR($A195="calculate", $A195="calculate_here")</formula>
+      <formula>OR($A191="calculate", $A191="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="547" priority="8" stopIfTrue="1">
-      <formula>$A195="note"</formula>
+      <formula>$A191="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="546" priority="10" stopIfTrue="1">
-      <formula>$A195="barcode"</formula>
+      <formula>$A191="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="545" priority="12" stopIfTrue="1">
-      <formula>$A195="geopoint"</formula>
+      <formula>$A191="geopoint"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="544" priority="13" stopIfTrue="1">
-      <formula>OR($A195="audio audit", $A195="text audit")</formula>
+      <formula>OR($A191="audio audit", $A191="text audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="543" priority="14" stopIfTrue="1">
-      <formula>OR($A195="username", $A195="phonenumber", $A195="start", $A195="end", $A195="deviceid", $A195="subscriberid", $A195="simserial")</formula>
+      <formula>OR($A191="username", $A191="phonenumber", $A191="start", $A191="end", $A191="deviceid", $A191="subscriberid", $A191="simserial")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="542" priority="15" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A195, 16)="select_multiple ", LEN($A195)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A195, 17)))), AND(LEFT($A195, 11)="select_one ", LEN($A195)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A195, 12)))))</formula>
+      <formula>OR(AND(LEFT($A191, 16)="select_multiple ", LEN($A191)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A191, 17)))), AND(LEFT($A191, 11)="select_one ", LEN($A191)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A191, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="541" priority="17" stopIfTrue="1">
-      <formula>$A195="decimal"</formula>
+      <formula>$A191="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="540" priority="19" stopIfTrue="1">
-      <formula>$A195="integer"</formula>
+      <formula>$A191="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="539" priority="20" stopIfTrue="1">
-      <formula>$A195="text"</formula>
+      <formula>$A191="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="538" priority="21" stopIfTrue="1">
-      <formula>$A195="end repeat"</formula>
+      <formula>$A191="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="537" priority="22" stopIfTrue="1">
-      <formula>$A195="begin repeat"</formula>
+      <formula>$A191="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="536" priority="23" stopIfTrue="1">
-      <formula>$A195="end group"</formula>
+      <formula>$A191="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="535" priority="24" stopIfTrue="1">
-      <formula>$A195="begin group"</formula>
+      <formula>$A191="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W8">
@@ -13500,12 +13309,12 @@
       <formula>$A5="decimal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 F1:F4 F9:F45 B9:B77 F48:F51 F55:F62 F65:F77 B79:B1048576 F79:F1048576">
+  <conditionalFormatting sqref="B1:B4 F1:F4 F9:F45 F48:F51 F64:F76 B9:B76 F55:F61 B78:B1048576 F78:F1048576">
     <cfRule type="expression" dxfId="513" priority="742" stopIfTrue="1">
       <formula>OR($A1="audio audit", $A1="text audit")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 N1:N4 N9:N44 B9:B77 N48:N62 N65:N66 N68:N77 N80:N82 N85:N88 N91:N92 N94:N125 N127:N129 N156:N158 N220:N221 N131:N154 N160:N218 B79:B1048576 N223:N1048576">
+  <conditionalFormatting sqref="B1:B4 N1:N4 N9:N44 N64:N65 N67:N76 N79:N81 N84:N87 N90:N91 N93:N124 N126:N128 N152:N154 N215:N216 N156:N213 N130:N150 B9:B76 N48:N61 B78:B1048576 N218:N1048576">
     <cfRule type="expression" dxfId="512" priority="734" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
@@ -13617,96 +13426,96 @@
       <formula>$A46="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B64">
+  <conditionalFormatting sqref="B62:B63">
     <cfRule type="expression" dxfId="478" priority="368" stopIfTrue="1">
-      <formula>OR($A63="audio", $A63="video")</formula>
+      <formula>OR($A62="audio", $A62="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="477" priority="369" stopIfTrue="1">
-      <formula>OR($A63="audio", $A63="video")</formula>
+      <formula>OR($A62="audio", $A62="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="476" priority="370" stopIfTrue="1">
-      <formula>$A63="image"</formula>
+      <formula>$A62="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="475" priority="371" stopIfTrue="1">
-      <formula>$A63="image"</formula>
+      <formula>$A62="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="474" priority="372" stopIfTrue="1">
-      <formula>OR($A63="date", $A63="datetime")</formula>
+      <formula>OR($A62="date", $A62="datetime")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="473" priority="373" stopIfTrue="1">
-      <formula>OR($A63="date", $A63="datetime")</formula>
+      <formula>OR($A62="date", $A62="datetime")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="472" priority="374" stopIfTrue="1">
-      <formula>OR($A63="calculate", $A63="calculate_here")</formula>
+      <formula>OR($A62="calculate", $A62="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="471" priority="375" stopIfTrue="1">
-      <formula>$A63="note"</formula>
+      <formula>$A62="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="470" priority="376" stopIfTrue="1">
-      <formula>$A63="note"</formula>
+      <formula>$A62="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="469" priority="377" stopIfTrue="1">
-      <formula>$A63="barcode"</formula>
+      <formula>$A62="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="468" priority="378" stopIfTrue="1">
-      <formula>$A63="barcode"</formula>
+      <formula>$A62="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="467" priority="379" stopIfTrue="1">
-      <formula>$A63="geopoint"</formula>
+      <formula>$A62="geopoint"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="466" priority="380" stopIfTrue="1">
-      <formula>$A63="geopoint"</formula>
+      <formula>$A62="geopoint"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="465" priority="381" stopIfTrue="1">
-      <formula>OR($A63="audio audit", $A63="text audit")</formula>
+      <formula>OR($A62="audio audit", $A62="text audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="464" priority="382" stopIfTrue="1">
-      <formula>OR($A63="username", $A63="phonenumber", $A63="start", $A63="end", $A63="deviceid", $A63="subscriberid", $A63="simserial")</formula>
+      <formula>OR($A62="username", $A62="phonenumber", $A62="start", $A62="end", $A62="deviceid", $A62="subscriberid", $A62="simserial")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="463" priority="383" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A63, 16)="select_multiple ", LEN($A63)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A63, 17)))), AND(LEFT($A63, 11)="select_one ", LEN($A63)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A63, 12)))))</formula>
+      <formula>OR(AND(LEFT($A62, 16)="select_multiple ", LEN($A62)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A62, 17)))), AND(LEFT($A62, 11)="select_one ", LEN($A62)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A62, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="462" priority="384" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A63, 16)="select_multiple ", LEN($A63)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A63, 17)))), AND(LEFT($A63, 11)="select_one ", LEN($A63)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A63, 12)))))</formula>
+      <formula>OR(AND(LEFT($A62, 16)="select_multiple ", LEN($A62)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A62, 17)))), AND(LEFT($A62, 11)="select_one ", LEN($A62)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A62, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="461" priority="385" stopIfTrue="1">
-      <formula>$A63="decimal"</formula>
+      <formula>$A62="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="460" priority="386" stopIfTrue="1">
-      <formula>$A63="decimal"</formula>
+      <formula>$A62="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="459" priority="387" stopIfTrue="1">
-      <formula>$A63="integer"</formula>
+      <formula>$A62="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="458" priority="388" stopIfTrue="1">
-      <formula>$A63="integer"</formula>
+      <formula>$A62="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="457" priority="389" stopIfTrue="1">
-      <formula>$A63="text"</formula>
+      <formula>$A62="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="456" priority="390" stopIfTrue="1">
-      <formula>$A63="text"</formula>
+      <formula>$A62="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="455" priority="391" stopIfTrue="1">
-      <formula>$A63="end repeat"</formula>
+      <formula>$A62="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="454" priority="392" stopIfTrue="1">
-      <formula>$A63="begin repeat"</formula>
+      <formula>$A62="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="453" priority="393" stopIfTrue="1">
-      <formula>$A63="begin repeat"</formula>
+      <formula>$A62="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="452" priority="394" stopIfTrue="1">
-      <formula>$A63="end group"</formula>
+      <formula>$A62="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="451" priority="395" stopIfTrue="1">
-      <formula>$A63="begin group"</formula>
+      <formula>$A62="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="450" priority="396" stopIfTrue="1">
-      <formula>$A63="begin group"</formula>
+      <formula>$A62="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C62 B65:C77 B79:C194 B198:C1048576">
+  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 B78:C190 B48:C61 B194:C1048576">
     <cfRule type="expression" dxfId="449" priority="736" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
@@ -13717,7 +13526,7 @@
       <formula>$A1="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 F1:F4 B9:C19 F9:F45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B48:C62 F55:F62 B65:C77 F65:F77 B79:C1048576 F79:F1048576">
+  <conditionalFormatting sqref="B1:C4 F1:F4 B9:C19 F9:F45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B64:C76 F64:F76 B48:C61 F55:F61 B78:C1048576 F78:F1048576">
     <cfRule type="expression" dxfId="446" priority="728" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
@@ -13728,12 +13537,12 @@
       <formula>OR(AND(LEFT($A1, 16)="select_multiple ", LEN($A1)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A1, 17)))), AND(LEFT($A1, 11)="select_one ", LEN($A1)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A1, 12)))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 F1:F4 I1:I4 B9:C19 F9:F45 I9:I45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B48:C62 I48:I62 F55:F62 B65:C77 F65:F77 I65:I77 B79:C1048576 F79:F1048576 I79:I1048576">
+  <conditionalFormatting sqref="B1:C4 F1:F4 I1:I4 B9:C19 F9:F45 I9:I45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B64:C76 F64:F76 I64:I76 B48:C61 I48:I61 F55:F61 B78:C1048576 F78:F1048576 I78:I1048576">
     <cfRule type="expression" dxfId="443" priority="767" stopIfTrue="1">
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 I1:I4 O1:O4 B9:C19 I9:I45 O9:O45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C62 I48:I62 O48:O62 B65:C77 I65:I77 O65:O77 B79:C1048576 I79:I1048576 O79:O1048576">
+  <conditionalFormatting sqref="B1:C4 I1:I4 O1:O4 B9:C19 I9:I45 O9:O45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 I64:I76 O64:O76 B48:C61 I48:I61 O48:O61 B78:C1048576 I78:I1048576 O78:O1048576">
     <cfRule type="expression" dxfId="442" priority="764" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
@@ -13776,28 +13585,28 @@
       <formula>$A5="file"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C62 B65:C77 B79:C1048576">
+  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 B48:C61 B78:C1048576">
     <cfRule type="expression" dxfId="431" priority="726" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195:C197">
+  <conditionalFormatting sqref="B191:C193">
     <cfRule type="expression" dxfId="430" priority="7" stopIfTrue="1">
-      <formula>$A195="note"</formula>
+      <formula>$A191="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="429" priority="9" stopIfTrue="1">
-      <formula>$A195="barcode"</formula>
+      <formula>$A191="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="428" priority="11" stopIfTrue="1">
-      <formula>$A195="geopoint"</formula>
+      <formula>$A191="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D4 F1:F4 B9:D19 F9:F45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 F48:F51 B48:D62 F55:F62 B65:D77 F65:F77 B79:D1048576 F79:F1048576">
+  <conditionalFormatting sqref="B1:D4 F1:F4 B9:D19 F9:F45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 F48:F51 B64:D76 F64:F76 B48:D61 F55:F61 B78:D1048576 F78:F1048576">
     <cfRule type="expression" dxfId="427" priority="761" stopIfTrue="1">
       <formula>$A1="text"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D4 G1:H4 B9:D19 G9:H45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 B48:D62 G48:H62 B65:D77 G65:H77 B79:D194 G79:H194 B198:D1048576 G198:H1048576">
+  <conditionalFormatting sqref="B1:D4 G1:H4 B9:D19 G9:H45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 B64:D76 G64:H76 B78:D190 G78:H190 B48:D61 G48:H61 B194:D1048576 G194:H1048576">
     <cfRule type="expression" dxfId="426" priority="757" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
     </cfRule>
@@ -13821,12 +13630,12 @@
       <formula>$A5="integer"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195:D197 G195:H197">
+  <conditionalFormatting sqref="B191:D193 G191:H193">
     <cfRule type="expression" dxfId="420" priority="16" stopIfTrue="1">
-      <formula>$A195="decimal"</formula>
+      <formula>$A191="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="419" priority="18" stopIfTrue="1">
-      <formula>$A195="integer"</formula>
+      <formula>$A191="integer"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20 C22 C25:C39">
@@ -14016,15 +13825,15 @@
       <formula>$A52="enumerator"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I121:I127">
+  <conditionalFormatting sqref="I120:I126">
     <cfRule type="expression" dxfId="357" priority="417" stopIfTrue="1">
-      <formula>$A121="decimal"</formula>
+      <formula>$A120="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="356" priority="418" stopIfTrue="1">
-      <formula>$A121="integer"</formula>
+      <formula>$A120="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="355" priority="419" stopIfTrue="1">
-      <formula>$A121="text"</formula>
+      <formula>$A120="text"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
@@ -14151,686 +13960,686 @@
       <formula>OR($A47="calculate", $A47="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63:N64">
+  <conditionalFormatting sqref="N62:N63">
     <cfRule type="expression" dxfId="314" priority="348" stopIfTrue="1">
-      <formula>$A63="enumerator"</formula>
+      <formula>$A62="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="313" priority="349" stopIfTrue="1">
-      <formula>$A63="barcode"</formula>
+      <formula>$A62="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="312" priority="350" stopIfTrue="1">
-      <formula>OR($A63="geopoint", $A63="geoshape", $A63="geotrace")</formula>
+      <formula>OR($A62="geopoint", $A62="geoshape", $A62="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="311" priority="351" stopIfTrue="1">
-      <formula>$A63="file"</formula>
+      <formula>$A62="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="310" priority="352" stopIfTrue="1">
-      <formula>$A63="note"</formula>
+      <formula>$A62="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="309" priority="353" stopIfTrue="1">
-      <formula>$A63="begin group"</formula>
+      <formula>$A62="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="308" priority="354" stopIfTrue="1">
-      <formula>OR($A63="audio", $A63="video")</formula>
+      <formula>OR($A62="audio", $A62="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="307" priority="355" stopIfTrue="1">
-      <formula>OR($A63="audio audit", $A63="text audit", $A63="speed violations count", $A63="speed violations list", $A63="speed violations audit")</formula>
+      <formula>OR($A62="audio audit", $A62="text audit", $A62="speed violations count", $A62="speed violations list", $A62="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="306" priority="356" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A63, 16)="select_multiple ", LEN($A63)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A63, 17)))), AND(LEFT($A63, 11)="select_one ", LEN($A63)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A63, 12)))))</formula>
+      <formula>OR(AND(LEFT($A62, 16)="select_multiple ", LEN($A62)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A62, 17)))), AND(LEFT($A62, 11)="select_one ", LEN($A62)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A62, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="305" priority="357" stopIfTrue="1">
-      <formula>$A63="decimal"</formula>
+      <formula>$A62="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="304" priority="358" stopIfTrue="1">
-      <formula>$A63="integer"</formula>
+      <formula>$A62="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="303" priority="359" stopIfTrue="1">
-      <formula>$A63="text"</formula>
+      <formula>$A62="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="302" priority="360" stopIfTrue="1">
-      <formula>$A63="image"</formula>
+      <formula>$A62="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="301" priority="361" stopIfTrue="1">
-      <formula>OR($A63="date", $A63="datetime", $A63="time")</formula>
+      <formula>OR($A62="date", $A62="datetime", $A62="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="300" priority="362" stopIfTrue="1">
-      <formula>OR($A63="calculate", $A63="calculate_here")</formula>
+      <formula>OR($A62="calculate", $A62="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="299" priority="363" stopIfTrue="1">
-      <formula>OR($A63="username", $A63="phonenumber", $A63="start", $A63="end", $A63="deviceid", $A63="subscriberid", $A63="simserial", $A63="caseid")</formula>
+      <formula>OR($A62="username", $A62="phonenumber", $A62="start", $A62="end", $A62="deviceid", $A62="subscriberid", $A62="simserial", $A62="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="298" priority="364" stopIfTrue="1">
-      <formula>$A63="end repeat"</formula>
+      <formula>$A62="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="297" priority="365" stopIfTrue="1">
-      <formula>$A63="begin repeat"</formula>
+      <formula>$A62="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="296" priority="366" stopIfTrue="1">
-      <formula>$A63="end group"</formula>
+      <formula>$A62="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="295" priority="367" stopIfTrue="1">
-      <formula>OR($A63="calculate", $A63="calculate_here")</formula>
+      <formula>OR($A62="calculate", $A62="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N67 N79">
+  <conditionalFormatting sqref="N66 N78">
     <cfRule type="expression" dxfId="294" priority="463" stopIfTrue="1">
-      <formula>$A67="enumerator"</formula>
+      <formula>$A66="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="293" priority="464" stopIfTrue="1">
-      <formula>$A67="barcode"</formula>
+      <formula>$A66="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="292" priority="465" stopIfTrue="1">
-      <formula>OR($A67="geopoint", $A67="geoshape", $A67="geotrace")</formula>
+      <formula>OR($A66="geopoint", $A66="geoshape", $A66="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="291" priority="466" stopIfTrue="1">
-      <formula>$A67="file"</formula>
+      <formula>$A66="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="290" priority="467" stopIfTrue="1">
-      <formula>$A67="note"</formula>
+      <formula>$A66="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="289" priority="468" stopIfTrue="1">
-      <formula>$A67="begin group"</formula>
+      <formula>$A66="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="288" priority="469" stopIfTrue="1">
-      <formula>OR($A67="audio", $A67="video")</formula>
+      <formula>OR($A66="audio", $A66="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="287" priority="470" stopIfTrue="1">
-      <formula>OR($A67="audio audit", $A67="text audit", $A67="speed violations count", $A67="speed violations list", $A67="speed violations audit")</formula>
+      <formula>OR($A66="audio audit", $A66="text audit", $A66="speed violations count", $A66="speed violations list", $A66="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="286" priority="471" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A67, 16)="select_multiple ", LEN($A67)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A67, 17)))), AND(LEFT($A67, 11)="select_one ", LEN($A67)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A67, 12)))))</formula>
+      <formula>OR(AND(LEFT($A66, 16)="select_multiple ", LEN($A66)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A66, 17)))), AND(LEFT($A66, 11)="select_one ", LEN($A66)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A66, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="285" priority="472" stopIfTrue="1">
-      <formula>$A67="decimal"</formula>
+      <formula>$A66="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="284" priority="473" stopIfTrue="1">
-      <formula>$A67="integer"</formula>
+      <formula>$A66="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="283" priority="474" stopIfTrue="1">
-      <formula>$A67="text"</formula>
+      <formula>$A66="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="282" priority="475" stopIfTrue="1">
-      <formula>$A67="image"</formula>
+      <formula>$A66="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="281" priority="476" stopIfTrue="1">
-      <formula>OR($A67="date", $A67="datetime", $A67="time")</formula>
+      <formula>OR($A66="date", $A66="datetime", $A66="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="280" priority="477" stopIfTrue="1">
-      <formula>OR($A67="calculate", $A67="calculate_here")</formula>
+      <formula>OR($A66="calculate", $A66="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="279" priority="478" stopIfTrue="1">
-      <formula>OR($A67="username", $A67="phonenumber", $A67="start", $A67="end", $A67="deviceid", $A67="subscriberid", $A67="simserial", $A67="caseid")</formula>
+      <formula>OR($A66="username", $A66="phonenumber", $A66="start", $A66="end", $A66="deviceid", $A66="subscriberid", $A66="simserial", $A66="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="278" priority="479" stopIfTrue="1">
-      <formula>$A67="end repeat"</formula>
+      <formula>$A66="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="277" priority="480" stopIfTrue="1">
-      <formula>$A67="begin repeat"</formula>
+      <formula>$A66="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="276" priority="481" stopIfTrue="1">
-      <formula>$A67="end group"</formula>
+      <formula>$A66="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="275" priority="678" stopIfTrue="1">
-      <formula>OR($A67="calculate", $A67="calculate_here")</formula>
+      <formula>OR($A66="calculate", $A66="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N83:N84">
+  <conditionalFormatting sqref="N82:N83">
     <cfRule type="expression" dxfId="274" priority="328" stopIfTrue="1">
-      <formula>$A83="enumerator"</formula>
+      <formula>$A82="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="273" priority="329" stopIfTrue="1">
-      <formula>$A83="barcode"</formula>
+      <formula>$A82="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="272" priority="330" stopIfTrue="1">
-      <formula>OR($A83="geopoint", $A83="geoshape", $A83="geotrace")</formula>
+      <formula>OR($A82="geopoint", $A82="geoshape", $A82="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="271" priority="331" stopIfTrue="1">
-      <formula>$A83="file"</formula>
+      <formula>$A82="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="270" priority="332" stopIfTrue="1">
-      <formula>$A83="note"</formula>
+      <formula>$A82="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="269" priority="333" stopIfTrue="1">
-      <formula>$A83="begin group"</formula>
+      <formula>$A82="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="268" priority="334" stopIfTrue="1">
-      <formula>OR($A83="audio", $A83="video")</formula>
+      <formula>OR($A82="audio", $A82="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="267" priority="335" stopIfTrue="1">
-      <formula>OR($A83="audio audit", $A83="text audit", $A83="speed violations count", $A83="speed violations list", $A83="speed violations audit")</formula>
+      <formula>OR($A82="audio audit", $A82="text audit", $A82="speed violations count", $A82="speed violations list", $A82="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="266" priority="336" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A83, 16)="select_multiple ", LEN($A83)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A83, 17)))), AND(LEFT($A83, 11)="select_one ", LEN($A83)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A83, 12)))))</formula>
+      <formula>OR(AND(LEFT($A82, 16)="select_multiple ", LEN($A82)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A82, 17)))), AND(LEFT($A82, 11)="select_one ", LEN($A82)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A82, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="265" priority="337" stopIfTrue="1">
-      <formula>$A83="decimal"</formula>
+      <formula>$A82="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="264" priority="338" stopIfTrue="1">
-      <formula>$A83="integer"</formula>
+      <formula>$A82="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="263" priority="339" stopIfTrue="1">
-      <formula>$A83="text"</formula>
+      <formula>$A82="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="262" priority="340" stopIfTrue="1">
-      <formula>$A83="image"</formula>
+      <formula>$A82="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="261" priority="341" stopIfTrue="1">
-      <formula>OR($A83="date", $A83="datetime", $A83="time")</formula>
+      <formula>OR($A82="date", $A82="datetime", $A82="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="260" priority="342" stopIfTrue="1">
-      <formula>OR($A83="calculate", $A83="calculate_here")</formula>
+      <formula>OR($A82="calculate", $A82="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="259" priority="343" stopIfTrue="1">
-      <formula>OR($A83="username", $A83="phonenumber", $A83="start", $A83="end", $A83="deviceid", $A83="subscriberid", $A83="simserial", $A83="caseid")</formula>
+      <formula>OR($A82="username", $A82="phonenumber", $A82="start", $A82="end", $A82="deviceid", $A82="subscriberid", $A82="simserial", $A82="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="258" priority="344" stopIfTrue="1">
-      <formula>$A83="end repeat"</formula>
+      <formula>$A82="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="257" priority="345" stopIfTrue="1">
-      <formula>$A83="begin repeat"</formula>
+      <formula>$A82="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="256" priority="346" stopIfTrue="1">
-      <formula>$A83="end group"</formula>
+      <formula>$A82="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="255" priority="347" stopIfTrue="1">
-      <formula>OR($A83="calculate", $A83="calculate_here")</formula>
+      <formula>OR($A82="calculate", $A82="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N89:N90">
+  <conditionalFormatting sqref="N88:N89">
     <cfRule type="expression" dxfId="254" priority="288" stopIfTrue="1">
-      <formula>$A89="enumerator"</formula>
+      <formula>$A88="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="253" priority="289" stopIfTrue="1">
-      <formula>$A89="barcode"</formula>
+      <formula>$A88="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="252" priority="290" stopIfTrue="1">
-      <formula>OR($A89="geopoint", $A89="geoshape", $A89="geotrace")</formula>
+      <formula>OR($A88="geopoint", $A88="geoshape", $A88="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="251" priority="291" stopIfTrue="1">
-      <formula>$A89="file"</formula>
+      <formula>$A88="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="250" priority="292" stopIfTrue="1">
-      <formula>$A89="note"</formula>
+      <formula>$A88="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="249" priority="293" stopIfTrue="1">
-      <formula>$A89="begin group"</formula>
+      <formula>$A88="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="248" priority="294" stopIfTrue="1">
-      <formula>OR($A89="audio", $A89="video")</formula>
+      <formula>OR($A88="audio", $A88="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="247" priority="295" stopIfTrue="1">
-      <formula>OR($A89="audio audit", $A89="text audit", $A89="speed violations count", $A89="speed violations list", $A89="speed violations audit")</formula>
+      <formula>OR($A88="audio audit", $A88="text audit", $A88="speed violations count", $A88="speed violations list", $A88="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="246" priority="296" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A89, 16)="select_multiple ", LEN($A89)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A89, 17)))), AND(LEFT($A89, 11)="select_one ", LEN($A89)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A89, 12)))))</formula>
+      <formula>OR(AND(LEFT($A88, 16)="select_multiple ", LEN($A88)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A88, 17)))), AND(LEFT($A88, 11)="select_one ", LEN($A88)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A88, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="245" priority="297" stopIfTrue="1">
-      <formula>$A89="decimal"</formula>
+      <formula>$A88="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="244" priority="298" stopIfTrue="1">
-      <formula>$A89="integer"</formula>
+      <formula>$A88="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="243" priority="299" stopIfTrue="1">
-      <formula>$A89="text"</formula>
+      <formula>$A88="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="242" priority="300" stopIfTrue="1">
-      <formula>$A89="image"</formula>
+      <formula>$A88="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="241" priority="301" stopIfTrue="1">
-      <formula>OR($A89="date", $A89="datetime", $A89="time")</formula>
+      <formula>OR($A88="date", $A88="datetime", $A88="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="240" priority="302" stopIfTrue="1">
-      <formula>OR($A89="calculate", $A89="calculate_here")</formula>
+      <formula>OR($A88="calculate", $A88="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="239" priority="303" stopIfTrue="1">
-      <formula>OR($A89="username", $A89="phonenumber", $A89="start", $A89="end", $A89="deviceid", $A89="subscriberid", $A89="simserial", $A89="caseid")</formula>
+      <formula>OR($A88="username", $A88="phonenumber", $A88="start", $A88="end", $A88="deviceid", $A88="subscriberid", $A88="simserial", $A88="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="238" priority="304" stopIfTrue="1">
-      <formula>$A89="end repeat"</formula>
+      <formula>$A88="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="237" priority="305" stopIfTrue="1">
-      <formula>$A89="begin repeat"</formula>
+      <formula>$A88="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="236" priority="306" stopIfTrue="1">
-      <formula>$A89="end group"</formula>
+      <formula>$A88="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="235" priority="307" stopIfTrue="1">
-      <formula>OR($A89="calculate", $A89="calculate_here")</formula>
+      <formula>OR($A88="calculate", $A88="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N93">
+  <conditionalFormatting sqref="N92">
     <cfRule type="expression" dxfId="234" priority="228" stopIfTrue="1">
-      <formula>$A93="enumerator"</formula>
+      <formula>$A92="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="233" priority="229" stopIfTrue="1">
-      <formula>$A93="barcode"</formula>
+      <formula>$A92="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="232" priority="230" stopIfTrue="1">
-      <formula>OR($A93="geopoint", $A93="geoshape", $A93="geotrace")</formula>
+      <formula>OR($A92="geopoint", $A92="geoshape", $A92="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="231" priority="231" stopIfTrue="1">
-      <formula>$A93="file"</formula>
+      <formula>$A92="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="230" priority="232" stopIfTrue="1">
-      <formula>$A93="note"</formula>
+      <formula>$A92="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="229" priority="233" stopIfTrue="1">
-      <formula>$A93="begin group"</formula>
+      <formula>$A92="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="228" priority="234" stopIfTrue="1">
-      <formula>OR($A93="audio", $A93="video")</formula>
+      <formula>OR($A92="audio", $A92="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="227" priority="235" stopIfTrue="1">
-      <formula>OR($A93="audio audit", $A93="text audit", $A93="speed violations count", $A93="speed violations list", $A93="speed violations audit")</formula>
+      <formula>OR($A92="audio audit", $A92="text audit", $A92="speed violations count", $A92="speed violations list", $A92="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="226" priority="236" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A93, 16)="select_multiple ", LEN($A93)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A93, 17)))), AND(LEFT($A93, 11)="select_one ", LEN($A93)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A93, 12)))))</formula>
+      <formula>OR(AND(LEFT($A92, 16)="select_multiple ", LEN($A92)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A92, 17)))), AND(LEFT($A92, 11)="select_one ", LEN($A92)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A92, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="225" priority="237" stopIfTrue="1">
-      <formula>$A93="decimal"</formula>
+      <formula>$A92="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="224" priority="238" stopIfTrue="1">
-      <formula>$A93="integer"</formula>
+      <formula>$A92="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="223" priority="239" stopIfTrue="1">
-      <formula>$A93="text"</formula>
+      <formula>$A92="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="222" priority="240" stopIfTrue="1">
-      <formula>$A93="image"</formula>
+      <formula>$A92="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="221" priority="241" stopIfTrue="1">
-      <formula>OR($A93="date", $A93="datetime", $A93="time")</formula>
+      <formula>OR($A92="date", $A92="datetime", $A92="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="220" priority="242" stopIfTrue="1">
-      <formula>OR($A93="calculate", $A93="calculate_here")</formula>
+      <formula>OR($A92="calculate", $A92="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="219" priority="243" stopIfTrue="1">
-      <formula>OR($A93="username", $A93="phonenumber", $A93="start", $A93="end", $A93="deviceid", $A93="subscriberid", $A93="simserial", $A93="caseid")</formula>
+      <formula>OR($A92="username", $A92="phonenumber", $A92="start", $A92="end", $A92="deviceid", $A92="subscriberid", $A92="simserial", $A92="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="218" priority="244" stopIfTrue="1">
-      <formula>$A93="end repeat"</formula>
+      <formula>$A92="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="217" priority="245" stopIfTrue="1">
-      <formula>$A93="begin repeat"</formula>
+      <formula>$A92="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="216" priority="246" stopIfTrue="1">
-      <formula>$A93="end group"</formula>
+      <formula>$A92="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="215" priority="247" stopIfTrue="1">
-      <formula>OR($A93="calculate", $A93="calculate_here")</formula>
+      <formula>OR($A92="calculate", $A92="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N126">
+  <conditionalFormatting sqref="N125">
     <cfRule type="expression" dxfId="214" priority="208" stopIfTrue="1">
-      <formula>$A126="enumerator"</formula>
+      <formula>$A125="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="213" priority="209" stopIfTrue="1">
-      <formula>$A126="barcode"</formula>
+      <formula>$A125="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="212" priority="210" stopIfTrue="1">
-      <formula>OR($A126="geopoint", $A126="geoshape", $A126="geotrace")</formula>
+      <formula>OR($A125="geopoint", $A125="geoshape", $A125="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="211" priority="211" stopIfTrue="1">
-      <formula>$A126="file"</formula>
+      <formula>$A125="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="210" priority="212" stopIfTrue="1">
-      <formula>$A126="note"</formula>
+      <formula>$A125="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="209" priority="213" stopIfTrue="1">
-      <formula>$A126="begin group"</formula>
+      <formula>$A125="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="208" priority="214" stopIfTrue="1">
-      <formula>OR($A126="audio", $A126="video")</formula>
+      <formula>OR($A125="audio", $A125="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="207" priority="215" stopIfTrue="1">
-      <formula>OR($A126="audio audit", $A126="text audit", $A126="speed violations count", $A126="speed violations list", $A126="speed violations audit")</formula>
+      <formula>OR($A125="audio audit", $A125="text audit", $A125="speed violations count", $A125="speed violations list", $A125="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="206" priority="216" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A126, 16)="select_multiple ", LEN($A126)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A126, 17)))), AND(LEFT($A126, 11)="select_one ", LEN($A126)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A126, 12)))))</formula>
+      <formula>OR(AND(LEFT($A125, 16)="select_multiple ", LEN($A125)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A125, 17)))), AND(LEFT($A125, 11)="select_one ", LEN($A125)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A125, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="205" priority="217" stopIfTrue="1">
-      <formula>$A126="decimal"</formula>
+      <formula>$A125="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="204" priority="218" stopIfTrue="1">
-      <formula>$A126="integer"</formula>
+      <formula>$A125="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="203" priority="219" stopIfTrue="1">
-      <formula>$A126="text"</formula>
+      <formula>$A125="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="202" priority="220" stopIfTrue="1">
-      <formula>$A126="image"</formula>
+      <formula>$A125="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="201" priority="221" stopIfTrue="1">
-      <formula>OR($A126="date", $A126="datetime", $A126="time")</formula>
+      <formula>OR($A125="date", $A125="datetime", $A125="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="200" priority="222" stopIfTrue="1">
-      <formula>OR($A126="calculate", $A126="calculate_here")</formula>
+      <formula>OR($A125="calculate", $A125="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="199" priority="223" stopIfTrue="1">
-      <formula>OR($A126="username", $A126="phonenumber", $A126="start", $A126="end", $A126="deviceid", $A126="subscriberid", $A126="simserial", $A126="caseid")</formula>
+      <formula>OR($A125="username", $A125="phonenumber", $A125="start", $A125="end", $A125="deviceid", $A125="subscriberid", $A125="simserial", $A125="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="198" priority="224" stopIfTrue="1">
-      <formula>$A126="end repeat"</formula>
+      <formula>$A125="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="197" priority="225" stopIfTrue="1">
-      <formula>$A126="begin repeat"</formula>
+      <formula>$A125="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="196" priority="226" stopIfTrue="1">
-      <formula>$A126="end group"</formula>
+      <formula>$A125="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="195" priority="227" stopIfTrue="1">
-      <formula>OR($A126="calculate", $A126="calculate_here")</formula>
+      <formula>OR($A125="calculate", $A125="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N130">
+  <conditionalFormatting sqref="N129">
     <cfRule type="expression" dxfId="194" priority="188" stopIfTrue="1">
-      <formula>$A130="enumerator"</formula>
+      <formula>$A129="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="193" priority="189" stopIfTrue="1">
-      <formula>$A130="barcode"</formula>
+      <formula>$A129="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="192" priority="190" stopIfTrue="1">
-      <formula>OR($A130="geopoint", $A130="geoshape", $A130="geotrace")</formula>
+      <formula>OR($A129="geopoint", $A129="geoshape", $A129="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="191" priority="191" stopIfTrue="1">
-      <formula>$A130="file"</formula>
+      <formula>$A129="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="190" priority="192" stopIfTrue="1">
-      <formula>$A130="note"</formula>
+      <formula>$A129="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="189" priority="193" stopIfTrue="1">
-      <formula>$A130="begin group"</formula>
+      <formula>$A129="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="188" priority="194" stopIfTrue="1">
-      <formula>OR($A130="audio", $A130="video")</formula>
+      <formula>OR($A129="audio", $A129="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="187" priority="195" stopIfTrue="1">
-      <formula>OR($A130="audio audit", $A130="text audit", $A130="speed violations count", $A130="speed violations list", $A130="speed violations audit")</formula>
+      <formula>OR($A129="audio audit", $A129="text audit", $A129="speed violations count", $A129="speed violations list", $A129="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="186" priority="196" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A130, 16)="select_multiple ", LEN($A130)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A130, 17)))), AND(LEFT($A130, 11)="select_one ", LEN($A130)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A130, 12)))))</formula>
+      <formula>OR(AND(LEFT($A129, 16)="select_multiple ", LEN($A129)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A129, 17)))), AND(LEFT($A129, 11)="select_one ", LEN($A129)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A129, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="185" priority="197" stopIfTrue="1">
-      <formula>$A130="decimal"</formula>
+      <formula>$A129="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="184" priority="198" stopIfTrue="1">
-      <formula>$A130="integer"</formula>
+      <formula>$A129="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="183" priority="199" stopIfTrue="1">
-      <formula>$A130="text"</formula>
+      <formula>$A129="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="182" priority="200" stopIfTrue="1">
-      <formula>$A130="image"</formula>
+      <formula>$A129="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="181" priority="201" stopIfTrue="1">
-      <formula>OR($A130="date", $A130="datetime", $A130="time")</formula>
+      <formula>OR($A129="date", $A129="datetime", $A129="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="180" priority="202" stopIfTrue="1">
-      <formula>OR($A130="calculate", $A130="calculate_here")</formula>
+      <formula>OR($A129="calculate", $A129="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="179" priority="203" stopIfTrue="1">
-      <formula>OR($A130="username", $A130="phonenumber", $A130="start", $A130="end", $A130="deviceid", $A130="subscriberid", $A130="simserial", $A130="caseid")</formula>
+      <formula>OR($A129="username", $A129="phonenumber", $A129="start", $A129="end", $A129="deviceid", $A129="subscriberid", $A129="simserial", $A129="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="178" priority="204" stopIfTrue="1">
-      <formula>$A130="end repeat"</formula>
+      <formula>$A129="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="177" priority="205" stopIfTrue="1">
-      <formula>$A130="begin repeat"</formula>
+      <formula>$A129="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="176" priority="206" stopIfTrue="1">
-      <formula>$A130="end group"</formula>
+      <formula>$A129="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="175" priority="207" stopIfTrue="1">
-      <formula>OR($A130="calculate", $A130="calculate_here")</formula>
+      <formula>OR($A129="calculate", $A129="calculate_here")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N151">
+    <cfRule type="expression" dxfId="174" priority="168" stopIfTrue="1">
+      <formula>$A151="enumerator"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="173" priority="169" stopIfTrue="1">
+      <formula>$A151="barcode"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="172" priority="170" stopIfTrue="1">
+      <formula>OR($A151="geopoint", $A151="geoshape", $A151="geotrace")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="171" priority="171" stopIfTrue="1">
+      <formula>$A151="file"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="170" priority="172" stopIfTrue="1">
+      <formula>$A151="note"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="173" stopIfTrue="1">
+      <formula>$A151="begin group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="174" stopIfTrue="1">
+      <formula>OR($A151="audio", $A151="video")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="167" priority="175" stopIfTrue="1">
+      <formula>OR($A151="audio audit", $A151="text audit", $A151="speed violations count", $A151="speed violations list", $A151="speed violations audit")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="176" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A151, 16)="select_multiple ", LEN($A151)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A151, 17)))), AND(LEFT($A151, 11)="select_one ", LEN($A151)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A151, 12)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="165" priority="177" stopIfTrue="1">
+      <formula>$A151="decimal"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="178" stopIfTrue="1">
+      <formula>$A151="integer"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="163" priority="179" stopIfTrue="1">
+      <formula>$A151="text"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="162" priority="180" stopIfTrue="1">
+      <formula>$A151="image"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="181" stopIfTrue="1">
+      <formula>OR($A151="date", $A151="datetime", $A151="time")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="160" priority="182" stopIfTrue="1">
+      <formula>OR($A151="calculate", $A151="calculate_here")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="183" stopIfTrue="1">
+      <formula>OR($A151="username", $A151="phonenumber", $A151="start", $A151="end", $A151="deviceid", $A151="subscriberid", $A151="simserial", $A151="caseid")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="184" stopIfTrue="1">
+      <formula>$A151="end repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="157" priority="185" stopIfTrue="1">
+      <formula>$A151="begin repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="156" priority="186" stopIfTrue="1">
+      <formula>$A151="end group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="155" priority="187" stopIfTrue="1">
+      <formula>OR($A151="calculate", $A151="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N155">
-    <cfRule type="expression" dxfId="174" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="148" stopIfTrue="1">
       <formula>$A155="enumerator"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="149" stopIfTrue="1">
       <formula>$A155="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="150" stopIfTrue="1">
       <formula>OR($A155="geopoint", $A155="geoshape", $A155="geotrace")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="151" stopIfTrue="1">
       <formula>$A155="file"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="152" stopIfTrue="1">
       <formula>$A155="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="153" stopIfTrue="1">
       <formula>$A155="begin group"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="154" stopIfTrue="1">
       <formula>OR($A155="audio", $A155="video")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="167" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="155" stopIfTrue="1">
       <formula>OR($A155="audio audit", $A155="text audit", $A155="speed violations count", $A155="speed violations list", $A155="speed violations audit")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="156" stopIfTrue="1">
       <formula>OR(AND(LEFT($A155, 16)="select_multiple ", LEN($A155)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A155, 17)))), AND(LEFT($A155, 11)="select_one ", LEN($A155)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A155, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="157" stopIfTrue="1">
       <formula>$A155="decimal"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="158" stopIfTrue="1">
       <formula>$A155="integer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="163" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="159" stopIfTrue="1">
       <formula>$A155="text"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="160" stopIfTrue="1">
       <formula>$A155="image"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="161" stopIfTrue="1">
       <formula>OR($A155="date", $A155="datetime", $A155="time")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="162" stopIfTrue="1">
       <formula>OR($A155="calculate", $A155="calculate_here")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="163" stopIfTrue="1">
       <formula>OR($A155="username", $A155="phonenumber", $A155="start", $A155="end", $A155="deviceid", $A155="subscriberid", $A155="simserial", $A155="caseid")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="164" stopIfTrue="1">
       <formula>$A155="end repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="165" stopIfTrue="1">
       <formula>$A155="begin repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="166" stopIfTrue="1">
       <formula>$A155="end group"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="167" stopIfTrue="1">
       <formula>OR($A155="calculate", $A155="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N159">
-    <cfRule type="expression" dxfId="154" priority="148" stopIfTrue="1">
-      <formula>$A159="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="149" stopIfTrue="1">
-      <formula>$A159="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="150" stopIfTrue="1">
-      <formula>OR($A159="geopoint", $A159="geoshape", $A159="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="151" priority="151" stopIfTrue="1">
-      <formula>$A159="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="150" priority="152" stopIfTrue="1">
-      <formula>$A159="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="149" priority="153" stopIfTrue="1">
-      <formula>$A159="begin group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="154" stopIfTrue="1">
-      <formula>OR($A159="audio", $A159="video")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="155" stopIfTrue="1">
-      <formula>OR($A159="audio audit", $A159="text audit", $A159="speed violations count", $A159="speed violations list", $A159="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="156" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A159, 16)="select_multiple ", LEN($A159)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A159, 17)))), AND(LEFT($A159, 11)="select_one ", LEN($A159)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A159, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="145" priority="157" stopIfTrue="1">
-      <formula>$A159="decimal"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="144" priority="158" stopIfTrue="1">
-      <formula>$A159="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="159" stopIfTrue="1">
-      <formula>$A159="text"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="160" stopIfTrue="1">
-      <formula>$A159="image"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="161" stopIfTrue="1">
-      <formula>OR($A159="date", $A159="datetime", $A159="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="140" priority="162" stopIfTrue="1">
-      <formula>OR($A159="calculate", $A159="calculate_here")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="163" stopIfTrue="1">
-      <formula>OR($A159="username", $A159="phonenumber", $A159="start", $A159="end", $A159="deviceid", $A159="subscriberid", $A159="simserial", $A159="caseid")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="138" priority="164" stopIfTrue="1">
-      <formula>$A159="end repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="165" stopIfTrue="1">
-      <formula>$A159="begin repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="136" priority="166" stopIfTrue="1">
-      <formula>$A159="end group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="167" stopIfTrue="1">
-      <formula>OR($A159="calculate", $A159="calculate_here")</formula>
+  <conditionalFormatting sqref="N214">
+    <cfRule type="expression" dxfId="134" priority="128" stopIfTrue="1">
+      <formula>$A214="enumerator"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="129" stopIfTrue="1">
+      <formula>$A214="barcode"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="130" stopIfTrue="1">
+      <formula>OR($A214="geopoint", $A214="geoshape", $A214="geotrace")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="131" stopIfTrue="1">
+      <formula>$A214="file"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="132" stopIfTrue="1">
+      <formula>$A214="note"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="133" stopIfTrue="1">
+      <formula>$A214="begin group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="134" stopIfTrue="1">
+      <formula>OR($A214="audio", $A214="video")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="127" priority="135" stopIfTrue="1">
+      <formula>OR($A214="audio audit", $A214="text audit", $A214="speed violations count", $A214="speed violations list", $A214="speed violations audit")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="136" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A214, 16)="select_multiple ", LEN($A214)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A214, 17)))), AND(LEFT($A214, 11)="select_one ", LEN($A214)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A214, 12)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="137" stopIfTrue="1">
+      <formula>$A214="decimal"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="124" priority="138" stopIfTrue="1">
+      <formula>$A214="integer"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="139" stopIfTrue="1">
+      <formula>$A214="text"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="140" stopIfTrue="1">
+      <formula>$A214="image"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="121" priority="141" stopIfTrue="1">
+      <formula>OR($A214="date", $A214="datetime", $A214="time")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="120" priority="142" stopIfTrue="1">
+      <formula>OR($A214="calculate", $A214="calculate_here")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="143" stopIfTrue="1">
+      <formula>OR($A214="username", $A214="phonenumber", $A214="start", $A214="end", $A214="deviceid", $A214="subscriberid", $A214="simserial", $A214="caseid")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="144" stopIfTrue="1">
+      <formula>$A214="end repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="145" stopIfTrue="1">
+      <formula>$A214="begin repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="146" stopIfTrue="1">
+      <formula>$A214="end group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="115" priority="147" stopIfTrue="1">
+      <formula>OR($A214="calculate", $A214="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N219">
-    <cfRule type="expression" dxfId="134" priority="128" stopIfTrue="1">
-      <formula>$A219="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="129" stopIfTrue="1">
-      <formula>$A219="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="130" stopIfTrue="1">
-      <formula>OR($A219="geopoint", $A219="geoshape", $A219="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="131" stopIfTrue="1">
-      <formula>$A219="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="130" priority="132" stopIfTrue="1">
-      <formula>$A219="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="133" stopIfTrue="1">
-      <formula>$A219="begin group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="128" priority="134" stopIfTrue="1">
-      <formula>OR($A219="audio", $A219="video")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="127" priority="135" stopIfTrue="1">
-      <formula>OR($A219="audio audit", $A219="text audit", $A219="speed violations count", $A219="speed violations list", $A219="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="126" priority="136" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A219, 16)="select_multiple ", LEN($A219)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A219, 17)))), AND(LEFT($A219, 11)="select_one ", LEN($A219)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A219, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="137" stopIfTrue="1">
-      <formula>$A219="decimal"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="138" stopIfTrue="1">
-      <formula>$A219="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="139" stopIfTrue="1">
-      <formula>$A219="text"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="122" priority="140" stopIfTrue="1">
-      <formula>$A219="image"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="141" stopIfTrue="1">
-      <formula>OR($A219="date", $A219="datetime", $A219="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="120" priority="142" stopIfTrue="1">
-      <formula>OR($A219="calculate", $A219="calculate_here")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="143" stopIfTrue="1">
-      <formula>OR($A219="username", $A219="phonenumber", $A219="start", $A219="end", $A219="deviceid", $A219="subscriberid", $A219="simserial", $A219="caseid")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="144" stopIfTrue="1">
-      <formula>$A219="end repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="145" stopIfTrue="1">
-      <formula>$A219="begin repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="116" priority="146" stopIfTrue="1">
-      <formula>$A219="end group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="147" stopIfTrue="1">
-      <formula>OR($A219="calculate", $A219="calculate_here")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N222">
+  <conditionalFormatting sqref="N217">
     <cfRule type="expression" dxfId="114" priority="68" stopIfTrue="1">
-      <formula>$A222="enumerator"</formula>
+      <formula>$A217="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="113" priority="69" stopIfTrue="1">
-      <formula>$A222="barcode"</formula>
+      <formula>$A217="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="112" priority="70" stopIfTrue="1">
-      <formula>OR($A222="geopoint", $A222="geoshape", $A222="geotrace")</formula>
+      <formula>OR($A217="geopoint", $A217="geoshape", $A217="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="111" priority="71" stopIfTrue="1">
-      <formula>$A222="file"</formula>
+      <formula>$A217="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="110" priority="72" stopIfTrue="1">
-      <formula>$A222="note"</formula>
+      <formula>$A217="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="109" priority="73" stopIfTrue="1">
-      <formula>$A222="begin group"</formula>
+      <formula>$A217="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="108" priority="74" stopIfTrue="1">
-      <formula>OR($A222="audio", $A222="video")</formula>
+      <formula>OR($A217="audio", $A217="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="107" priority="75" stopIfTrue="1">
-      <formula>OR($A222="audio audit", $A222="text audit", $A222="speed violations count", $A222="speed violations list", $A222="speed violations audit")</formula>
+      <formula>OR($A217="audio audit", $A217="text audit", $A217="speed violations count", $A217="speed violations list", $A217="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="76" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A222, 16)="select_multiple ", LEN($A222)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A222, 17)))), AND(LEFT($A222, 11)="select_one ", LEN($A222)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A222, 12)))))</formula>
+      <formula>OR(AND(LEFT($A217, 16)="select_multiple ", LEN($A217)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A217, 17)))), AND(LEFT($A217, 11)="select_one ", LEN($A217)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A217, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="77" stopIfTrue="1">
-      <formula>$A222="decimal"</formula>
+      <formula>$A217="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="104" priority="78" stopIfTrue="1">
-      <formula>$A222="integer"</formula>
+      <formula>$A217="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="103" priority="79" stopIfTrue="1">
-      <formula>$A222="text"</formula>
+      <formula>$A217="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="102" priority="80" stopIfTrue="1">
-      <formula>$A222="image"</formula>
+      <formula>$A217="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="81" stopIfTrue="1">
-      <formula>OR($A222="date", $A222="datetime", $A222="time")</formula>
+      <formula>OR($A217="date", $A217="datetime", $A217="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="82" stopIfTrue="1">
-      <formula>OR($A222="calculate", $A222="calculate_here")</formula>
+      <formula>OR($A217="calculate", $A217="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="99" priority="83" stopIfTrue="1">
-      <formula>OR($A222="username", $A222="phonenumber", $A222="start", $A222="end", $A222="deviceid", $A222="subscriberid", $A222="simserial", $A222="caseid")</formula>
+      <formula>OR($A217="username", $A217="phonenumber", $A217="start", $A217="end", $A217="deviceid", $A217="subscriberid", $A217="simserial", $A217="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="98" priority="84" stopIfTrue="1">
-      <formula>$A222="end repeat"</formula>
+      <formula>$A217="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="97" priority="85" stopIfTrue="1">
-      <formula>$A222="begin repeat"</formula>
+      <formula>$A217="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="96" priority="86" stopIfTrue="1">
-      <formula>$A222="end group"</formula>
+      <formula>$A217="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="95" priority="87" stopIfTrue="1">
-      <formula>OR($A222="calculate", $A222="calculate_here")</formula>
+      <formula>OR($A217="calculate", $A217="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666667" right="0.74791666666666667" top="0.98402777777777772" bottom="0.98402777777777772" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -15000,7 +14809,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -15022,7 +14831,7 @@
         <v>77</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -15044,7 +14853,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15055,7 +14864,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15066,51 +14875,51 @@
         <v>3</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="14" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="B20" s="14">
         <v>1</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="14" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="B21" s="14">
         <v>2</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="14" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="B22" s="14">
         <v>3</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="14" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="B23" s="14">
         <v>4</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15418,7 +15227,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15819,73 +15628,73 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B88" s="14">
         <v>1</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B89" s="14">
         <v>2</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B90" s="14">
         <v>3</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B91" s="14">
         <v>4</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B92" s="14">
         <v>5</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B93" s="14">
         <v>6</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B94" s="14">
         <v>66</v>
@@ -15896,7 +15705,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B95" s="14">
         <v>1</v>
@@ -15907,7 +15716,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B96" s="14">
         <v>2</v>
@@ -15918,18 +15727,18 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B97" s="14">
         <v>3</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B98" s="14">
         <v>99</v>
@@ -15940,623 +15749,623 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B99" s="14">
         <v>1</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B100" s="14">
         <v>2</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B101" s="14">
         <v>3</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B102" s="14">
         <v>4</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B103" s="14">
         <v>5</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B104" s="14">
         <v>99</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B105" s="14">
         <v>1</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B106" s="14">
         <v>2</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B107" s="14">
         <v>3</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B108" s="14">
         <v>4</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B109" s="14">
         <v>1</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B110" s="14">
         <v>2</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B111" s="14">
         <v>3</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B112" s="14">
         <v>4</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B113" s="14">
         <v>3</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B114" s="14">
         <v>99</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B115" s="14">
         <v>0</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B116" s="14">
         <v>1</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B117" s="14">
         <v>2</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B118" s="14">
         <v>3</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B119" s="14">
         <v>4</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B120" s="14">
         <v>5</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B121" s="14">
         <v>6</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B122" s="14">
         <v>7</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B123" s="14">
         <v>1</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B124" s="14">
         <v>2</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B125" s="14">
         <v>3</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B126" s="14">
         <v>1</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B127" s="14">
         <v>2</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B128" s="14">
         <v>3</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B129" s="14">
         <v>4</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B130" s="14">
         <v>5</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B131" s="14">
         <v>1</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B132" s="14">
         <v>2</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B133" s="14">
         <v>3</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B134" s="14">
         <v>1</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B135" s="14">
         <v>2</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B136" s="14">
         <v>3</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B137" s="14">
         <v>1</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B138" s="14">
         <v>2</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B139" s="14">
         <v>3</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B140" s="14">
         <v>4</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B141" s="14">
         <v>5</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B142" s="14">
         <v>6</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B143" s="14">
         <v>7</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B144" s="14">
         <v>8</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B145" s="14">
         <v>9</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B146" s="14">
         <v>10</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B147" s="14">
         <v>11</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B148" s="14">
         <v>12</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B149" s="14">
         <v>13</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B150" s="14">
         <v>66</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B151" s="14">
         <v>1</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B152" s="14">
         <v>2</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B153" s="14">
         <v>3</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B154" s="14">
         <v>4</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B155" s="14">
         <v>5</v>
@@ -16567,150 +16376,150 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B156" s="14">
         <v>1</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B157" s="14">
         <v>2</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B158" s="14">
         <v>3</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B159" s="14">
         <v>4</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B160" s="14">
         <v>5</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="16.5" thickBot="1">
       <c r="A161" s="14" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B161" s="14">
         <v>6</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B162" s="14">
         <v>1</v>
       </c>
       <c r="C162" s="55" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B163" s="14">
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B164" s="14">
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B165" s="14">
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B166" s="14">
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B167" s="14">
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B168" s="14">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B169" s="14">
         <v>66</v>
@@ -16721,95 +16530,95 @@
     </row>
     <row r="170" spans="1:3" ht="16.5" thickBot="1">
       <c r="A170" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B170" s="14">
         <v>8</v>
       </c>
       <c r="C170" s="56" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B171" s="14">
         <v>1</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B172" s="14">
         <v>2</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B173" s="14">
         <v>3</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B174" s="14">
         <v>4</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B175" s="14">
         <v>5</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B176" s="14">
         <v>6</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B177" s="14">
         <v>7</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B178" s="14">
         <v>66</v>
@@ -16820,189 +16629,189 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B179" s="14">
         <v>8</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B180" s="14">
         <v>1</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B181" s="14">
         <v>2</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B182" s="14">
         <v>3</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B183" s="14">
         <v>4</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B184" s="14">
         <v>5</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>891</v>
+        <v>869</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B185" s="14">
         <v>6</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B186" s="14">
         <v>7</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>892</v>
+        <v>870</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B187" s="14">
         <v>8</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B188" s="14">
         <v>9</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B189" s="14">
         <v>10</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>895</v>
+        <v>873</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B190" s="14">
         <v>11</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>896</v>
+        <v>874</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B191" s="14">
         <v>12</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>897</v>
+        <v>875</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B192" s="14">
         <v>13</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B193" s="14">
         <v>14</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B194" s="14">
         <v>15</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>900</v>
+        <v>878</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="14" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="B195" s="14">
         <v>16</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>901</v>
+        <v>879</v>
       </c>
     </row>
   </sheetData>
@@ -17123,7 +16932,7 @@
       </c>
       <c r="C2" s="15" t="str">
         <f ca="1">TEXT(YEAR(NOW())-2000, "00") &amp; TEXT(MONTH(NOW()), "00") &amp; TEXT(DAY(NOW()), "00") &amp; TEXT(HOUR(NOW()), "00") &amp; TEXT(MINUTE(NOW()), "00")</f>
-        <v>2602260928</v>
+        <v>2602271516</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="17"/>

--- a/raw_data/Instrumento_mercy_ODK.xlsx
+++ b/raw_data/Instrumento_mercy_ODK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\EQUILIBRIUM   Intranet 🌍📂\🥁 PROYECTOS\🏆 Proyectos S. Desarrollo\176. Mercy Corps\02. Implementación\Campo Mercy\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED126A4-7223-4A79-848D-4DC36DECD2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE55A30B-7E33-4A63-A1C2-24FC6E21CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="534" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="534" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">choices!$A$1:$D$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$T$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$T$220</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="945">
   <si>
     <t>deviceid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2649,18 +2649,9 @@
     <t>Cédula de ciudadanía (CC)</t>
   </si>
   <si>
-    <t>string-length(.) &gt;= 5</t>
-  </si>
-  <si>
-    <t>Escriba un documento válido</t>
-  </si>
-  <si>
     <t>select_one sexo</t>
   </si>
   <si>
-    <t>numero_documento</t>
-  </si>
-  <si>
     <t>sexo</t>
   </si>
   <si>
@@ -3799,9 +3790,6 @@
   </si>
   <si>
     <t>15. Tipo de documento de identidad</t>
-  </si>
-  <si>
-    <t>16. Número de documento</t>
   </si>
   <si>
     <t>17. Sexo</t>
@@ -9830,7 +9818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z221"/>
+  <dimension ref="A1:Z220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="29" style="8" customWidth="1"/>
@@ -10059,7 +10047,7 @@
     </row>
     <row r="8" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="58" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>314</v>
@@ -10099,7 +10087,7 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="N9" s="8" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -10107,12 +10095,12 @@
         <v>41</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="I10" s="50"/>
       <c r="J10" s="10"/>
       <c r="N10" s="8" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -10120,12 +10108,12 @@
         <v>41</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="I11" s="50"/>
       <c r="J11" s="10"/>
       <c r="N11" s="8" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -10133,13 +10121,13 @@
         <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C12" s="59"/>
       <c r="I12" s="50"/>
       <c r="J12" s="10"/>
       <c r="N12" s="8" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -10147,13 +10135,13 @@
         <v>41</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C13" s="59"/>
       <c r="I13" s="50"/>
       <c r="J13" s="10"/>
       <c r="N13" s="8" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -10161,13 +10149,13 @@
         <v>41</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C14" s="59"/>
       <c r="I14" s="50"/>
       <c r="J14" s="10"/>
       <c r="N14" s="8" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -10175,13 +10163,13 @@
         <v>41</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C15" s="59"/>
       <c r="I15" s="50"/>
       <c r="J15" s="10"/>
       <c r="N15" s="8" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -10189,13 +10177,13 @@
         <v>41</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C16" s="59"/>
       <c r="I16" s="50"/>
       <c r="J16" s="10"/>
       <c r="N16" s="8" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -10203,13 +10191,13 @@
         <v>41</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C17" s="59"/>
       <c r="I17" s="50"/>
       <c r="J17" s="10"/>
       <c r="N17" s="8" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -10217,13 +10205,13 @@
         <v>41</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C18" s="59"/>
       <c r="I18" s="50"/>
       <c r="J18" s="10"/>
       <c r="N18" s="8" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="47.25">
@@ -10231,13 +10219,13 @@
         <v>36</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="8" t="s">
@@ -10263,7 +10251,7 @@
         <v>290</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -10292,7 +10280,7 @@
         <v>299</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>328</v>
@@ -10309,10 +10297,10 @@
         <v>295</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>38</v>
@@ -10358,7 +10346,7 @@
         <v>333</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J27" s="10"/>
       <c r="K27" s="8" t="s">
@@ -10370,13 +10358,13 @@
         <v>41</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C28" s="51"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="N28" s="10" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="31.5">
@@ -10384,13 +10372,13 @@
         <v>41</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C29" s="51"/>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="N29" s="10" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="141.75">
@@ -10398,13 +10386,13 @@
         <v>41</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C30" s="51"/>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="N30" s="10" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="141.75">
@@ -10412,13 +10400,13 @@
         <v>41</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C31" s="51"/>
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="N31" s="10" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -10426,13 +10414,13 @@
         <v>41</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C32" s="51"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="N32" s="8" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="31.5">
@@ -10440,13 +10428,13 @@
         <v>43</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="8" t="s">
@@ -10458,13 +10446,13 @@
         <v>41</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C34" s="51"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="N34" s="8" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -10472,13 +10460,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C35" s="60" t="s">
         <v>912</v>
       </c>
-      <c r="C35" s="60" t="s">
-        <v>916</v>
-      </c>
       <c r="I35" s="10" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="8" t="s">
@@ -10503,11 +10491,11 @@
         <v>157</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C37" s="51"/>
       <c r="F37" s="8" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -10517,11 +10505,11 @@
         <v>157</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C38" s="51"/>
       <c r="F38" s="8" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -10531,11 +10519,11 @@
         <v>157</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C39" s="51"/>
       <c r="F39" s="8" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -10548,7 +10536,7 @@
         <v>303</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>306</v>
@@ -10562,10 +10550,10 @@
         <v>43</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>304</v>
@@ -10585,7 +10573,7 @@
         <v>305</v>
       </c>
       <c r="C42" s="44" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>307</v>
@@ -10619,10 +10607,10 @@
         <v>153</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="N45" s="54" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -10638,10 +10626,10 @@
         <v>153</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="N47" s="54" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -10652,7 +10640,7 @@
         <v>338</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -10663,7 +10651,7 @@
         <v>339</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="47.25">
@@ -10674,7 +10662,7 @@
         <v>337</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>38</v>
@@ -10688,10 +10676,10 @@
         <v>340</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>38</v>
@@ -10705,13 +10693,13 @@
         <v>342</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F52" s="49" t="s">
         <v>343</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="K52" s="8" t="s">
         <v>38</v>
@@ -10722,11 +10710,11 @@
         <v>41</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="F53" s="49"/>
       <c r="N53" s="8" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="31.5">
@@ -10740,10 +10728,10 @@
         <v>347</v>
       </c>
       <c r="F54" s="52" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>38</v>
@@ -10757,13 +10745,13 @@
         <v>348</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>349</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>38</v>
@@ -10777,7 +10765,7 @@
         <v>352</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>38</v>
@@ -10791,7 +10779,7 @@
         <v>353</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="K57" s="8" t="s">
         <v>38</v>
@@ -10808,10 +10796,10 @@
         <v>355</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="K58" s="8" t="s">
         <v>38</v>
@@ -10825,7 +10813,7 @@
         <v>356</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="K59" s="8" t="s">
         <v>38</v>
@@ -10848,7 +10836,7 @@
         <v>360</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="K60" s="8" t="s">
         <v>38</v>
@@ -10859,13 +10847,13 @@
         <v>43</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="K61" s="8" t="s">
         <v>38</v>
@@ -10876,10 +10864,10 @@
         <v>153</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="N62" s="54" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -10887,10 +10875,10 @@
         <v>41</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N63" s="54" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -10914,10 +10902,10 @@
         <v>153</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="N66" s="54" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="78.75">
@@ -10928,7 +10916,7 @@
         <v>388</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="K67" s="8" t="s">
         <v>38</v>
@@ -10965,27 +10953,24 @@
         <v>394</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="K69" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="31.5">
+    <row r="70" spans="1:14">
       <c r="A70" s="8" t="s">
-        <v>43</v>
+        <v>406</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>790</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>407</v>
+        <v>787</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="K70" s="8" t="s">
         <v>38</v>
@@ -10993,13 +10978,13 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>393</v>
@@ -11010,191 +10995,191 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="8" t="s">
-        <v>413</v>
+        <v>43</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>792</v>
+        <v>416</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="K72" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" ht="47.25">
       <c r="A73" s="8" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>418</v>
       </c>
       <c r="C73" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="G73" s="8" t="s">
         <v>419</v>
       </c>
+      <c r="H73" s="10" t="s">
+        <v>420</v>
+      </c>
       <c r="I73" s="8" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="K73" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="47.25">
+    <row r="74" spans="1:14">
       <c r="A74" s="8" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>793</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="K74" s="8" t="s">
+      <c r="N74" s="8" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="31.5">
+      <c r="A75" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="K75" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="N75" s="8" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="31.5">
+    <row r="76" spans="1:14" ht="47.25">
       <c r="A76" s="8" t="s">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>435</v>
       </c>
       <c r="D76" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="H76" s="10" t="s">
         <v>436</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="K76" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="47.25">
+    <row r="77" spans="1:14">
       <c r="A77" s="8" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>38</v>
+        <v>699</v>
+      </c>
+      <c r="N77" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="N78" s="54" t="s">
-        <v>693</v>
+        <v>700</v>
+      </c>
+      <c r="N78" s="8" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="N79" s="8" t="s">
-        <v>704</v>
+        <v>387</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
+        <v>692</v>
+      </c>
+      <c r="N81" s="54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="31.5">
       <c r="A82" s="8" t="s">
-        <v>153</v>
+        <v>790</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="N82" s="54" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="31.5">
+        <v>791</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N82" s="54"/>
+    </row>
+    <row r="83" spans="1:14" ht="63">
       <c r="A83" s="8" t="s">
-        <v>794</v>
+        <v>362</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>795</v>
+        <v>363</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>802</v>
+        <v>799</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>800</v>
       </c>
       <c r="K83" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N83" s="54"/>
-    </row>
-    <row r="84" spans="1:14" ht="63">
+    </row>
+    <row r="84" spans="1:14" ht="31.5">
       <c r="A84" s="8" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K84" s="8" t="s">
         <v>38</v>
@@ -11202,16 +11187,16 @@
     </row>
     <row r="85" spans="1:14" ht="31.5">
       <c r="A85" s="8" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="K85" s="8" t="s">
         <v>38</v>
@@ -11219,93 +11204,90 @@
     </row>
     <row r="86" spans="1:14" ht="31.5">
       <c r="A86" s="8" t="s">
-        <v>291</v>
+        <v>378</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>806</v>
+        <v>386</v>
       </c>
       <c r="K86" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="31.5">
+    <row r="87" spans="1:14">
       <c r="A87" s="8" t="s">
-        <v>378</v>
+        <v>153</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>808</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="K87" s="8" t="s">
-        <v>38</v>
+        <v>693</v>
+      </c>
+      <c r="N87" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="N88" s="54" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="N89" s="54" t="s">
-        <v>700</v>
+        <v>361</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>361</v>
+        <v>525</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
+        <v>702</v>
+      </c>
+      <c r="N91" s="54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="47.25">
       <c r="A92" s="8" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="N92" s="54" t="s">
-        <v>693</v>
+        <v>526</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="47.25">
       <c r="A93" s="8" t="s">
-        <v>291</v>
+        <v>527</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>809</v>
@@ -11314,43 +11296,46 @@
         <v>38</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="47.25">
+    <row r="94" spans="1:14" ht="31.5">
       <c r="A94" s="8" t="s">
-        <v>530</v>
+        <v>291</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="K94" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="31.5">
+    <row r="95" spans="1:14" ht="47.25">
       <c r="A95" s="8" t="s">
-        <v>291</v>
+        <v>534</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="K95" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="47.25">
+    <row r="96" spans="1:14">
       <c r="A96" s="8" t="s">
-        <v>537</v>
+        <v>43</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>538</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>815</v>
+        <v>539</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>808</v>
       </c>
       <c r="K96" s="8" t="s">
         <v>38</v>
@@ -11358,46 +11343,49 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B97" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="299.25">
+      <c r="A98" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B98" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C98" s="9" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="299.25">
-      <c r="A99" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>544</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>816</v>
+        <v>545</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>547</v>
@@ -11406,7 +11394,7 @@
         <v>548</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>99</v>
@@ -11417,16 +11405,16 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B101" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="C101" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="D101" s="8" t="s">
         <v>551</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>572</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>99</v>
@@ -11437,7 +11425,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>552</v>
@@ -11446,7 +11434,7 @@
         <v>553</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>99</v>
@@ -11457,16 +11445,16 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B103" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="C103" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="D103" s="8" t="s">
         <v>556</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>573</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>99</v>
@@ -11475,40 +11463,40 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" ht="63">
       <c r="A104" s="8" t="s">
-        <v>545</v>
+        <v>36</v>
       </c>
       <c r="B104" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="B105" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C105" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D105" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="F104" s="8" t="s">
+      <c r="F105" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="K104" s="8" t="s">
+      <c r="K105" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="63">
-      <c r="A105" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>560</v>
@@ -11528,7 +11516,7 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>563</v>
@@ -11548,7 +11536,7 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>566</v>
@@ -11568,63 +11556,60 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8" t="s">
-        <v>545</v>
+        <v>46</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K109" s="8" t="s">
-        <v>38</v>
+        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
+        <v>579</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="220.5">
       <c r="A111" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="220.5">
+        <v>580</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="63">
       <c r="A112" s="8" t="s">
-        <v>36</v>
+        <v>542</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>589</v>
+        <v>813</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="63">
       <c r="A113" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>99</v>
@@ -11633,15 +11618,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="63">
+    <row r="114" spans="1:14" ht="47.25">
       <c r="A114" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>99</v>
@@ -11650,15 +11635,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="47.25">
+    <row r="115" spans="1:14" ht="78.75">
       <c r="A115" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>99</v>
@@ -11667,15 +11652,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="78.75">
+    <row r="116" spans="1:14" ht="47.25">
       <c r="A116" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>99</v>
@@ -11684,380 +11669,377 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="47.25">
+    <row r="117" spans="1:14">
       <c r="A117" s="8" t="s">
-        <v>545</v>
+        <v>46</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>821</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K117" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="47.25">
+      <c r="A118" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="K118" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
-      <c r="A118" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" ht="47.25">
+    <row r="119" spans="1:14" ht="31.5">
       <c r="A119" s="8" t="s">
-        <v>291</v>
+        <v>592</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>822</v>
+        <v>819</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>942</v>
       </c>
       <c r="K119" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="31.5">
+    <row r="120" spans="1:14" ht="47.25">
       <c r="A120" s="8" t="s">
-        <v>595</v>
+        <v>291</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>823</v>
-      </c>
-      <c r="I120" s="8" t="s">
-        <v>946</v>
+        <v>820</v>
       </c>
       <c r="K120" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="47.25">
+    <row r="121" spans="1:14" ht="31.5">
       <c r="A121" s="8" t="s">
-        <v>291</v>
+        <v>592</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>824</v>
+        <v>821</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>943</v>
       </c>
       <c r="K121" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="31.5">
+    <row r="122" spans="1:14" ht="47.25">
       <c r="A122" s="8" t="s">
-        <v>595</v>
+        <v>291</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="I122" s="8" t="s">
-        <v>947</v>
+        <v>822</v>
       </c>
       <c r="K122" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="47.25">
+    <row r="123" spans="1:14" ht="31.5">
       <c r="A123" s="8" t="s">
-        <v>291</v>
+        <v>592</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>826</v>
+        <v>823</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>944</v>
       </c>
       <c r="K123" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="31.5">
+    <row r="124" spans="1:14">
       <c r="A124" s="8" t="s">
-        <v>595</v>
+        <v>153</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="C124" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="I124" s="8" t="s">
-        <v>948</v>
-      </c>
-      <c r="K124" s="8" t="s">
-        <v>38</v>
+        <v>703</v>
+      </c>
+      <c r="N124" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="N125" s="54" t="s">
-        <v>693</v>
+        <v>704</v>
+      </c>
+      <c r="N125" s="8" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="N126" s="8" t="s">
-        <v>708</v>
+        <v>525</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>528</v>
+        <v>466</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="N128" s="54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="63">
+      <c r="A129" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B128" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
-      <c r="A129" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="N129" s="54" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" ht="63">
-      <c r="A130" s="8" t="s">
-        <v>470</v>
-      </c>
       <c r="B130" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>828</v>
-      </c>
-      <c r="K130" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="94.5">
+      <c r="A131" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="47.25">
+      <c r="A132" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="K132" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
-      <c r="A131" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B131" s="8" t="s">
+    <row r="133" spans="1:11">
+      <c r="A133" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="F131" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" ht="94.5">
-      <c r="A132" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="C132" s="9" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" ht="47.25">
-      <c r="A133" s="8" t="s">
+      <c r="B133" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="B133" s="8" t="s">
-        <v>489</v>
-      </c>
       <c r="C133" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K133" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:11">
       <c r="A134" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K134" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:11" ht="31.5">
       <c r="A135" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K135" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="31.5">
+    <row r="136" spans="1:11" ht="47.25">
       <c r="A136" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K136" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="47.25">
+    <row r="137" spans="1:11" ht="94.5">
       <c r="A137" s="8" t="s">
-        <v>487</v>
+        <v>36</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>493</v>
+        <v>727</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="K137" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="K138" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="94.5">
-      <c r="A138" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="C138" s="9" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:11" ht="31.5">
       <c r="A139" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K139" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="31.5">
+    <row r="140" spans="1:11" ht="31.5">
       <c r="A140" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K140" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="31.5">
+    <row r="141" spans="1:11" ht="31.5">
       <c r="A141" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K141" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="31.5">
+    <row r="142" spans="1:11" ht="31.5">
       <c r="A142" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K142" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="31.5">
+    <row r="143" spans="1:11" ht="94.5">
       <c r="A143" s="8" t="s">
-        <v>487</v>
+        <v>36</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>498</v>
+        <v>728</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="K143" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K144" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="94.5">
-      <c r="A144" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="C144" s="9" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" ht="31.5">
       <c r="A145" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K145" s="8" t="s">
         <v>38</v>
@@ -12065,13 +12047,13 @@
     </row>
     <row r="146" spans="1:14" ht="31.5">
       <c r="A146" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K146" s="8" t="s">
         <v>38</v>
@@ -12079,13 +12061,13 @@
     </row>
     <row r="147" spans="1:14" ht="31.5">
       <c r="A147" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K147" s="8" t="s">
         <v>38</v>
@@ -12093,926 +12075,923 @@
     </row>
     <row r="148" spans="1:14" ht="31.5">
       <c r="A148" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K148" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="31.5">
+    <row r="149" spans="1:14">
       <c r="A149" s="8" t="s">
-        <v>487</v>
+        <v>46</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="C149" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="K149" s="8" t="s">
-        <v>38</v>
+        <v>481</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="8" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>484</v>
+        <v>707</v>
+      </c>
+      <c r="N150" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="N151" s="54" t="s">
-        <v>693</v>
+        <v>708</v>
+      </c>
+      <c r="N151" s="8" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="N152" s="8" t="s">
-        <v>712</v>
+        <v>466</v>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>469</v>
+        <v>626</v>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="8" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14">
+        <v>710</v>
+      </c>
+      <c r="N154" s="54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" ht="47.25">
       <c r="A155" s="8" t="s">
-        <v>153</v>
+        <v>627</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="N155" s="54" t="s">
-        <v>693</v>
+        <v>628</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="K155" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:14" ht="47.25">
       <c r="A156" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B156" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="B156" s="8" t="s">
-        <v>631</v>
-      </c>
       <c r="C156" s="9" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="47.25">
+    <row r="157" spans="1:14" ht="31.5">
       <c r="A157" s="8" t="s">
-        <v>632</v>
+        <v>45</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>847</v>
+        <v>844</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>683</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="31.5">
+    <row r="158" spans="1:14">
       <c r="A158" s="8" t="s">
-        <v>45</v>
+        <v>632</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>848</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>686</v>
+        <v>845</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" ht="47.25">
       <c r="A159" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B159" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="C159" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="D159" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="C159" s="9" t="s">
-        <v>849</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="47.25">
+    <row r="160" spans="1:14" ht="78.75">
       <c r="A160" s="8" t="s">
-        <v>637</v>
+        <v>45</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>638</v>
+        <v>848</v>
       </c>
       <c r="C160" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="H160" s="10" t="s">
         <v>850</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>639</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="78.75">
+    <row r="161" spans="1:14">
       <c r="A161" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B161" s="8" t="str">
+        <f>CONCATENATE(B160,"_number")</f>
+        <v>ingresos_mes_number</v>
+      </c>
+      <c r="N161" s="8" t="str">
+        <f>CONCATENATE("if(${",B160,"} = 88 or ${",B160,"} = 99, 0, ${",B160,"})")</f>
+        <v>if(${ingresos_mes} = 88 or ${ingresos_mes} = 99, 0, ${ingresos_mes})</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" ht="78.75">
+      <c r="A162" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B161" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="C161" s="9" t="s">
-        <v>894</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>854</v>
-      </c>
-      <c r="K161" s="8" t="s">
+      <c r="B162" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K162" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
-      <c r="A162" s="8" t="s">
+    <row r="163" spans="1:14">
+      <c r="A163" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B162" s="8" t="str">
-        <f>CONCATENATE(B161,"_number")</f>
-        <v>ingresos_mes_number</v>
-      </c>
-      <c r="N162" s="8" t="str">
-        <f>CONCATENATE("if(${",B161,"} = 88 or ${",B161,"} = 99, 0, ${",B161,"})")</f>
-        <v>if(${ingresos_mes} = 88 or ${ingresos_mes} = 99, 0, ${ingresos_mes})</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" ht="78.75">
-      <c r="A163" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="C163" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K163" s="8" t="s">
-        <v>38</v>
+      <c r="B163" s="8" t="str">
+        <f>CONCATENATE(B162,"_number")</f>
+        <v>gasto_alimentos_number</v>
+      </c>
+      <c r="N163" s="8" t="str">
+        <f>CONCATENATE("if(${",B162,"} = 88 or ${",B162,"} = 99, 0, ${",B162,"})")</f>
+        <v>if(${gasto_alimentos} = 88 or ${gasto_alimentos} = 99, 0, ${gasto_alimentos})</v>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="C164" t="s">
+        <v>913</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" ht="78.75">
+      <c r="A165" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K165" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14">
+      <c r="A166" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B164" s="8" t="str">
-        <f>CONCATENATE(B163,"_number")</f>
-        <v>gasto_alimentos_number</v>
-      </c>
-      <c r="N164" s="8" t="str">
-        <f>CONCATENATE("if(${",B163,"} = 88 or ${",B163,"} = 99, 0, ${",B163,"})")</f>
-        <v>if(${gasto_alimentos} = 88 or ${gasto_alimentos} = 99, 0, ${gasto_alimentos})</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14">
-      <c r="A165" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="C165" t="s">
-        <v>917</v>
-      </c>
-      <c r="I165" s="8" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" ht="78.75">
-      <c r="A166" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B166" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="C166" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="D166" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K166" s="8" t="s">
-        <v>38</v>
+      <c r="B166" s="8" t="str">
+        <f>CONCATENATE(B165,"_number")</f>
+        <v>gasto_educacion_number</v>
+      </c>
+      <c r="N166" s="8" t="str">
+        <f>CONCATENATE("if(${",B165,"} = 88 or ${",B165,"} = 99, 0, ${",B165,"})")</f>
+        <v>if(${gasto_educacion} = 88 or ${gasto_educacion} = 99, 0, ${gasto_educacion})</v>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="C167" t="s">
+        <v>914</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" ht="78.75">
+      <c r="A168" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14">
+      <c r="A169" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B167" s="8" t="str">
-        <f>CONCATENATE(B166,"_number")</f>
-        <v>gasto_educacion_number</v>
-      </c>
-      <c r="N167" s="8" t="str">
-        <f>CONCATENATE("if(${",B166,"} = 88 or ${",B166,"} = 99, 0, ${",B166,"})")</f>
-        <v>if(${gasto_educacion} = 88 or ${gasto_educacion} = 99, 0, ${gasto_educacion})</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14">
-      <c r="A168" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="C168" t="s">
-        <v>918</v>
-      </c>
-      <c r="I168" s="8" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" ht="78.75">
-      <c r="A169" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K169" s="8" t="s">
-        <v>38</v>
+      <c r="B169" s="8" t="str">
+        <f>CONCATENATE(B168,"_number")</f>
+        <v>gasto_transporte_number</v>
+      </c>
+      <c r="N169" s="8" t="str">
+        <f>CONCATENATE("if(${",B168,"} = 88 or ${",B168,"} = 99, 0, ${",B168,"})")</f>
+        <v>if(${gasto_transporte} = 88 or ${gasto_transporte} = 99, 0, ${gasto_transporte})</v>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="C170" t="s">
+        <v>915</v>
+      </c>
+      <c r="I170" s="8" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" ht="94.5">
+      <c r="A171" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14">
+      <c r="A172" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B170" s="8" t="str">
-        <f>CONCATENATE(B169,"_number")</f>
-        <v>gasto_transporte_number</v>
-      </c>
-      <c r="N170" s="8" t="str">
-        <f>CONCATENATE("if(${",B169,"} = 88 or ${",B169,"} = 99, 0, ${",B169,"})")</f>
-        <v>if(${gasto_transporte} = 88 or ${gasto_transporte} = 99, 0, ${gasto_transporte})</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14">
-      <c r="A171" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="C171" t="s">
-        <v>919</v>
-      </c>
-      <c r="I171" s="8" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" ht="94.5">
-      <c r="A172" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K172" s="8" t="s">
-        <v>38</v>
+      <c r="B172" s="8" t="str">
+        <f>CONCATENATE(B171,"_number")</f>
+        <v>gasto_salud_number</v>
+      </c>
+      <c r="N172" s="8" t="str">
+        <f>CONCATENATE("if(${",B171,"} = 88 or ${",B171,"} = 99, 0, ${",B171,"})")</f>
+        <v>if(${gasto_salud} = 88 or ${gasto_salud} = 99, 0, ${gasto_salud})</v>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="C173" t="s">
+        <v>916</v>
+      </c>
+      <c r="I173" s="8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" ht="78.75">
+      <c r="A174" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B173" s="8" t="str">
-        <f>CONCATENATE(B172,"_number")</f>
-        <v>gasto_salud_number</v>
-      </c>
-      <c r="N173" s="8" t="str">
-        <f>CONCATENATE("if(${",B172,"} = 88 or ${",B172,"} = 99, 0, ${",B172,"})")</f>
-        <v>if(${gasto_salud} = 88 or ${gasto_salud} = 99, 0, ${gasto_salud})</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
-      <c r="A174" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="C174" t="s">
-        <v>920</v>
-      </c>
-      <c r="I174" s="8" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" ht="78.75">
-      <c r="A175" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K175" s="8" t="s">
-        <v>38</v>
+      <c r="B175" s="8" t="str">
+        <f>CONCATENATE(B174,"_number")</f>
+        <v>gasto_arriendo_number</v>
+      </c>
+      <c r="N175" s="8" t="str">
+        <f>CONCATENATE("if(${",B174,"} = 88 or ${",B174,"} = 99, 0, ${",B174,"})")</f>
+        <v>if(${gasto_arriendo} = 88 or ${gasto_arriendo} = 99, 0, ${gasto_arriendo})</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B176" s="8" t="str">
-        <f>CONCATENATE(B175,"_number")</f>
-        <v>gasto_arriendo_number</v>
-      </c>
-      <c r="N176" s="8" t="str">
-        <f>CONCATENATE("if(${",B175,"} = 88 or ${",B175,"} = 99, 0, ${",B175,"})")</f>
-        <v>if(${gasto_arriendo} = 88 or ${gasto_arriendo} = 99, 0, ${gasto_arriendo})</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="C176" t="s">
+        <v>917</v>
+      </c>
+      <c r="I176" s="8" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" ht="31.5">
       <c r="A177" s="8" t="s">
-        <v>36</v>
+        <v>291</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="C177" t="s">
-        <v>921</v>
-      </c>
-      <c r="I177" s="8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" ht="31.5">
+        <v>851</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="K177" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" ht="78.75">
       <c r="A178" s="8" t="s">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>855</v>
+        <v>641</v>
       </c>
       <c r="C178" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="I178" s="8" t="s">
         <v>856</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="78.75">
+    <row r="179" spans="1:14">
       <c r="A179" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>861</v>
-      </c>
-      <c r="I179" s="8" t="s">
-        <v>860</v>
-      </c>
-      <c r="K179" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="B179" s="8" t="str">
+        <f>CONCATENATE(B178,"_number")</f>
+        <v>gasto_agua_number</v>
+      </c>
+      <c r="N179" s="8" t="str">
+        <f>CONCATENATE("if(${",B178,"} = 88 or ${",B178,"} = 99, 0, ${",B178,"})")</f>
+        <v>if(${gasto_agua} = 88 or ${gasto_agua} = 99, 0, ${gasto_agua})</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="C180" t="s">
+        <v>918</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" ht="94.5">
+      <c r="A181" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="I181" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="K181" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
+      <c r="A182" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B180" s="8" t="str">
-        <f>CONCATENATE(B179,"_number")</f>
-        <v>gasto_agua_number</v>
-      </c>
-      <c r="N180" s="8" t="str">
-        <f>CONCATENATE("if(${",B179,"} = 88 or ${",B179,"} = 99, 0, ${",B179,"})")</f>
-        <v>if(${gasto_agua} = 88 or ${gasto_agua} = 99, 0, ${gasto_agua})</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="A181" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B181" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C181" t="s">
-        <v>922</v>
-      </c>
-      <c r="I181" s="8" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" ht="94.5">
-      <c r="A182" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>861</v>
-      </c>
-      <c r="I182" s="8" t="s">
-        <v>860</v>
-      </c>
-      <c r="K182" s="8" t="s">
-        <v>38</v>
+      <c r="B182" s="8" t="str">
+        <f>CONCATENATE(B181,"_number")</f>
+        <v>gasto_energia_number</v>
+      </c>
+      <c r="N182" s="8" t="str">
+        <f>CONCATENATE("if(${",B181,"} = 88 or ${",B181,"} = 99, 0, ${",B181,"})")</f>
+        <v>if(${gasto_energia} = 88 or ${gasto_energia} = 99, 0, ${gasto_energia})</v>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="C183" t="s">
+        <v>919</v>
+      </c>
+      <c r="I183" s="8" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" ht="78.75">
+      <c r="A184" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="I184" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="K184" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14">
+      <c r="A185" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B183" s="8" t="str">
-        <f>CONCATENATE(B182,"_number")</f>
-        <v>gasto_energia_number</v>
-      </c>
-      <c r="N183" s="8" t="str">
-        <f>CONCATENATE("if(${",B182,"} = 88 or ${",B182,"} = 99, 0, ${",B182,"})")</f>
-        <v>if(${gasto_energia} = 88 or ${gasto_energia} = 99, 0, ${gasto_energia})</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14">
-      <c r="A184" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B184" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="C184" t="s">
-        <v>923</v>
-      </c>
-      <c r="I184" s="8" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14" ht="78.75">
-      <c r="A185" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="C185" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="D185" s="8" t="s">
-        <v>861</v>
-      </c>
-      <c r="I185" s="8" t="s">
-        <v>860</v>
-      </c>
-      <c r="K185" s="8" t="s">
-        <v>38</v>
+      <c r="B185" s="8" t="str">
+        <f>CONCATENATE(B184,"_number")</f>
+        <v>gasto_gas_gasolina_number</v>
+      </c>
+      <c r="N185" s="8" t="str">
+        <f>CONCATENATE("if(${",B184,"} = 88 or ${",B184,"} = 99, 0, ${",B184,"})")</f>
+        <v>if(${gasto_gas_gasolina} = 88 or ${gasto_gas_gasolina} = 99, 0, ${gasto_gas_gasolina})</v>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="C186" t="s">
+        <v>920</v>
+      </c>
+      <c r="I186" s="8" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" ht="78.75">
+      <c r="A187" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K187" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
+      <c r="A188" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B186" s="8" t="str">
-        <f>CONCATENATE(B185,"_number")</f>
-        <v>gasto_gas_gasolina_number</v>
-      </c>
-      <c r="N186" s="8" t="str">
-        <f>CONCATENATE("if(${",B185,"} = 88 or ${",B185,"} = 99, 0, ${",B185,"})")</f>
-        <v>if(${gasto_gas_gasolina} = 88 or ${gasto_gas_gasolina} = 99, 0, ${gasto_gas_gasolina})</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14">
-      <c r="A187" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B187" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="C187" t="s">
-        <v>924</v>
-      </c>
-      <c r="I187" s="8" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" ht="78.75">
-      <c r="A188" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K188" s="8" t="s">
-        <v>38</v>
+      <c r="B188" s="8" t="str">
+        <f>CONCATENATE(B187,"_number")</f>
+        <v>gasto_carbon_lena_number</v>
+      </c>
+      <c r="N188" s="8" t="str">
+        <f>CONCATENATE("if(${",B187,"} = 88 or ${",B187,"} = 99, 0, ${",B187,"})")</f>
+        <v>if(${gasto_carbon_lena} = 88 or ${gasto_carbon_lena} = 99, 0, ${gasto_carbon_lena})</v>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C189" t="s">
+        <v>921</v>
+      </c>
+      <c r="I189" s="8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" ht="94.5">
+      <c r="A190" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K190" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14">
+      <c r="A191" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B189" s="8" t="str">
-        <f>CONCATENATE(B188,"_number")</f>
-        <v>gasto_carbon_lena_number</v>
-      </c>
-      <c r="N189" s="8" t="str">
-        <f>CONCATENATE("if(${",B188,"} = 88 or ${",B188,"} = 99, 0, ${",B188,"})")</f>
-        <v>if(${gasto_carbon_lena} = 88 or ${gasto_carbon_lena} = 99, 0, ${gasto_carbon_lena})</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14">
-      <c r="A190" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="C190" t="s">
-        <v>925</v>
-      </c>
-      <c r="I190" s="8" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" ht="94.5">
-      <c r="A191" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B191" s="8" t="s">
-        <v>857</v>
-      </c>
-      <c r="C191" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="D191" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K191" s="8" t="s">
-        <v>38</v>
+      <c r="B191" s="8" t="str">
+        <f>CONCATENATE(B190,"_number")</f>
+        <v>gasto_internet_number</v>
+      </c>
+      <c r="N191" s="8" t="str">
+        <f>CONCATENATE("if(${",B190,"} = 88 or ${",B190,"} = 99, 0, ${",B190,"})")</f>
+        <v>if(${gasto_internet} = 88 or ${gasto_internet} = 99, 0, ${gasto_internet})</v>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="C192" t="s">
+        <v>922</v>
+      </c>
+      <c r="I192" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" ht="110.25">
+      <c r="A193" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K193" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
+      <c r="A194" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B192" s="8" t="str">
-        <f>CONCATENATE(B191,"_number")</f>
-        <v>gasto_internet_number</v>
-      </c>
-      <c r="N192" s="8" t="str">
-        <f>CONCATENATE("if(${",B191,"} = 88 or ${",B191,"} = 99, 0, ${",B191,"})")</f>
-        <v>if(${gasto_internet} = 88 or ${gasto_internet} = 99, 0, ${gasto_internet})</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14">
-      <c r="A193" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="C193" t="s">
-        <v>926</v>
-      </c>
-      <c r="I193" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" ht="110.25">
-      <c r="A194" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K194" s="8" t="s">
-        <v>38</v>
+      <c r="B194" s="8" t="str">
+        <f>CONCATENATE(B193,"_number")</f>
+        <v>gasto_no_alim_number</v>
+      </c>
+      <c r="N194" s="8" t="str">
+        <f>CONCATENATE("if(${",B193,"} = 88 or ${",B193,"} = 99, 0, ${",B193,"})")</f>
+        <v>if(${gasto_no_alim} = 88 or ${gasto_no_alim} = 99, 0, ${gasto_no_alim})</v>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C195" t="s">
+        <v>923</v>
+      </c>
+      <c r="I195" s="8" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="94.5">
+      <c r="A196" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K196" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="A197" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B195" s="8" t="str">
-        <f>CONCATENATE(B194,"_number")</f>
-        <v>gasto_no_alim_number</v>
-      </c>
-      <c r="N195" s="8" t="str">
-        <f>CONCATENATE("if(${",B194,"} = 88 or ${",B194,"} = 99, 0, ${",B194,"})")</f>
-        <v>if(${gasto_no_alim} = 88 or ${gasto_no_alim} = 99, 0, ${gasto_no_alim})</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14">
-      <c r="A196" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="C196" t="s">
-        <v>927</v>
-      </c>
-      <c r="I196" s="8" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14" ht="94.5">
-      <c r="A197" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="D197" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K197" s="8" t="s">
-        <v>38</v>
+      <c r="B197" s="8" t="str">
+        <f>CONCATENATE(B196,"_number")</f>
+        <v>gasto_prestamos_number</v>
+      </c>
+      <c r="N197" s="8" t="str">
+        <f>CONCATENATE("if(${",B196,"} = 88 or ${",B196,"} = 99, 0, ${",B196,"})")</f>
+        <v>if(${gasto_prestamos} = 88 or ${gasto_prestamos} = 99, 0, ${gasto_prestamos})</v>
       </c>
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C198" t="s">
+        <v>924</v>
+      </c>
+      <c r="I198" s="8" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" ht="94.5">
+      <c r="A199" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K199" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14">
+      <c r="A200" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B198" s="8" t="str">
-        <f>CONCATENATE(B197,"_number")</f>
-        <v>gasto_prestamos_number</v>
-      </c>
-      <c r="N198" s="8" t="str">
-        <f>CONCATENATE("if(${",B197,"} = 88 or ${",B197,"} = 99, 0, ${",B197,"})")</f>
-        <v>if(${gasto_prestamos} = 88 or ${gasto_prestamos} = 99, 0, ${gasto_prestamos})</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14">
-      <c r="A199" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B199" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="C199" t="s">
-        <v>928</v>
-      </c>
-      <c r="I199" s="8" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" ht="94.5">
-      <c r="A200" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="D200" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K200" s="8" t="s">
-        <v>38</v>
+      <c r="B200" s="8" t="str">
+        <f>CONCATENATE(B199,"_number")</f>
+        <v>gasto_inversion_number</v>
+      </c>
+      <c r="N200" s="8" t="str">
+        <f>CONCATENATE("if(${",B199,"} = 88 or ${",B199,"} = 99, 0, ${",B199,"})")</f>
+        <v>if(${gasto_inversion} = 88 or ${gasto_inversion} = 99, 0, ${gasto_inversion})</v>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="C201" t="s">
+        <v>925</v>
+      </c>
+      <c r="I201" s="8" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" ht="94.5">
+      <c r="A202" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K202" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14">
+      <c r="A203" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B201" s="8" t="str">
-        <f>CONCATENATE(B200,"_number")</f>
-        <v>gasto_inversion_number</v>
-      </c>
-      <c r="N201" s="8" t="str">
-        <f>CONCATENATE("if(${",B200,"} = 88 or ${",B200,"} = 99, 0, ${",B200,"})")</f>
-        <v>if(${gasto_inversion} = 88 or ${gasto_inversion} = 99, 0, ${gasto_inversion})</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14">
-      <c r="A202" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="C202" t="s">
-        <v>929</v>
-      </c>
-      <c r="I202" s="8" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" ht="94.5">
-      <c r="A203" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="C203" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="D203" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K203" s="8" t="s">
-        <v>38</v>
+      <c r="B203" s="8" t="str">
+        <f>CONCATENATE(B202,"_number")</f>
+        <v>gasto_remesas_ven_number</v>
+      </c>
+      <c r="N203" s="8" t="str">
+        <f>CONCATENATE("if(${",B202,"} = 88 or ${",B202,"} = 99, 0, ${",B202,"})")</f>
+        <v>if(${gasto_remesas_ven} = 88 or ${gasto_remesas_ven} = 99, 0, ${gasto_remesas_ven})</v>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C204" t="s">
+        <v>926</v>
+      </c>
+      <c r="I204" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="78.75">
+      <c r="A205" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K205" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14">
+      <c r="A206" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B204" s="8" t="str">
-        <f>CONCATENATE(B203,"_number")</f>
-        <v>gasto_remesas_ven_number</v>
-      </c>
-      <c r="N204" s="8" t="str">
-        <f>CONCATENATE("if(${",B203,"} = 88 or ${",B203,"} = 99, 0, ${",B203,"})")</f>
-        <v>if(${gasto_remesas_ven} = 88 or ${gasto_remesas_ven} = 99, 0, ${gasto_remesas_ven})</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14">
-      <c r="A205" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B205" s="8" t="s">
-        <v>678</v>
-      </c>
-      <c r="C205" t="s">
-        <v>930</v>
-      </c>
-      <c r="I205" s="8" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" ht="78.75">
-      <c r="A206" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>862</v>
-      </c>
-      <c r="D206" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K206" s="8" t="s">
-        <v>38</v>
+      <c r="B206" s="8" t="str">
+        <f>CONCATENATE(B205,"_number")</f>
+        <v>gasto_ahorros_number</v>
+      </c>
+      <c r="N206" s="8" t="str">
+        <f>CONCATENATE("if(${",B205,"} = 88 or ${",B205,"} = 99, 0, ${",B205,"})")</f>
+        <v>if(${gasto_ahorros} = 88 or ${gasto_ahorros} = 99, 0, ${gasto_ahorros})</v>
       </c>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C207" t="s">
+        <v>927</v>
+      </c>
+      <c r="I207" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" ht="78.75">
+      <c r="A208" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K208" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14">
+      <c r="A209" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B207" s="8" t="str">
-        <f>CONCATENATE(B206,"_number")</f>
-        <v>gasto_ahorros_number</v>
-      </c>
-      <c r="N207" s="8" t="str">
-        <f>CONCATENATE("if(${",B206,"} = 88 or ${",B206,"} = 99, 0, ${",B206,"})")</f>
-        <v>if(${gasto_ahorros} = 88 or ${gasto_ahorros} = 99, 0, ${gasto_ahorros})</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14">
-      <c r="A208" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="C208" t="s">
-        <v>931</v>
-      </c>
-      <c r="I208" s="8" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" ht="78.75">
-      <c r="A209" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>761</v>
-      </c>
-      <c r="D209" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="K209" s="8" t="s">
-        <v>38</v>
+      <c r="B209" s="8" t="str">
+        <f>CONCATENATE(B208,"_number")</f>
+        <v>gasto_otros_number</v>
+      </c>
+      <c r="N209" s="8" t="str">
+        <f>CONCATENATE("if(${",B208,"} = 88 or ${",B208,"} = 99, 0, ${",B208,"})")</f>
+        <v>if(${gasto_otros} = 88 or ${gasto_otros} = 99, 0, ${gasto_otros})</v>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B210" s="8" t="str">
-        <f>CONCATENATE(B209,"_number")</f>
-        <v>gasto_otros_number</v>
-      </c>
-      <c r="N210" s="8" t="str">
-        <f>CONCATENATE("if(${",B209,"} = 88 or ${",B209,"} = 99, 0, ${",B209,"})")</f>
-        <v>if(${gasto_otros} = 88 or ${gasto_otros} = 99, 0, ${gasto_otros})</v>
+        <v>36</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C210" t="s">
+        <v>928</v>
+      </c>
+      <c r="I210" s="8" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="C211" t="s">
-        <v>932</v>
-      </c>
-      <c r="I211" s="8" t="s">
-        <v>685</v>
+        <v>859</v>
+      </c>
+      <c r="N211" s="2" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="212" spans="1:14">
@@ -13020,116 +12999,105 @@
         <v>41</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="N212" s="2" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="8" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="N213" s="2" t="s">
-        <v>881</v>
+        <v>711</v>
+      </c>
+      <c r="N213" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="N214" s="54" t="s">
-        <v>693</v>
+        <v>712</v>
+      </c>
+      <c r="N214" s="8" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>715</v>
-      </c>
-      <c r="N215" s="8" t="s">
-        <v>716</v>
+        <v>626</v>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="8" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>629</v>
+        <v>717</v>
+      </c>
+      <c r="N216" s="54" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="8" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="N217" s="54" t="s">
-        <v>693</v>
+        <v>714</v>
+      </c>
+      <c r="N217" s="8" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="N218" s="8" t="s">
-        <v>718</v>
+        <v>292</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14">
+        <v>688</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" ht="31.5">
       <c r="A220" s="8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14" ht="31.5">
-      <c r="A221" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B221" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="D221" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="K221" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="D220" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="K220" s="8" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <autoFilter ref="A1:T221" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T220" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T61 A64:T65 A66:M66 A77:M77 A78:T80 A81:M82 A83:T86 A87:M88 A89:T90 A91:M91 A92:T123 A124:M124 A125:T127 A128:M128 A129:T149 A150:M151 A152:T153 A154:M154 A155:T189 A193:T212 A213:M213 A214:T215 A216:M217 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A76 O77:T77 O81:T82 O87:T88 O91:T91 O124:T124 O128:T128 O150:T151 N151 O154:T154 O213:T213 O216:T217 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="567" priority="737" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
@@ -13140,12 +13108,12 @@
       <formula>$A1="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A214:M214 A215:T216 A217:M218 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A156:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 A21:T21 A22:B22 A23:T24 A25:B39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T61 A64:T65 A66:M66 A77:M77 A78:T80 A81:M82 A83:T86 A87:M88 A89:T90 A91:M91 A92:T123 A124:M124 A125:T127 A128:M128 A129:T149 A150:M151 A152:T153 A154:M154 A155:T212 A213:M213 A214:T215 A216:M217 D20:T20 D22:T22 D25:T39 O45:T45 G52:T54 O66:T66 A76 O77:T77 O81:T82 O87:T88 O91:T91 O124:T124 O128:T128 O150:T151 N151 O154:T154 O213:T213 O216:T217 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="564" priority="727" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 O45:T45 G52:T54 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 A55:T61 A64:T65 A66:M66 A77:M77 A78:T80 A81:M82 A83:T86 A87:M88 A89:T90 A91:M91 A92:T123 A124:M124 A125:T127 A128:M128 A129:T149 A150:M151 A152:T153 A154:M154 A155:T189 A193:T212 A213:M213 A214:T215 A216:M217 O45:T45 G52:T54 O66:T66 A76 O77:T77 O81:T82 O87:T88 O91:T91 O124:T124 O128:T128 O150:T151 N151 O154:T154 O213:T213 O216:T217 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="563" priority="729" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
@@ -13162,7 +13130,7 @@
       <formula>$A1="text"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 O45:T45 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 N152 O155:T155 O214:T214 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A55:T61 A64:T65 A66:M66 A77:M77 A78:T80 A81:M82 A83:T86 A87:M88 A89:T90 A91:M91 A92:T123 A124:M124 A125:T127 A128:M128 A129:T149 A150:M151 A152:T153 A154:M154 A155:T189 A193:T212 A213:M213 A214:T215 A216:M217 O45:T45 O66:T66 A76 O77:T77 O81:T82 O87:T88 O91:T91 O124:T124 O128:T128 O150:T151 N151 O154:T154 O213:T213 O216:T217 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="558" priority="758" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
     </cfRule>
@@ -13173,12 +13141,12 @@
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 A67:T76 A78:M78 A79:T81 A82:M83 A84:T87 A88:M89 A90:T91 A92:M92 A93:T124 A125:M125 A126:T128 A129:M129 A151:M152 N152 A153:T154 A155:M155 A156:T190 A214:M214 A215:T216 A217:M218 N218 O45:T45 O66:T66 A77 O78:T78 O82:T83 O88:T89 O92:T92 O125:T125 O129:T129 O151:T152 O155:T155 O214:T214 O217:T218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 A48:T51 A52:E54 G52:T54 A55:T61 A64:T65 A66:M66 A77:M77 A78:T80 A81:M82 A83:T86 A87:M88 A89:T90 A91:M91 A92:T123 A124:M124 A125:T127 A128:M128 A129:T149 A150:M151 N151 A152:T153 A154:M154 A155:T189 A193:T212 A213:M213 A214:T215 A216:M217 N217 O45:T45 O66:T66 A76 O77:T77 O81:T82 O87:T88 O91:T91 O124:T124 O128:T128 O150:T151 O154:T154 O213:T213 O216:T217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="555" priority="735" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 O66:T66 A67:T76 A77 A78:M78 O78:T78 A79:T81 A82:M83 O82:T83 A84:T87 A88:M89 O88:T89 A90:T91 A92:M92 O92:T92 A93:T124 A125:M125 O125:T125 A126:T128 A129:M129 O129:T129 A151:M152 O151:T152 N152 A153:T154 A155:M155 O155:T155 A156:T190 A214:M214 O214:T214 A215:T216 A217:M218 O217:T218 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A55:T61 A64:T65 A66:M66 O66:T66 A76 A77:M77 O77:T77 A78:T80 A81:M82 O81:T82 A83:T86 A87:M88 O87:T88 A89:T90 A91:M91 O91:T91 A92:T123 A124:M124 O124:T124 A125:T127 A128:M128 O128:T128 A129:T149 A150:M151 O150:T151 N151 A152:T153 A154:M154 O154:T154 A155:T189 A193:T212 A213:M213 O213:T213 A214:T215 A216:M217 O216:T217 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="554" priority="746" stopIfTrue="1">
       <formula>OR($A1="username", $A1="phonenumber", $A1="start", $A1="end", $A1="deviceid", $A1="subscriberid", $A1="simserial")</formula>
     </cfRule>
@@ -13189,59 +13157,59 @@
       <formula>$A1="end group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A64:T65 A66:M66 O66:T66 A67:T76 A78:M78 O78:T78 A79:T81 A82:M83 O82:T83 A84:T87 A88:M89 O88:T89 A90:T91 A92:M92 O92:T92 A93:T124 A125:M125 O125:T125 A126:T128 A129:M129 O129:T129 A151:M152 O151:T152 A153:T154 A155:M155 O155:T155 A156:T190 A214:M214 O214:T214 A215:T216 A217:M218 O217:T218 A77 N152 N218 A194:T213 A130:T150 A55:T61 A219:T1048576">
+  <conditionalFormatting sqref="A1:T4 A9:T19 A20:B20 D20:T20 A21:T21 A22:B22 D22:T22 A23:T24 A25:B39 D25:T39 A40:T44 A45:M45 O45:T45 A48:T51 A52:E54 G52:T54 A55:T61 A64:T65 A66:M66 O66:T66 A77:M77 O77:T77 A78:T80 A81:M82 O81:T82 A83:T86 A87:M88 O87:T88 A89:T90 A91:M91 O91:T91 A92:T123 A124:M124 O124:T124 A125:T127 A128:M128 O128:T128 A129:T149 A150:M151 O150:T151 A152:T153 A154:M154 O154:T154 A155:T189 A193:T212 A213:M213 O213:T213 A214:T215 A216:M217 O216:T217 A76 N151 N217 A67:T75 A218:T1048576">
     <cfRule type="expression" dxfId="551" priority="765" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:T193">
+  <conditionalFormatting sqref="A190:T192">
     <cfRule type="expression" dxfId="550" priority="4" stopIfTrue="1">
-      <formula>$A191="image"</formula>
+      <formula>$A190="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="549" priority="5" stopIfTrue="1">
-      <formula>OR($A191="date", $A191="datetime")</formula>
+      <formula>OR($A190="date", $A190="datetime")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="548" priority="6" stopIfTrue="1">
-      <formula>OR($A191="calculate", $A191="calculate_here")</formula>
+      <formula>OR($A190="calculate", $A190="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="547" priority="8" stopIfTrue="1">
-      <formula>$A191="note"</formula>
+      <formula>$A190="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="546" priority="10" stopIfTrue="1">
-      <formula>$A191="barcode"</formula>
+      <formula>$A190="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="545" priority="12" stopIfTrue="1">
-      <formula>$A191="geopoint"</formula>
+      <formula>$A190="geopoint"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="544" priority="13" stopIfTrue="1">
-      <formula>OR($A191="audio audit", $A191="text audit")</formula>
+      <formula>OR($A190="audio audit", $A190="text audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="543" priority="14" stopIfTrue="1">
-      <formula>OR($A191="username", $A191="phonenumber", $A191="start", $A191="end", $A191="deviceid", $A191="subscriberid", $A191="simserial")</formula>
+      <formula>OR($A190="username", $A190="phonenumber", $A190="start", $A190="end", $A190="deviceid", $A190="subscriberid", $A190="simserial")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="542" priority="15" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A191, 16)="select_multiple ", LEN($A191)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A191, 17)))), AND(LEFT($A191, 11)="select_one ", LEN($A191)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A191, 12)))))</formula>
+      <formula>OR(AND(LEFT($A190, 16)="select_multiple ", LEN($A190)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A190, 17)))), AND(LEFT($A190, 11)="select_one ", LEN($A190)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A190, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="541" priority="17" stopIfTrue="1">
-      <formula>$A191="decimal"</formula>
+      <formula>$A190="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="540" priority="19" stopIfTrue="1">
-      <formula>$A191="integer"</formula>
+      <formula>$A190="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="539" priority="20" stopIfTrue="1">
-      <formula>$A191="text"</formula>
+      <formula>$A190="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="538" priority="21" stopIfTrue="1">
-      <formula>$A191="end repeat"</formula>
+      <formula>$A190="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="537" priority="22" stopIfTrue="1">
-      <formula>$A191="begin repeat"</formula>
+      <formula>$A190="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="536" priority="23" stopIfTrue="1">
-      <formula>$A191="end group"</formula>
+      <formula>$A190="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="535" priority="24" stopIfTrue="1">
-      <formula>$A191="begin group"</formula>
+      <formula>$A190="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W8">
@@ -13309,12 +13277,12 @@
       <formula>$A5="decimal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 F1:F4 F9:F45 F48:F51 F64:F76 B9:B76 F55:F61 B78:B1048576 F78:F1048576">
+  <conditionalFormatting sqref="B1:B4 F1:F4 F9:F45 F48:F51 F55:F61 B9:B75 F64:F75 B77:B1048576 F77:F1048576">
     <cfRule type="expression" dxfId="513" priority="742" stopIfTrue="1">
       <formula>OR($A1="audio audit", $A1="text audit")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 N1:N4 N9:N44 N64:N65 N67:N76 N79:N81 N84:N87 N90:N91 N93:N124 N126:N128 N152:N154 N215:N216 N156:N213 N130:N150 B9:B76 N48:N61 B78:B1048576 N218:N1048576">
+  <conditionalFormatting sqref="B1:B4 N1:N4 N9:N44 N48:N61 N64:N65 N78:N80 N83:N86 N89:N90 N92:N123 N125:N127 N129:N149 N151:N153 N155:N212 N214:N215 B9:B75 N67:N75 B77:B1048576 N217:N1048576">
     <cfRule type="expression" dxfId="512" priority="734" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
@@ -13515,7 +13483,7 @@
       <formula>$A62="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 B78:C190 B48:C61 B194:C1048576">
+  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C61 B77:C189 B64:C75 B193:C1048576">
     <cfRule type="expression" dxfId="449" priority="736" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
@@ -13526,7 +13494,7 @@
       <formula>$A1="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 F1:F4 B9:C19 F9:F45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B64:C76 F64:F76 B48:C61 F55:F61 B78:C1048576 F78:F1048576">
+  <conditionalFormatting sqref="B1:C4 F1:F4 B9:C19 F9:F45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B48:C61 F55:F61 B64:C75 F64:F75 B77:C1048576 F77:F1048576">
     <cfRule type="expression" dxfId="446" priority="728" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
@@ -13537,12 +13505,12 @@
       <formula>OR(AND(LEFT($A1, 16)="select_multiple ", LEN($A1)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A1, 17)))), AND(LEFT($A1, 11)="select_one ", LEN($A1)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A1, 12)))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 F1:F4 I1:I4 B9:C19 F9:F45 I9:I45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B64:C76 F64:F76 I64:I76 B48:C61 I48:I61 F55:F61 B78:C1048576 F78:F1048576 I78:I1048576">
+  <conditionalFormatting sqref="B1:C4 F1:F4 I1:I4 B9:C19 F9:F45 I9:I45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 F48:F51 B48:C61 I48:I61 F55:F61 B64:C75 F64:F75 I64:I75 B77:C1048576 F77:F1048576 I77:I1048576">
     <cfRule type="expression" dxfId="443" priority="767" stopIfTrue="1">
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 I1:I4 O1:O4 B9:C19 I9:I45 O9:O45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 I64:I76 O64:O76 B48:C61 I48:I61 O48:O61 B78:C1048576 I78:I1048576 O78:O1048576">
+  <conditionalFormatting sqref="B1:C4 I1:I4 O1:O4 B9:C19 I9:I45 O9:O45 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C61 I48:I61 O48:O61 B64:C75 I64:I75 O64:O75 B77:C1048576 I77:I1048576 O77:O1048576">
     <cfRule type="expression" dxfId="442" priority="764" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
@@ -13585,28 +13553,28 @@
       <formula>$A5="file"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B64:C76 B48:C61 B78:C1048576">
+  <conditionalFormatting sqref="B1:C4 B9:C19 B20 B21:C21 B22 B23:C24 B25:B39 B40:C45 B48:C61 B77:C1048576 B64:C75">
     <cfRule type="expression" dxfId="431" priority="726" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191:C193">
+  <conditionalFormatting sqref="B190:C192">
     <cfRule type="expression" dxfId="430" priority="7" stopIfTrue="1">
-      <formula>$A191="note"</formula>
+      <formula>$A190="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="429" priority="9" stopIfTrue="1">
-      <formula>$A191="barcode"</formula>
+      <formula>$A190="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="428" priority="11" stopIfTrue="1">
-      <formula>$A191="geopoint"</formula>
+      <formula>$A190="geopoint"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D4 F1:F4 B9:D19 F9:F45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 F48:F51 B64:D76 F64:F76 B48:D61 F55:F61 B78:D1048576 F78:F1048576">
+  <conditionalFormatting sqref="B1:D4 F1:F4 B9:D19 F9:F45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 F48:F51 B48:D61 F55:F61 B64:D75 F64:F75 B77:D1048576 F77:F1048576">
     <cfRule type="expression" dxfId="427" priority="761" stopIfTrue="1">
       <formula>$A1="text"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D4 G1:H4 B9:D19 G9:H45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 B64:D76 G64:H76 B78:D190 G78:H190 B48:D61 G48:H61 B194:D1048576 G194:H1048576">
+  <conditionalFormatting sqref="B1:D4 G1:H4 B9:D19 G9:H45 B20 D20 B21:D21 B22 D22 B23:D24 B25:B39 D25:D39 B40:D45 B48:D61 G48:H61 B77:D189 G77:H189 B64:D75 G64:H75 B193:D1048576 G193:H1048576">
     <cfRule type="expression" dxfId="426" priority="757" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
     </cfRule>
@@ -13630,12 +13598,12 @@
       <formula>$A5="integer"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191:D193 G191:H193">
+  <conditionalFormatting sqref="B190:D192 G190:H192">
     <cfRule type="expression" dxfId="420" priority="16" stopIfTrue="1">
-      <formula>$A191="decimal"</formula>
+      <formula>$A190="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="419" priority="18" stopIfTrue="1">
-      <formula>$A191="integer"</formula>
+      <formula>$A190="integer"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20 C22 C25:C39">
@@ -13825,15 +13793,15 @@
       <formula>$A52="enumerator"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I120:I126">
+  <conditionalFormatting sqref="I119:I125">
     <cfRule type="expression" dxfId="357" priority="417" stopIfTrue="1">
-      <formula>$A120="decimal"</formula>
+      <formula>$A119="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="356" priority="418" stopIfTrue="1">
-      <formula>$A120="integer"</formula>
+      <formula>$A119="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="355" priority="419" stopIfTrue="1">
-      <formula>$A120="text"</formula>
+      <formula>$A119="text"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
@@ -14022,7 +13990,7 @@
       <formula>OR($A62="calculate", $A62="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N66 N78">
+  <conditionalFormatting sqref="N66 N77">
     <cfRule type="expression" dxfId="294" priority="463" stopIfTrue="1">
       <formula>$A66="enumerator"</formula>
     </cfRule>
@@ -14084,562 +14052,562 @@
       <formula>OR($A66="calculate", $A66="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N82:N83">
+  <conditionalFormatting sqref="N81:N82">
     <cfRule type="expression" dxfId="274" priority="328" stopIfTrue="1">
-      <formula>$A82="enumerator"</formula>
+      <formula>$A81="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="273" priority="329" stopIfTrue="1">
-      <formula>$A82="barcode"</formula>
+      <formula>$A81="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="272" priority="330" stopIfTrue="1">
-      <formula>OR($A82="geopoint", $A82="geoshape", $A82="geotrace")</formula>
+      <formula>OR($A81="geopoint", $A81="geoshape", $A81="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="271" priority="331" stopIfTrue="1">
-      <formula>$A82="file"</formula>
+      <formula>$A81="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="270" priority="332" stopIfTrue="1">
-      <formula>$A82="note"</formula>
+      <formula>$A81="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="269" priority="333" stopIfTrue="1">
-      <formula>$A82="begin group"</formula>
+      <formula>$A81="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="268" priority="334" stopIfTrue="1">
-      <formula>OR($A82="audio", $A82="video")</formula>
+      <formula>OR($A81="audio", $A81="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="267" priority="335" stopIfTrue="1">
-      <formula>OR($A82="audio audit", $A82="text audit", $A82="speed violations count", $A82="speed violations list", $A82="speed violations audit")</formula>
+      <formula>OR($A81="audio audit", $A81="text audit", $A81="speed violations count", $A81="speed violations list", $A81="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="266" priority="336" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A82, 16)="select_multiple ", LEN($A82)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A82, 17)))), AND(LEFT($A82, 11)="select_one ", LEN($A82)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A82, 12)))))</formula>
+      <formula>OR(AND(LEFT($A81, 16)="select_multiple ", LEN($A81)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A81, 17)))), AND(LEFT($A81, 11)="select_one ", LEN($A81)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A81, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="265" priority="337" stopIfTrue="1">
-      <formula>$A82="decimal"</formula>
+      <formula>$A81="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="264" priority="338" stopIfTrue="1">
-      <formula>$A82="integer"</formula>
+      <formula>$A81="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="263" priority="339" stopIfTrue="1">
-      <formula>$A82="text"</formula>
+      <formula>$A81="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="262" priority="340" stopIfTrue="1">
-      <formula>$A82="image"</formula>
+      <formula>$A81="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="261" priority="341" stopIfTrue="1">
-      <formula>OR($A82="date", $A82="datetime", $A82="time")</formula>
+      <formula>OR($A81="date", $A81="datetime", $A81="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="260" priority="342" stopIfTrue="1">
-      <formula>OR($A82="calculate", $A82="calculate_here")</formula>
+      <formula>OR($A81="calculate", $A81="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="259" priority="343" stopIfTrue="1">
-      <formula>OR($A82="username", $A82="phonenumber", $A82="start", $A82="end", $A82="deviceid", $A82="subscriberid", $A82="simserial", $A82="caseid")</formula>
+      <formula>OR($A81="username", $A81="phonenumber", $A81="start", $A81="end", $A81="deviceid", $A81="subscriberid", $A81="simserial", $A81="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="258" priority="344" stopIfTrue="1">
-      <formula>$A82="end repeat"</formula>
+      <formula>$A81="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="257" priority="345" stopIfTrue="1">
-      <formula>$A82="begin repeat"</formula>
+      <formula>$A81="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="256" priority="346" stopIfTrue="1">
-      <formula>$A82="end group"</formula>
+      <formula>$A81="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="255" priority="347" stopIfTrue="1">
-      <formula>OR($A82="calculate", $A82="calculate_here")</formula>
+      <formula>OR($A81="calculate", $A81="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N88:N89">
+  <conditionalFormatting sqref="N87:N88">
     <cfRule type="expression" dxfId="254" priority="288" stopIfTrue="1">
-      <formula>$A88="enumerator"</formula>
+      <formula>$A87="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="253" priority="289" stopIfTrue="1">
-      <formula>$A88="barcode"</formula>
+      <formula>$A87="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="252" priority="290" stopIfTrue="1">
-      <formula>OR($A88="geopoint", $A88="geoshape", $A88="geotrace")</formula>
+      <formula>OR($A87="geopoint", $A87="geoshape", $A87="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="251" priority="291" stopIfTrue="1">
-      <formula>$A88="file"</formula>
+      <formula>$A87="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="250" priority="292" stopIfTrue="1">
-      <formula>$A88="note"</formula>
+      <formula>$A87="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="249" priority="293" stopIfTrue="1">
-      <formula>$A88="begin group"</formula>
+      <formula>$A87="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="248" priority="294" stopIfTrue="1">
-      <formula>OR($A88="audio", $A88="video")</formula>
+      <formula>OR($A87="audio", $A87="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="247" priority="295" stopIfTrue="1">
-      <formula>OR($A88="audio audit", $A88="text audit", $A88="speed violations count", $A88="speed violations list", $A88="speed violations audit")</formula>
+      <formula>OR($A87="audio audit", $A87="text audit", $A87="speed violations count", $A87="speed violations list", $A87="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="246" priority="296" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A88, 16)="select_multiple ", LEN($A88)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A88, 17)))), AND(LEFT($A88, 11)="select_one ", LEN($A88)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A88, 12)))))</formula>
+      <formula>OR(AND(LEFT($A87, 16)="select_multiple ", LEN($A87)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A87, 17)))), AND(LEFT($A87, 11)="select_one ", LEN($A87)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A87, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="245" priority="297" stopIfTrue="1">
-      <formula>$A88="decimal"</formula>
+      <formula>$A87="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="244" priority="298" stopIfTrue="1">
-      <formula>$A88="integer"</formula>
+      <formula>$A87="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="243" priority="299" stopIfTrue="1">
-      <formula>$A88="text"</formula>
+      <formula>$A87="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="242" priority="300" stopIfTrue="1">
-      <formula>$A88="image"</formula>
+      <formula>$A87="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="241" priority="301" stopIfTrue="1">
-      <formula>OR($A88="date", $A88="datetime", $A88="time")</formula>
+      <formula>OR($A87="date", $A87="datetime", $A87="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="240" priority="302" stopIfTrue="1">
-      <formula>OR($A88="calculate", $A88="calculate_here")</formula>
+      <formula>OR($A87="calculate", $A87="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="239" priority="303" stopIfTrue="1">
-      <formula>OR($A88="username", $A88="phonenumber", $A88="start", $A88="end", $A88="deviceid", $A88="subscriberid", $A88="simserial", $A88="caseid")</formula>
+      <formula>OR($A87="username", $A87="phonenumber", $A87="start", $A87="end", $A87="deviceid", $A87="subscriberid", $A87="simserial", $A87="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="238" priority="304" stopIfTrue="1">
-      <formula>$A88="end repeat"</formula>
+      <formula>$A87="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="237" priority="305" stopIfTrue="1">
-      <formula>$A88="begin repeat"</formula>
+      <formula>$A87="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="236" priority="306" stopIfTrue="1">
-      <formula>$A88="end group"</formula>
+      <formula>$A87="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="235" priority="307" stopIfTrue="1">
-      <formula>OR($A88="calculate", $A88="calculate_here")</formula>
+      <formula>OR($A87="calculate", $A87="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N92">
+  <conditionalFormatting sqref="N91">
     <cfRule type="expression" dxfId="234" priority="228" stopIfTrue="1">
-      <formula>$A92="enumerator"</formula>
+      <formula>$A91="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="233" priority="229" stopIfTrue="1">
-      <formula>$A92="barcode"</formula>
+      <formula>$A91="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="232" priority="230" stopIfTrue="1">
-      <formula>OR($A92="geopoint", $A92="geoshape", $A92="geotrace")</formula>
+      <formula>OR($A91="geopoint", $A91="geoshape", $A91="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="231" priority="231" stopIfTrue="1">
-      <formula>$A92="file"</formula>
+      <formula>$A91="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="230" priority="232" stopIfTrue="1">
-      <formula>$A92="note"</formula>
+      <formula>$A91="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="229" priority="233" stopIfTrue="1">
-      <formula>$A92="begin group"</formula>
+      <formula>$A91="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="228" priority="234" stopIfTrue="1">
-      <formula>OR($A92="audio", $A92="video")</formula>
+      <formula>OR($A91="audio", $A91="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="227" priority="235" stopIfTrue="1">
-      <formula>OR($A92="audio audit", $A92="text audit", $A92="speed violations count", $A92="speed violations list", $A92="speed violations audit")</formula>
+      <formula>OR($A91="audio audit", $A91="text audit", $A91="speed violations count", $A91="speed violations list", $A91="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="226" priority="236" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A92, 16)="select_multiple ", LEN($A92)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A92, 17)))), AND(LEFT($A92, 11)="select_one ", LEN($A92)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A92, 12)))))</formula>
+      <formula>OR(AND(LEFT($A91, 16)="select_multiple ", LEN($A91)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A91, 17)))), AND(LEFT($A91, 11)="select_one ", LEN($A91)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A91, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="225" priority="237" stopIfTrue="1">
-      <formula>$A92="decimal"</formula>
+      <formula>$A91="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="224" priority="238" stopIfTrue="1">
-      <formula>$A92="integer"</formula>
+      <formula>$A91="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="223" priority="239" stopIfTrue="1">
-      <formula>$A92="text"</formula>
+      <formula>$A91="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="222" priority="240" stopIfTrue="1">
-      <formula>$A92="image"</formula>
+      <formula>$A91="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="221" priority="241" stopIfTrue="1">
-      <formula>OR($A92="date", $A92="datetime", $A92="time")</formula>
+      <formula>OR($A91="date", $A91="datetime", $A91="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="220" priority="242" stopIfTrue="1">
-      <formula>OR($A92="calculate", $A92="calculate_here")</formula>
+      <formula>OR($A91="calculate", $A91="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="219" priority="243" stopIfTrue="1">
-      <formula>OR($A92="username", $A92="phonenumber", $A92="start", $A92="end", $A92="deviceid", $A92="subscriberid", $A92="simserial", $A92="caseid")</formula>
+      <formula>OR($A91="username", $A91="phonenumber", $A91="start", $A91="end", $A91="deviceid", $A91="subscriberid", $A91="simserial", $A91="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="218" priority="244" stopIfTrue="1">
-      <formula>$A92="end repeat"</formula>
+      <formula>$A91="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="217" priority="245" stopIfTrue="1">
-      <formula>$A92="begin repeat"</formula>
+      <formula>$A91="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="216" priority="246" stopIfTrue="1">
-      <formula>$A92="end group"</formula>
+      <formula>$A91="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="215" priority="247" stopIfTrue="1">
-      <formula>OR($A92="calculate", $A92="calculate_here")</formula>
+      <formula>OR($A91="calculate", $A91="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N125">
+  <conditionalFormatting sqref="N124">
     <cfRule type="expression" dxfId="214" priority="208" stopIfTrue="1">
-      <formula>$A125="enumerator"</formula>
+      <formula>$A124="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="213" priority="209" stopIfTrue="1">
-      <formula>$A125="barcode"</formula>
+      <formula>$A124="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="212" priority="210" stopIfTrue="1">
-      <formula>OR($A125="geopoint", $A125="geoshape", $A125="geotrace")</formula>
+      <formula>OR($A124="geopoint", $A124="geoshape", $A124="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="211" priority="211" stopIfTrue="1">
-      <formula>$A125="file"</formula>
+      <formula>$A124="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="210" priority="212" stopIfTrue="1">
-      <formula>$A125="note"</formula>
+      <formula>$A124="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="209" priority="213" stopIfTrue="1">
-      <formula>$A125="begin group"</formula>
+      <formula>$A124="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="208" priority="214" stopIfTrue="1">
-      <formula>OR($A125="audio", $A125="video")</formula>
+      <formula>OR($A124="audio", $A124="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="207" priority="215" stopIfTrue="1">
-      <formula>OR($A125="audio audit", $A125="text audit", $A125="speed violations count", $A125="speed violations list", $A125="speed violations audit")</formula>
+      <formula>OR($A124="audio audit", $A124="text audit", $A124="speed violations count", $A124="speed violations list", $A124="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="206" priority="216" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A125, 16)="select_multiple ", LEN($A125)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A125, 17)))), AND(LEFT($A125, 11)="select_one ", LEN($A125)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A125, 12)))))</formula>
+      <formula>OR(AND(LEFT($A124, 16)="select_multiple ", LEN($A124)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A124, 17)))), AND(LEFT($A124, 11)="select_one ", LEN($A124)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A124, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="205" priority="217" stopIfTrue="1">
-      <formula>$A125="decimal"</formula>
+      <formula>$A124="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="204" priority="218" stopIfTrue="1">
-      <formula>$A125="integer"</formula>
+      <formula>$A124="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="203" priority="219" stopIfTrue="1">
-      <formula>$A125="text"</formula>
+      <formula>$A124="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="202" priority="220" stopIfTrue="1">
-      <formula>$A125="image"</formula>
+      <formula>$A124="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="201" priority="221" stopIfTrue="1">
-      <formula>OR($A125="date", $A125="datetime", $A125="time")</formula>
+      <formula>OR($A124="date", $A124="datetime", $A124="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="200" priority="222" stopIfTrue="1">
-      <formula>OR($A125="calculate", $A125="calculate_here")</formula>
+      <formula>OR($A124="calculate", $A124="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="199" priority="223" stopIfTrue="1">
-      <formula>OR($A125="username", $A125="phonenumber", $A125="start", $A125="end", $A125="deviceid", $A125="subscriberid", $A125="simserial", $A125="caseid")</formula>
+      <formula>OR($A124="username", $A124="phonenumber", $A124="start", $A124="end", $A124="deviceid", $A124="subscriberid", $A124="simserial", $A124="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="198" priority="224" stopIfTrue="1">
-      <formula>$A125="end repeat"</formula>
+      <formula>$A124="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="197" priority="225" stopIfTrue="1">
-      <formula>$A125="begin repeat"</formula>
+      <formula>$A124="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="196" priority="226" stopIfTrue="1">
-      <formula>$A125="end group"</formula>
+      <formula>$A124="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="195" priority="227" stopIfTrue="1">
-      <formula>OR($A125="calculate", $A125="calculate_here")</formula>
+      <formula>OR($A124="calculate", $A124="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N129">
+  <conditionalFormatting sqref="N128">
     <cfRule type="expression" dxfId="194" priority="188" stopIfTrue="1">
-      <formula>$A129="enumerator"</formula>
+      <formula>$A128="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="193" priority="189" stopIfTrue="1">
-      <formula>$A129="barcode"</formula>
+      <formula>$A128="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="192" priority="190" stopIfTrue="1">
-      <formula>OR($A129="geopoint", $A129="geoshape", $A129="geotrace")</formula>
+      <formula>OR($A128="geopoint", $A128="geoshape", $A128="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="191" priority="191" stopIfTrue="1">
-      <formula>$A129="file"</formula>
+      <formula>$A128="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="190" priority="192" stopIfTrue="1">
-      <formula>$A129="note"</formula>
+      <formula>$A128="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="189" priority="193" stopIfTrue="1">
-      <formula>$A129="begin group"</formula>
+      <formula>$A128="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="188" priority="194" stopIfTrue="1">
-      <formula>OR($A129="audio", $A129="video")</formula>
+      <formula>OR($A128="audio", $A128="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="187" priority="195" stopIfTrue="1">
-      <formula>OR($A129="audio audit", $A129="text audit", $A129="speed violations count", $A129="speed violations list", $A129="speed violations audit")</formula>
+      <formula>OR($A128="audio audit", $A128="text audit", $A128="speed violations count", $A128="speed violations list", $A128="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="186" priority="196" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A129, 16)="select_multiple ", LEN($A129)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A129, 17)))), AND(LEFT($A129, 11)="select_one ", LEN($A129)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A129, 12)))))</formula>
+      <formula>OR(AND(LEFT($A128, 16)="select_multiple ", LEN($A128)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A128, 17)))), AND(LEFT($A128, 11)="select_one ", LEN($A128)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A128, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="185" priority="197" stopIfTrue="1">
-      <formula>$A129="decimal"</formula>
+      <formula>$A128="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="184" priority="198" stopIfTrue="1">
-      <formula>$A129="integer"</formula>
+      <formula>$A128="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="183" priority="199" stopIfTrue="1">
-      <formula>$A129="text"</formula>
+      <formula>$A128="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="182" priority="200" stopIfTrue="1">
-      <formula>$A129="image"</formula>
+      <formula>$A128="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="181" priority="201" stopIfTrue="1">
-      <formula>OR($A129="date", $A129="datetime", $A129="time")</formula>
+      <formula>OR($A128="date", $A128="datetime", $A128="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="180" priority="202" stopIfTrue="1">
-      <formula>OR($A129="calculate", $A129="calculate_here")</formula>
+      <formula>OR($A128="calculate", $A128="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="179" priority="203" stopIfTrue="1">
-      <formula>OR($A129="username", $A129="phonenumber", $A129="start", $A129="end", $A129="deviceid", $A129="subscriberid", $A129="simserial", $A129="caseid")</formula>
+      <formula>OR($A128="username", $A128="phonenumber", $A128="start", $A128="end", $A128="deviceid", $A128="subscriberid", $A128="simserial", $A128="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="178" priority="204" stopIfTrue="1">
-      <formula>$A129="end repeat"</formula>
+      <formula>$A128="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="177" priority="205" stopIfTrue="1">
-      <formula>$A129="begin repeat"</formula>
+      <formula>$A128="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="176" priority="206" stopIfTrue="1">
-      <formula>$A129="end group"</formula>
+      <formula>$A128="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="175" priority="207" stopIfTrue="1">
-      <formula>OR($A129="calculate", $A129="calculate_here")</formula>
+      <formula>OR($A128="calculate", $A128="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N151">
+  <conditionalFormatting sqref="N150">
     <cfRule type="expression" dxfId="174" priority="168" stopIfTrue="1">
-      <formula>$A151="enumerator"</formula>
+      <formula>$A150="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="173" priority="169" stopIfTrue="1">
-      <formula>$A151="barcode"</formula>
+      <formula>$A150="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="172" priority="170" stopIfTrue="1">
-      <formula>OR($A151="geopoint", $A151="geoshape", $A151="geotrace")</formula>
+      <formula>OR($A150="geopoint", $A150="geoshape", $A150="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="171" priority="171" stopIfTrue="1">
-      <formula>$A151="file"</formula>
+      <formula>$A150="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="170" priority="172" stopIfTrue="1">
-      <formula>$A151="note"</formula>
+      <formula>$A150="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="169" priority="173" stopIfTrue="1">
-      <formula>$A151="begin group"</formula>
+      <formula>$A150="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="168" priority="174" stopIfTrue="1">
-      <formula>OR($A151="audio", $A151="video")</formula>
+      <formula>OR($A150="audio", $A150="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="167" priority="175" stopIfTrue="1">
-      <formula>OR($A151="audio audit", $A151="text audit", $A151="speed violations count", $A151="speed violations list", $A151="speed violations audit")</formula>
+      <formula>OR($A150="audio audit", $A150="text audit", $A150="speed violations count", $A150="speed violations list", $A150="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="166" priority="176" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A151, 16)="select_multiple ", LEN($A151)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A151, 17)))), AND(LEFT($A151, 11)="select_one ", LEN($A151)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A151, 12)))))</formula>
+      <formula>OR(AND(LEFT($A150, 16)="select_multiple ", LEN($A150)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A150, 17)))), AND(LEFT($A150, 11)="select_one ", LEN($A150)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A150, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="165" priority="177" stopIfTrue="1">
-      <formula>$A151="decimal"</formula>
+      <formula>$A150="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="164" priority="178" stopIfTrue="1">
-      <formula>$A151="integer"</formula>
+      <formula>$A150="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="163" priority="179" stopIfTrue="1">
-      <formula>$A151="text"</formula>
+      <formula>$A150="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="162" priority="180" stopIfTrue="1">
-      <formula>$A151="image"</formula>
+      <formula>$A150="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="161" priority="181" stopIfTrue="1">
-      <formula>OR($A151="date", $A151="datetime", $A151="time")</formula>
+      <formula>OR($A150="date", $A150="datetime", $A150="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="160" priority="182" stopIfTrue="1">
-      <formula>OR($A151="calculate", $A151="calculate_here")</formula>
+      <formula>OR($A150="calculate", $A150="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="159" priority="183" stopIfTrue="1">
-      <formula>OR($A151="username", $A151="phonenumber", $A151="start", $A151="end", $A151="deviceid", $A151="subscriberid", $A151="simserial", $A151="caseid")</formula>
+      <formula>OR($A150="username", $A150="phonenumber", $A150="start", $A150="end", $A150="deviceid", $A150="subscriberid", $A150="simserial", $A150="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="158" priority="184" stopIfTrue="1">
-      <formula>$A151="end repeat"</formula>
+      <formula>$A150="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="157" priority="185" stopIfTrue="1">
-      <formula>$A151="begin repeat"</formula>
+      <formula>$A150="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="156" priority="186" stopIfTrue="1">
-      <formula>$A151="end group"</formula>
+      <formula>$A150="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="155" priority="187" stopIfTrue="1">
-      <formula>OR($A151="calculate", $A151="calculate_here")</formula>
+      <formula>OR($A150="calculate", $A150="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N155">
+  <conditionalFormatting sqref="N154">
     <cfRule type="expression" dxfId="154" priority="148" stopIfTrue="1">
-      <formula>$A155="enumerator"</formula>
+      <formula>$A154="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="153" priority="149" stopIfTrue="1">
-      <formula>$A155="barcode"</formula>
+      <formula>$A154="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="152" priority="150" stopIfTrue="1">
-      <formula>OR($A155="geopoint", $A155="geoshape", $A155="geotrace")</formula>
+      <formula>OR($A154="geopoint", $A154="geoshape", $A154="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="151" priority="151" stopIfTrue="1">
-      <formula>$A155="file"</formula>
+      <formula>$A154="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="150" priority="152" stopIfTrue="1">
-      <formula>$A155="note"</formula>
+      <formula>$A154="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="149" priority="153" stopIfTrue="1">
-      <formula>$A155="begin group"</formula>
+      <formula>$A154="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="148" priority="154" stopIfTrue="1">
-      <formula>OR($A155="audio", $A155="video")</formula>
+      <formula>OR($A154="audio", $A154="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="147" priority="155" stopIfTrue="1">
-      <formula>OR($A155="audio audit", $A155="text audit", $A155="speed violations count", $A155="speed violations list", $A155="speed violations audit")</formula>
+      <formula>OR($A154="audio audit", $A154="text audit", $A154="speed violations count", $A154="speed violations list", $A154="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="146" priority="156" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A155, 16)="select_multiple ", LEN($A155)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A155, 17)))), AND(LEFT($A155, 11)="select_one ", LEN($A155)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A155, 12)))))</formula>
+      <formula>OR(AND(LEFT($A154, 16)="select_multiple ", LEN($A154)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A154, 17)))), AND(LEFT($A154, 11)="select_one ", LEN($A154)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A154, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="145" priority="157" stopIfTrue="1">
-      <formula>$A155="decimal"</formula>
+      <formula>$A154="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="144" priority="158" stopIfTrue="1">
-      <formula>$A155="integer"</formula>
+      <formula>$A154="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="143" priority="159" stopIfTrue="1">
-      <formula>$A155="text"</formula>
+      <formula>$A154="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="142" priority="160" stopIfTrue="1">
-      <formula>$A155="image"</formula>
+      <formula>$A154="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="141" priority="161" stopIfTrue="1">
-      <formula>OR($A155="date", $A155="datetime", $A155="time")</formula>
+      <formula>OR($A154="date", $A154="datetime", $A154="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="140" priority="162" stopIfTrue="1">
-      <formula>OR($A155="calculate", $A155="calculate_here")</formula>
+      <formula>OR($A154="calculate", $A154="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="139" priority="163" stopIfTrue="1">
-      <formula>OR($A155="username", $A155="phonenumber", $A155="start", $A155="end", $A155="deviceid", $A155="subscriberid", $A155="simserial", $A155="caseid")</formula>
+      <formula>OR($A154="username", $A154="phonenumber", $A154="start", $A154="end", $A154="deviceid", $A154="subscriberid", $A154="simserial", $A154="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="138" priority="164" stopIfTrue="1">
-      <formula>$A155="end repeat"</formula>
+      <formula>$A154="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="137" priority="165" stopIfTrue="1">
-      <formula>$A155="begin repeat"</formula>
+      <formula>$A154="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="136" priority="166" stopIfTrue="1">
-      <formula>$A155="end group"</formula>
+      <formula>$A154="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="135" priority="167" stopIfTrue="1">
-      <formula>OR($A155="calculate", $A155="calculate_here")</formula>
+      <formula>OR($A154="calculate", $A154="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N214">
+  <conditionalFormatting sqref="N213">
     <cfRule type="expression" dxfId="134" priority="128" stopIfTrue="1">
-      <formula>$A214="enumerator"</formula>
+      <formula>$A213="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="133" priority="129" stopIfTrue="1">
-      <formula>$A214="barcode"</formula>
+      <formula>$A213="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="132" priority="130" stopIfTrue="1">
-      <formula>OR($A214="geopoint", $A214="geoshape", $A214="geotrace")</formula>
+      <formula>OR($A213="geopoint", $A213="geoshape", $A213="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="131" priority="131" stopIfTrue="1">
-      <formula>$A214="file"</formula>
+      <formula>$A213="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="130" priority="132" stopIfTrue="1">
-      <formula>$A214="note"</formula>
+      <formula>$A213="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="129" priority="133" stopIfTrue="1">
-      <formula>$A214="begin group"</formula>
+      <formula>$A213="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="128" priority="134" stopIfTrue="1">
-      <formula>OR($A214="audio", $A214="video")</formula>
+      <formula>OR($A213="audio", $A213="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="127" priority="135" stopIfTrue="1">
-      <formula>OR($A214="audio audit", $A214="text audit", $A214="speed violations count", $A214="speed violations list", $A214="speed violations audit")</formula>
+      <formula>OR($A213="audio audit", $A213="text audit", $A213="speed violations count", $A213="speed violations list", $A213="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="126" priority="136" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A214, 16)="select_multiple ", LEN($A214)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A214, 17)))), AND(LEFT($A214, 11)="select_one ", LEN($A214)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A214, 12)))))</formula>
+      <formula>OR(AND(LEFT($A213, 16)="select_multiple ", LEN($A213)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A213, 17)))), AND(LEFT($A213, 11)="select_one ", LEN($A213)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A213, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="125" priority="137" stopIfTrue="1">
-      <formula>$A214="decimal"</formula>
+      <formula>$A213="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="124" priority="138" stopIfTrue="1">
-      <formula>$A214="integer"</formula>
+      <formula>$A213="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="123" priority="139" stopIfTrue="1">
-      <formula>$A214="text"</formula>
+      <formula>$A213="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="122" priority="140" stopIfTrue="1">
-      <formula>$A214="image"</formula>
+      <formula>$A213="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="121" priority="141" stopIfTrue="1">
-      <formula>OR($A214="date", $A214="datetime", $A214="time")</formula>
+      <formula>OR($A213="date", $A213="datetime", $A213="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="120" priority="142" stopIfTrue="1">
-      <formula>OR($A214="calculate", $A214="calculate_here")</formula>
+      <formula>OR($A213="calculate", $A213="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="119" priority="143" stopIfTrue="1">
-      <formula>OR($A214="username", $A214="phonenumber", $A214="start", $A214="end", $A214="deviceid", $A214="subscriberid", $A214="simserial", $A214="caseid")</formula>
+      <formula>OR($A213="username", $A213="phonenumber", $A213="start", $A213="end", $A213="deviceid", $A213="subscriberid", $A213="simserial", $A213="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="118" priority="144" stopIfTrue="1">
-      <formula>$A214="end repeat"</formula>
+      <formula>$A213="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="117" priority="145" stopIfTrue="1">
-      <formula>$A214="begin repeat"</formula>
+      <formula>$A213="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="116" priority="146" stopIfTrue="1">
-      <formula>$A214="end group"</formula>
+      <formula>$A213="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="115" priority="147" stopIfTrue="1">
-      <formula>OR($A214="calculate", $A214="calculate_here")</formula>
+      <formula>OR($A213="calculate", $A213="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N217">
+  <conditionalFormatting sqref="N216">
     <cfRule type="expression" dxfId="114" priority="68" stopIfTrue="1">
-      <formula>$A217="enumerator"</formula>
+      <formula>$A216="enumerator"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="113" priority="69" stopIfTrue="1">
-      <formula>$A217="barcode"</formula>
+      <formula>$A216="barcode"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="112" priority="70" stopIfTrue="1">
-      <formula>OR($A217="geopoint", $A217="geoshape", $A217="geotrace")</formula>
+      <formula>OR($A216="geopoint", $A216="geoshape", $A216="geotrace")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="111" priority="71" stopIfTrue="1">
-      <formula>$A217="file"</formula>
+      <formula>$A216="file"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="110" priority="72" stopIfTrue="1">
-      <formula>$A217="note"</formula>
+      <formula>$A216="note"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="109" priority="73" stopIfTrue="1">
-      <formula>$A217="begin group"</formula>
+      <formula>$A216="begin group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="108" priority="74" stopIfTrue="1">
-      <formula>OR($A217="audio", $A217="video")</formula>
+      <formula>OR($A216="audio", $A216="video")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="107" priority="75" stopIfTrue="1">
-      <formula>OR($A217="audio audit", $A217="text audit", $A217="speed violations count", $A217="speed violations list", $A217="speed violations audit")</formula>
+      <formula>OR($A216="audio audit", $A216="text audit", $A216="speed violations count", $A216="speed violations list", $A216="speed violations audit")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="76" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A217, 16)="select_multiple ", LEN($A217)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A217, 17)))), AND(LEFT($A217, 11)="select_one ", LEN($A217)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A217, 12)))))</formula>
+      <formula>OR(AND(LEFT($A216, 16)="select_multiple ", LEN($A216)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A216, 17)))), AND(LEFT($A216, 11)="select_one ", LEN($A216)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A216, 12)))))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="77" stopIfTrue="1">
-      <formula>$A217="decimal"</formula>
+      <formula>$A216="decimal"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="104" priority="78" stopIfTrue="1">
-      <formula>$A217="integer"</formula>
+      <formula>$A216="integer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="103" priority="79" stopIfTrue="1">
-      <formula>$A217="text"</formula>
+      <formula>$A216="text"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="102" priority="80" stopIfTrue="1">
-      <formula>$A217="image"</formula>
+      <formula>$A216="image"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="81" stopIfTrue="1">
-      <formula>OR($A217="date", $A217="datetime", $A217="time")</formula>
+      <formula>OR($A216="date", $A216="datetime", $A216="time")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="82" stopIfTrue="1">
-      <formula>OR($A217="calculate", $A217="calculate_here")</formula>
+      <formula>OR($A216="calculate", $A216="calculate_here")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="99" priority="83" stopIfTrue="1">
-      <formula>OR($A217="username", $A217="phonenumber", $A217="start", $A217="end", $A217="deviceid", $A217="subscriberid", $A217="simserial", $A217="caseid")</formula>
+      <formula>OR($A216="username", $A216="phonenumber", $A216="start", $A216="end", $A216="deviceid", $A216="subscriberid", $A216="simserial", $A216="caseid")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="98" priority="84" stopIfTrue="1">
-      <formula>$A217="end repeat"</formula>
+      <formula>$A216="end repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="97" priority="85" stopIfTrue="1">
-      <formula>$A217="begin repeat"</formula>
+      <formula>$A216="begin repeat"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="96" priority="86" stopIfTrue="1">
-      <formula>$A217="end group"</formula>
+      <formula>$A216="end group"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="95" priority="87" stopIfTrue="1">
-      <formula>OR($A217="calculate", $A217="calculate_here")</formula>
+      <formula>OR($A216="calculate", $A216="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666667" right="0.74791666666666667" top="0.98402777777777772" bottom="0.98402777777777772" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -14809,7 +14777,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -14831,7 +14799,7 @@
         <v>77</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -14853,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -14864,7 +14832,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -14875,51 +14843,51 @@
         <v>3</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B20" s="14">
         <v>1</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B21" s="14">
         <v>2</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B22" s="14">
         <v>3</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B23" s="14">
         <v>4</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15177,535 +15145,535 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B47" s="14">
         <v>1</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B48" s="14">
         <v>2</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B49" s="14">
         <v>1</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B50" s="14">
         <v>2</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B51" s="14">
         <v>3</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B52" s="14">
         <v>66</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B53" s="14">
         <v>1</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B54" s="14">
         <v>2</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B55" s="14">
         <v>3</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B56" s="14">
         <v>66</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B57" s="14">
         <v>1</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B58" s="14">
         <v>2</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B59" s="14">
         <v>3</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B60" s="14">
         <v>4</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B61" s="14">
         <v>5</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B62" s="14">
         <v>6</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B63" s="14">
         <v>7</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B64" s="14">
         <v>8</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B65" s="14">
         <v>9</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B66" s="14">
         <v>10</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B67" s="14">
         <v>11</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B68" s="14">
         <v>12</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B69" s="14">
         <v>13</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B70" s="14">
         <v>14</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B71" s="14">
         <v>15</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B72" s="14">
         <v>16</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B73" s="14">
         <v>17</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B74" s="14">
         <v>1</v>
       </c>
       <c r="C74" s="53" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B75" s="14">
         <v>2</v>
       </c>
       <c r="C75" s="53" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B76" s="14">
         <v>3</v>
       </c>
       <c r="C76" s="53" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B77" s="14">
         <v>4</v>
       </c>
       <c r="C77" s="53" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B78" s="14">
         <v>5</v>
       </c>
       <c r="C78" s="53" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B79" s="14">
         <v>6</v>
       </c>
       <c r="C79" s="53" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B80" s="14">
         <v>7</v>
       </c>
       <c r="C80" s="53" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B81" s="14">
         <v>8</v>
       </c>
       <c r="C81" s="53" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B82" s="14">
         <v>9</v>
       </c>
       <c r="C82" s="53" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B83" s="14">
         <v>99</v>
       </c>
       <c r="C83" s="53" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B84" s="14">
         <v>1</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B85" s="14">
         <v>2</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B86" s="14">
         <v>3</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B87" s="14">
         <v>4</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B88" s="14">
         <v>1</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B89" s="14">
         <v>2</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B90" s="14">
         <v>3</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B91" s="14">
         <v>4</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B92" s="14">
         <v>5</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B93" s="14">
         <v>6</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B94" s="14">
         <v>66</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B95" s="14">
         <v>1</v>
@@ -15716,7 +15684,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B96" s="14">
         <v>2</v>
@@ -15727,1091 +15695,1091 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B97" s="14">
         <v>3</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B98" s="14">
         <v>99</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B99" s="14">
         <v>1</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B100" s="14">
         <v>2</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B101" s="14">
         <v>3</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B102" s="14">
         <v>4</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B103" s="14">
         <v>5</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B104" s="14">
         <v>99</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B105" s="14">
         <v>1</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B106" s="14">
         <v>2</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B107" s="14">
         <v>3</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B108" s="14">
         <v>4</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B109" s="14">
         <v>1</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B110" s="14">
         <v>2</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B111" s="14">
         <v>3</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B112" s="14">
         <v>4</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B113" s="14">
         <v>3</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B114" s="14">
         <v>99</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B115" s="14">
         <v>0</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B116" s="14">
         <v>1</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B117" s="14">
         <v>2</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B118" s="14">
         <v>3</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B119" s="14">
         <v>4</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B120" s="14">
         <v>5</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B121" s="14">
         <v>6</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B122" s="14">
         <v>7</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="14" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B123" s="14">
         <v>1</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="14" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B124" s="14">
         <v>2</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="14" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B125" s="14">
         <v>3</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B126" s="14">
         <v>1</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B127" s="14">
         <v>2</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B128" s="14">
         <v>3</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B129" s="14">
         <v>4</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B130" s="14">
         <v>5</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B131" s="14">
         <v>1</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B132" s="14">
         <v>2</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B133" s="14">
         <v>3</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B134" s="14">
         <v>1</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B135" s="14">
         <v>2</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B136" s="14">
         <v>3</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B137" s="14">
         <v>1</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B138" s="14">
         <v>2</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B139" s="14">
         <v>3</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B140" s="14">
         <v>4</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B141" s="14">
         <v>5</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B142" s="14">
         <v>6</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B143" s="14">
         <v>7</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B144" s="14">
         <v>8</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B145" s="14">
         <v>9</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B146" s="14">
         <v>10</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B147" s="14">
         <v>11</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B148" s="14">
         <v>12</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B149" s="14">
         <v>13</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B150" s="14">
         <v>66</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B151" s="14">
         <v>1</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B152" s="14">
         <v>2</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B153" s="14">
         <v>3</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B154" s="14">
         <v>4</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B155" s="14">
         <v>5</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B156" s="14">
         <v>1</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B157" s="14">
         <v>2</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B158" s="14">
         <v>3</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B159" s="14">
         <v>4</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B160" s="14">
         <v>5</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="16.5" thickBot="1">
       <c r="A161" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B161" s="14">
         <v>6</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B162" s="14">
         <v>1</v>
       </c>
       <c r="C162" s="55" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B163" s="14">
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B164" s="14">
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B165" s="14">
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B166" s="14">
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B167" s="14">
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B168" s="14">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B169" s="14">
         <v>66</v>
       </c>
       <c r="C169" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="16.5" thickBot="1">
       <c r="A170" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B170" s="14">
         <v>8</v>
       </c>
       <c r="C170" s="56" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B171" s="14">
         <v>1</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B172" s="14">
         <v>2</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B173" s="14">
         <v>3</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B174" s="14">
         <v>4</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B175" s="14">
         <v>5</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B176" s="14">
         <v>6</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B177" s="14">
         <v>7</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B178" s="14">
         <v>66</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B179" s="14">
         <v>8</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B180" s="14">
         <v>1</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B181" s="14">
         <v>2</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B182" s="14">
         <v>3</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B183" s="14">
         <v>4</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B184" s="14">
         <v>5</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B185" s="14">
         <v>6</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B186" s="14">
         <v>7</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B187" s="14">
         <v>8</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B188" s="14">
         <v>9</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B189" s="14">
         <v>10</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B190" s="14">
         <v>11</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B191" s="14">
         <v>12</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B192" s="14">
         <v>13</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B193" s="14">
         <v>14</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B194" s="14">
         <v>15</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="14" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B195" s="14">
         <v>16</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -16925,19 +16893,19 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C2" s="15" t="str">
         <f ca="1">TEXT(YEAR(NOW())-2000, "00") &amp; TEXT(MONTH(NOW()), "00") &amp; TEXT(DAY(NOW()), "00") &amp; TEXT(HOUR(NOW()), "00") &amp; TEXT(MINUTE(NOW()), "00")</f>
-        <v>2602271516</v>
+        <v>2603031153</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="17"/>
       <c r="F2" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
